--- a/meta_leases_capex_analysis.xlsx
+++ b/meta_leases_capex_analysis.xlsx
@@ -7,10 +7,11 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="CapEx Comparison" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Meta Leases Detail" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Margin Impact" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Peer Lease Comparison" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Lease Matrix" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="CapEx Comparison" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Meta Leases Detail" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Margin Impact" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Peer Lease Comparison" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -19,11 +20,12 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="3">
     <numFmt numFmtId="164" formatCode="#,##0.0"/>
     <numFmt numFmtId="165" formatCode="0.0%"/>
+    <numFmt numFmtId="166" formatCode="0.00x"/>
   </numFmts>
-  <fonts count="7">
+  <fonts count="12">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -63,8 +65,35 @@
       <b val="1"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00548235"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <i val="1"/>
+      <color rgb="00BF8F00"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <sz val="9"/>
+    </font>
   </fonts>
-  <fills count="8">
+  <fills count="11">
     <fill>
       <patternFill/>
     </fill>
@@ -107,8 +136,26 @@
         <bgColor rgb="00C6EFCE"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="0044546A"/>
+        <bgColor rgb="0044546A"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F2F2F2"/>
+        <bgColor rgb="00F2F2F2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FCE4D6"/>
+        <bgColor rgb="00FCE4D6"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -122,11 +169,39 @@
       <top style="thin"/>
       <bottom style="thin"/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin"/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="36">
+  <cellXfs count="58">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -221,6 +296,66 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="8" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -586,6 +721,1584 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:J53"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
+    <col width="30" customWidth="1" min="9" max="9"/>
+    <col width="48" customWidth="1" min="10" max="10"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="20" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Hyperscaler-to-Landlord Data Center Lease Matrix</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="n"/>
+      <c r="C1" s="1" t="n"/>
+      <c r="D1" s="1" t="n"/>
+      <c r="E1" s="1" t="n"/>
+      <c r="F1" s="1" t="n"/>
+      <c r="G1" s="1" t="n"/>
+      <c r="H1" s="1" t="n"/>
+      <c r="I1" s="1" t="n"/>
+      <c r="J1" s="1" t="n"/>
+    </row>
+    <row r="2" ht="20" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Who leases from whom  |  Confirmed relationships as of Q1 2026  |  ✓ = confirmed tenant, ~ = suspected/indirect</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="2" t="n"/>
+      <c r="D2" s="2" t="n"/>
+      <c r="E2" s="2" t="n"/>
+      <c r="F2" s="2" t="n"/>
+      <c r="G2" s="2" t="n"/>
+      <c r="H2" s="2" t="n"/>
+      <c r="I2" s="2" t="n"/>
+      <c r="J2" s="2" t="n"/>
+    </row>
+    <row r="3" ht="20" customHeight="1"/>
+    <row r="4" ht="20" customHeight="1">
+      <c r="A4" s="36" t="inlineStr">
+        <is>
+          <t>A. DATA CENTER OPERATOR / LANDLORD  ×  HYPERSCALER TENANT MATRIX</t>
+        </is>
+      </c>
+      <c r="B4" s="36" t="n"/>
+      <c r="C4" s="36" t="n"/>
+      <c r="D4" s="36" t="n"/>
+      <c r="E4" s="36" t="n"/>
+      <c r="F4" s="36" t="n"/>
+      <c r="G4" s="36" t="n"/>
+      <c r="H4" s="36" t="n"/>
+      <c r="I4" s="36" t="n"/>
+      <c r="J4" s="36" t="n"/>
+    </row>
+    <row r="5" ht="20" customHeight="1">
+      <c r="A5" s="37" t="inlineStr">
+        <is>
+          <t>DC Operator / Landlord</t>
+        </is>
+      </c>
+      <c r="B5" s="37" t="inlineStr">
+        <is>
+          <t>Capacity (GW)</t>
+        </is>
+      </c>
+      <c r="C5" s="37" t="inlineStr">
+        <is>
+          <t>Amazon / AWS</t>
+        </is>
+      </c>
+      <c r="D5" s="37" t="inlineStr">
+        <is>
+          <t>Microsoft</t>
+        </is>
+      </c>
+      <c r="E5" s="37" t="inlineStr">
+        <is>
+          <t>Google / Alphabet</t>
+        </is>
+      </c>
+      <c r="F5" s="37" t="inlineStr">
+        <is>
+          <t>Meta</t>
+        </is>
+      </c>
+      <c r="G5" s="37" t="inlineStr">
+        <is>
+          <t>Oracle</t>
+        </is>
+      </c>
+      <c r="H5" s="37" t="inlineStr">
+        <is>
+          <t>CoreWeave / xAI</t>
+        </is>
+      </c>
+      <c r="I5" s="37" t="inlineStr">
+        <is>
+          <t>Owner / Backer</t>
+        </is>
+      </c>
+      <c r="J5" s="37" t="inlineStr">
+        <is>
+          <t>Key Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="20" customHeight="1">
+      <c r="A6" s="10" t="inlineStr">
+        <is>
+          <t>QTS Realty Trust</t>
+        </is>
+      </c>
+      <c r="B6" s="38" t="inlineStr">
+        <is>
+          <t>4.8 GW</t>
+        </is>
+      </c>
+      <c r="C6" s="39" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="D6" s="39" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="E6" s="39" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="F6" s="40" t="inlineStr">
+        <is>
+          <t>~</t>
+        </is>
+      </c>
+      <c r="G6" s="39" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="H6" s="38" t="inlineStr"/>
+      <c r="I6" s="41" t="inlineStr">
+        <is>
+          <t>Blackstone ($10B acq. 2021)</t>
+        </is>
+      </c>
+      <c r="J6" s="41" t="inlineStr">
+        <is>
+          <t>Largest by MW; AWS anchor in ATL, CHI, NJ. $12B+ investment pipeline.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="20" customHeight="1">
+      <c r="A7" s="42" t="inlineStr">
+        <is>
+          <t>Vantage Data Centers</t>
+        </is>
+      </c>
+      <c r="B7" s="43" t="inlineStr">
+        <is>
+          <t>4.2 GW</t>
+        </is>
+      </c>
+      <c r="C7" s="39" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="D7" s="39" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="E7" s="39" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="F7" s="39" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="G7" s="43" t="inlineStr"/>
+      <c r="H7" s="43" t="inlineStr"/>
+      <c r="I7" s="44" t="inlineStr">
+        <is>
+          <t>DigitalBridge / Silver Lake</t>
+        </is>
+      </c>
+      <c r="J7" s="44" t="inlineStr">
+        <is>
+          <t>100% hyperscale focus. Frontier Campus TX (1.4 GW), Port Washington WI (1.3 GW).</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="20" customHeight="1">
+      <c r="A8" s="10" t="inlineStr">
+        <is>
+          <t>Digital Realty Trust (DLR)</t>
+        </is>
+      </c>
+      <c r="B8" s="38" t="inlineStr">
+        <is>
+          <t>2.3 GW</t>
+        </is>
+      </c>
+      <c r="C8" s="39" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="D8" s="39" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="E8" s="39" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="F8" s="39" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="G8" s="39" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="H8" s="38" t="inlineStr"/>
+      <c r="I8" s="41" t="inlineStr">
+        <is>
+          <t>Public REIT (NYSE: DLR)</t>
+        </is>
+      </c>
+      <c r="J8" s="41" t="inlineStr">
+        <is>
+          <t>310 DCs, 42.5M sq ft. $817M backlog. Broadest tenant diversification.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="20" customHeight="1">
+      <c r="A9" s="42" t="inlineStr">
+        <is>
+          <t>STACK Infrastructure</t>
+        </is>
+      </c>
+      <c r="B9" s="43" t="inlineStr">
+        <is>
+          <t>7.5+ GW</t>
+        </is>
+      </c>
+      <c r="C9" s="39" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="D9" s="40" t="inlineStr">
+        <is>
+          <t>~</t>
+        </is>
+      </c>
+      <c r="E9" s="40" t="inlineStr">
+        <is>
+          <t>~</t>
+        </is>
+      </c>
+      <c r="F9" s="43" t="inlineStr"/>
+      <c r="G9" s="39" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="H9" s="43" t="inlineStr"/>
+      <c r="I9" s="44" t="inlineStr">
+        <is>
+          <t>IPI Partners / Mubadala</t>
+        </is>
+      </c>
+      <c r="J9" s="44" t="inlineStr">
+        <is>
+          <t>$12B Amazon partnership in Louisiana. 24 global markets. GW-scale campuses.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="20" customHeight="1">
+      <c r="A10" s="10" t="inlineStr">
+        <is>
+          <t>Aligned Data Centers</t>
+        </is>
+      </c>
+      <c r="B10" s="38" t="inlineStr">
+        <is>
+          <t>5.0 GW</t>
+        </is>
+      </c>
+      <c r="C10" s="38" t="inlineStr"/>
+      <c r="D10" s="39" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="E10" s="38" t="inlineStr"/>
+      <c r="F10" s="38" t="inlineStr"/>
+      <c r="G10" s="38" t="inlineStr"/>
+      <c r="H10" s="39" t="inlineStr">
+        <is>
+          <t>✓ (xAI)</t>
+        </is>
+      </c>
+      <c r="I10" s="41" t="inlineStr">
+        <is>
+          <t>BlackRock AIP / Nvidia / MSFT / xAI</t>
+        </is>
+      </c>
+      <c r="J10" s="41" t="inlineStr">
+        <is>
+          <t>$40B acquisition (Oct 2025). 50 campuses. Largest DC deal in history.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="20" customHeight="1">
+      <c r="A11" s="42" t="inlineStr">
+        <is>
+          <t>Equinix (EQIX)</t>
+        </is>
+      </c>
+      <c r="B11" s="43" t="inlineStr">
+        <is>
+          <t>0.5 GW</t>
+        </is>
+      </c>
+      <c r="C11" s="39" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="D11" s="39" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="E11" s="39" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="F11" s="39" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="G11" s="39" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="H11" s="43" t="inlineStr"/>
+      <c r="I11" s="44" t="inlineStr">
+        <is>
+          <t>Public REIT (NYSE: EQIX)</t>
+        </is>
+      </c>
+      <c r="J11" s="44" t="inlineStr">
+        <is>
+          <t>Interconnection-focused. 260+ DCs. 63% of Fortune 500. Direct cloud on-ramps.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="20" customHeight="1">
+      <c r="A12" s="10" t="inlineStr">
+        <is>
+          <t>CyrusOne</t>
+        </is>
+      </c>
+      <c r="B12" s="38" t="inlineStr">
+        <is>
+          <t>0.8 GW</t>
+        </is>
+      </c>
+      <c r="C12" s="39" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="D12" s="39" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="E12" s="38" t="inlineStr"/>
+      <c r="F12" s="38" t="inlineStr"/>
+      <c r="G12" s="38" t="inlineStr"/>
+      <c r="H12" s="38" t="inlineStr"/>
+      <c r="I12" s="41" t="inlineStr">
+        <is>
+          <t>KKR / GIP (acq. 2022)</t>
+        </is>
+      </c>
+      <c r="J12" s="41" t="inlineStr">
+        <is>
+          <t>AWS &amp; MSFT London leases. Calpine energy partnership (400 MW TX).</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="20" customHeight="1">
+      <c r="A13" s="42" t="inlineStr">
+        <is>
+          <t>Compass Datacenters</t>
+        </is>
+      </c>
+      <c r="B13" s="43" t="inlineStr">
+        <is>
+          <t>~2.0 GW</t>
+        </is>
+      </c>
+      <c r="C13" s="43" t="inlineStr"/>
+      <c r="D13" s="40" t="inlineStr">
+        <is>
+          <t>~</t>
+        </is>
+      </c>
+      <c r="E13" s="43" t="inlineStr"/>
+      <c r="F13" s="40" t="inlineStr">
+        <is>
+          <t>~</t>
+        </is>
+      </c>
+      <c r="G13" s="43" t="inlineStr"/>
+      <c r="H13" s="43" t="inlineStr"/>
+      <c r="I13" s="44" t="inlineStr">
+        <is>
+          <t>Brookfield Infra / OTPP</t>
+        </is>
+      </c>
+      <c r="J13" s="44" t="inlineStr">
+        <is>
+          <t>$10B Meridian MS campus. Tenant undisclosed (suspected Meta or MSFT).</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="20" customHeight="1">
+      <c r="A14" s="10" t="inlineStr">
+        <is>
+          <t>Crusoe Energy Systems</t>
+        </is>
+      </c>
+      <c r="B14" s="38" t="inlineStr">
+        <is>
+          <t>1.2 GW</t>
+        </is>
+      </c>
+      <c r="C14" s="38" t="inlineStr"/>
+      <c r="D14" s="40" t="inlineStr">
+        <is>
+          <t>~</t>
+        </is>
+      </c>
+      <c r="E14" s="38" t="inlineStr"/>
+      <c r="F14" s="38" t="inlineStr"/>
+      <c r="G14" s="39" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="H14" s="38" t="inlineStr"/>
+      <c r="I14" s="41" t="inlineStr">
+        <is>
+          <t>Blue Owl / PE-backed</t>
+        </is>
+      </c>
+      <c r="J14" s="41" t="inlineStr">
+        <is>
+          <t>Abilene TX flagship. Oracle tenant → leases to MSFT → OpenAI. 15-yr lease.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="20" customHeight="1">
+      <c r="A15" s="42" t="inlineStr">
+        <is>
+          <t>Hut 8 Corp</t>
+        </is>
+      </c>
+      <c r="B15" s="43" t="inlineStr">
+        <is>
+          <t>0.3 GW</t>
+        </is>
+      </c>
+      <c r="C15" s="43" t="inlineStr"/>
+      <c r="D15" s="43" t="inlineStr"/>
+      <c r="E15" s="39" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="F15" s="43" t="inlineStr"/>
+      <c r="G15" s="43" t="inlineStr"/>
+      <c r="H15" s="43" t="inlineStr"/>
+      <c r="I15" s="44" t="inlineStr">
+        <is>
+          <t>Public (NASDAQ: HUT)</t>
+        </is>
+      </c>
+      <c r="J15" s="44" t="inlineStr">
+        <is>
+          <t>$7B, 15-yr lease w/ Fluidstack (Google-backed). River Bend LA. 245 MW.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="20" customHeight="1">
+      <c r="A16" s="10" t="inlineStr">
+        <is>
+          <t>Applied Digital</t>
+        </is>
+      </c>
+      <c r="B16" s="38" t="inlineStr">
+        <is>
+          <t>0.4 GW</t>
+        </is>
+      </c>
+      <c r="C16" s="38" t="inlineStr"/>
+      <c r="D16" s="38" t="inlineStr"/>
+      <c r="E16" s="38" t="inlineStr"/>
+      <c r="F16" s="38" t="inlineStr"/>
+      <c r="G16" s="38" t="inlineStr"/>
+      <c r="H16" s="39" t="inlineStr">
+        <is>
+          <t>✓ (CoreWeave)</t>
+        </is>
+      </c>
+      <c r="I16" s="41" t="inlineStr">
+        <is>
+          <t>Public (NASDAQ: APLD)</t>
+        </is>
+      </c>
+      <c r="J16" s="41" t="inlineStr">
+        <is>
+          <t>$11B contracted from CoreWeave. Polaris Forge ND campus. 400 MW.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="20" customHeight="1">
+      <c r="A17" s="42" t="inlineStr">
+        <is>
+          <t>EdgeConneX</t>
+        </is>
+      </c>
+      <c r="B17" s="43" t="inlineStr">
+        <is>
+          <t>1.0+ GW</t>
+        </is>
+      </c>
+      <c r="C17" s="39" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="D17" s="39" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="E17" s="39" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="F17" s="40" t="inlineStr">
+        <is>
+          <t>~</t>
+        </is>
+      </c>
+      <c r="G17" s="39" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="H17" s="43" t="inlineStr"/>
+      <c r="I17" s="44" t="inlineStr">
+        <is>
+          <t>EQT Partners</t>
+        </is>
+      </c>
+      <c r="J17" s="44" t="inlineStr">
+        <is>
+          <t>80+ DCs, 60+ markets, 20+ countries. Cloud on-ramps for all major providers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="20" customHeight="1">
+      <c r="A18" s="10" t="inlineStr">
+        <is>
+          <t>Meta SPV (Pimco / Blue Owl)</t>
+        </is>
+      </c>
+      <c r="B18" s="38" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C18" s="38" t="inlineStr"/>
+      <c r="D18" s="38" t="inlineStr"/>
+      <c r="E18" s="38" t="inlineStr"/>
+      <c r="F18" s="39" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="G18" s="38" t="inlineStr"/>
+      <c r="H18" s="38" t="inlineStr"/>
+      <c r="I18" s="41" t="inlineStr">
+        <is>
+          <t>Meta 20% co-ownership</t>
+        </is>
+      </c>
+      <c r="J18" s="41" t="inlineStr">
+        <is>
+          <t>Louisiana Hyperion: $29B Pimco debt + $3B Blue Owl equity. Build-to-suit.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="20" customHeight="1">
+      <c r="A19" s="42" t="inlineStr">
+        <is>
+          <t>Stargate JV (Oracle-led)</t>
+        </is>
+      </c>
+      <c r="B19" s="43" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C19" s="43" t="inlineStr"/>
+      <c r="D19" s="39" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="E19" s="43" t="inlineStr"/>
+      <c r="F19" s="40" t="inlineStr">
+        <is>
+          <t>~</t>
+        </is>
+      </c>
+      <c r="G19" s="39" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="H19" s="43" t="inlineStr"/>
+      <c r="I19" s="44" t="inlineStr">
+        <is>
+          <t>Oracle / SoftBank / OpenAI</t>
+        </is>
+      </c>
+      <c r="J19" s="44" t="inlineStr">
+        <is>
+          <t>Abilene TX mega-campus. MSFT &amp; Meta negotiating capacity. $500B vision.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="20" customHeight="1"/>
+    <row r="21" ht="20" customHeight="1"/>
+    <row r="22" ht="20" customHeight="1">
+      <c r="A22" s="36" t="inlineStr">
+        <is>
+          <t>B. HYPERSCALER FUTURE LEASE COMMITMENTS (as of Q1 2026, $B)</t>
+        </is>
+      </c>
+      <c r="B22" s="36" t="n"/>
+      <c r="C22" s="36" t="n"/>
+      <c r="D22" s="36" t="n"/>
+      <c r="E22" s="36" t="n"/>
+      <c r="F22" s="36" t="n"/>
+      <c r="G22" s="36" t="n"/>
+      <c r="H22" s="36" t="n"/>
+      <c r="I22" s="36" t="n"/>
+      <c r="J22" s="36" t="n"/>
+    </row>
+    <row r="23" ht="20" customHeight="1">
+      <c r="A23" s="45" t="inlineStr">
+        <is>
+          <t>Hyperscaler</t>
+        </is>
+      </c>
+      <c r="B23" s="37" t="inlineStr">
+        <is>
+          <t>Total Future Lease Commitments ($B)</t>
+        </is>
+      </c>
+      <c r="C23" s="37" t="inlineStr">
+        <is>
+          <t>On-Balance-Sheet Lease Liab. ($B)</t>
+        </is>
+      </c>
+      <c r="D23" s="37" t="inlineStr">
+        <is>
+          <t>Off-B/S Uncommenced Leases ($B)</t>
+        </is>
+      </c>
+      <c r="E23" s="37" t="inlineStr">
+        <is>
+          <t>Lease Commit. / Revenue</t>
+        </is>
+      </c>
+      <c r="F23" s="37" t="inlineStr">
+        <is>
+          <t>Lease Commit. / Op. Income</t>
+        </is>
+      </c>
+      <c r="G23" s="37" t="inlineStr">
+        <is>
+          <t>Primary Lease Strategy</t>
+        </is>
+      </c>
+      <c r="H23" s="37" t="inlineStr">
+        <is>
+          <t>Key Landlord Partners</t>
+        </is>
+      </c>
+      <c r="I23" s="46" t="inlineStr"/>
+      <c r="J23" s="46" t="inlineStr"/>
+    </row>
+    <row r="24" ht="20" customHeight="1">
+      <c r="A24" s="10" t="inlineStr">
+        <is>
+          <t>Oracle</t>
+        </is>
+      </c>
+      <c r="B24" s="47" t="n">
+        <v>261</v>
+      </c>
+      <c r="C24" s="48" t="n">
+        <v>13</v>
+      </c>
+      <c r="D24" s="47" t="n">
+        <v>248</v>
+      </c>
+      <c r="E24" s="49" t="n">
+        <v>4.35</v>
+      </c>
+      <c r="F24" s="49" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="G24" s="41" t="inlineStr">
+        <is>
+          <t>Aggressive third-party leasing; Stargate anchor</t>
+        </is>
+      </c>
+      <c r="H24" s="41" t="inlineStr">
+        <is>
+          <t>Crusoe, Stargate JV, EdgeConneX</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="20" customHeight="1">
+      <c r="A25" s="42" t="inlineStr">
+        <is>
+          <t>Microsoft</t>
+        </is>
+      </c>
+      <c r="B25" s="50" t="n">
+        <v>155</v>
+      </c>
+      <c r="C25" s="50" t="n">
+        <v>50</v>
+      </c>
+      <c r="D25" s="50" t="n">
+        <v>105</v>
+      </c>
+      <c r="E25" s="51" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="F25" s="51" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="G25" s="44" t="inlineStr">
+        <is>
+          <t>Mix of owned + build-to-suit + co-invested (AIP/Aligned)</t>
+        </is>
+      </c>
+      <c r="H25" s="44" t="inlineStr">
+        <is>
+          <t>Aligned, QTS, Vantage, CyrusOne, Compass</t>
+        </is>
+      </c>
+      <c r="I25" s="52" t="n"/>
+      <c r="J25" s="52" t="n"/>
+    </row>
+    <row r="26" ht="20" customHeight="1">
+      <c r="A26" s="10" t="inlineStr">
+        <is>
+          <t>Meta</t>
+        </is>
+      </c>
+      <c r="B26" s="48" t="n">
+        <v>104</v>
+      </c>
+      <c r="C26" s="48" t="n">
+        <v>26.1</v>
+      </c>
+      <c r="D26" s="48" t="n">
+        <v>78</v>
+      </c>
+      <c r="E26" s="49" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="F26" s="49" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="G26" s="41" t="inlineStr">
+        <is>
+          <t>SPV-financed build-to-suit; growing third-party leasing</t>
+        </is>
+      </c>
+      <c r="H26" s="41" t="inlineStr">
+        <is>
+          <t>Pimco/Blue Owl SPV, Digital Realty, Vantage, EdgeConneX</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="20" customHeight="1">
+      <c r="A27" s="42" t="inlineStr">
+        <is>
+          <t>Google / Alphabet</t>
+        </is>
+      </c>
+      <c r="B27" s="50" t="n">
+        <v>42.6</v>
+      </c>
+      <c r="C27" s="50" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="D27" s="50" t="n">
+        <v>20.1</v>
+      </c>
+      <c r="E27" s="51" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="F27" s="51" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="G27" s="44" t="inlineStr">
+        <is>
+          <t>Mostly owned; selective leasing for speed-to-capacity</t>
+        </is>
+      </c>
+      <c r="H27" s="44" t="inlineStr">
+        <is>
+          <t>Hut 8 (Fluidstack), Digital Realty, Vantage, QTS</t>
+        </is>
+      </c>
+      <c r="I27" s="52" t="n"/>
+      <c r="J27" s="52" t="n"/>
+    </row>
+    <row r="28" ht="20" customHeight="1">
+      <c r="A28" s="10" t="inlineStr">
+        <is>
+          <t>Amazon / AWS</t>
+        </is>
+      </c>
+      <c r="B28" s="38" t="inlineStr">
+        <is>
+          <t>~80-100</t>
+        </is>
+      </c>
+      <c r="C28" s="48" t="n">
+        <v>160</v>
+      </c>
+      <c r="D28" s="38" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="E28" s="38" t="inlineStr">
+        <is>
+          <t>~0.13</t>
+        </is>
+      </c>
+      <c r="F28" s="38" t="inlineStr">
+        <is>
+          <t>~1.2</t>
+        </is>
+      </c>
+      <c r="G28" s="41" t="inlineStr">
+        <is>
+          <t>Mix of owned mega-campuses + colocation at scale</t>
+        </is>
+      </c>
+      <c r="H28" s="41" t="inlineStr">
+        <is>
+          <t>QTS, STACK, Vantage, Digital Realty, EdgeConneX</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="20" customHeight="1"/>
+    <row r="30" ht="20" customHeight="1">
+      <c r="A30" s="36" t="inlineStr">
+        <is>
+          <t>C. TOP CUSTOMERS / TENANTS BY DATA CENTER OPERATOR (Ranked by Estimated Revenue Contribution)</t>
+        </is>
+      </c>
+      <c r="B30" s="36" t="n"/>
+      <c r="C30" s="36" t="n"/>
+      <c r="D30" s="36" t="n"/>
+      <c r="E30" s="36" t="n"/>
+      <c r="F30" s="36" t="n"/>
+      <c r="G30" s="36" t="n"/>
+      <c r="H30" s="36" t="n"/>
+      <c r="I30" s="36" t="n"/>
+      <c r="J30" s="36" t="n"/>
+    </row>
+    <row r="31" ht="20" customHeight="1">
+      <c r="A31" s="37" t="inlineStr">
+        <is>
+          <t>DC Operator</t>
+        </is>
+      </c>
+      <c r="B31" s="37" t="inlineStr">
+        <is>
+          <t>#1 Customer</t>
+        </is>
+      </c>
+      <c r="C31" s="37" t="inlineStr">
+        <is>
+          <t>#2 Customer</t>
+        </is>
+      </c>
+      <c r="D31" s="37" t="inlineStr">
+        <is>
+          <t>#3 Customer</t>
+        </is>
+      </c>
+      <c r="E31" s="37" t="inlineStr">
+        <is>
+          <t>Revenue Concentration Risk</t>
+        </is>
+      </c>
+      <c r="F31" s="37" t="inlineStr">
+        <is>
+          <t>Avg Lease Term (Yrs)</t>
+        </is>
+      </c>
+      <c r="G31" s="37" t="inlineStr">
+        <is>
+          <t>Lease Structure</t>
+        </is>
+      </c>
+      <c r="H31" s="37" t="inlineStr">
+        <is>
+          <t>Est. Annual Rent from Top 3 ($B)</t>
+        </is>
+      </c>
+      <c r="I31" s="46" t="inlineStr"/>
+      <c r="J31" s="46" t="inlineStr"/>
+    </row>
+    <row r="32" ht="20" customHeight="1">
+      <c r="A32" s="10" t="inlineStr">
+        <is>
+          <t>QTS (Blackstone)</t>
+        </is>
+      </c>
+      <c r="B32" s="38" t="inlineStr">
+        <is>
+          <t>Amazon / AWS</t>
+        </is>
+      </c>
+      <c r="C32" s="38" t="inlineStr">
+        <is>
+          <t>Microsoft</t>
+        </is>
+      </c>
+      <c r="D32" s="38" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="E32" s="53" t="inlineStr">
+        <is>
+          <t>High — dominated by 2-3 hyperscalers</t>
+        </is>
+      </c>
+      <c r="F32" s="38" t="inlineStr">
+        <is>
+          <t>10-20</t>
+        </is>
+      </c>
+      <c r="G32" s="41" t="inlineStr">
+        <is>
+          <t>Triple-net, build-to-suit</t>
+        </is>
+      </c>
+      <c r="H32" s="38" t="inlineStr">
+        <is>
+          <t>~$4-6</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="20" customHeight="1">
+      <c r="A33" s="42" t="inlineStr">
+        <is>
+          <t>Vantage</t>
+        </is>
+      </c>
+      <c r="B33" s="43" t="inlineStr">
+        <is>
+          <t>Microsoft</t>
+        </is>
+      </c>
+      <c r="C33" s="43" t="inlineStr">
+        <is>
+          <t>Meta</t>
+        </is>
+      </c>
+      <c r="D33" s="43" t="inlineStr">
+        <is>
+          <t>Amazon / AWS</t>
+        </is>
+      </c>
+      <c r="E33" s="54" t="inlineStr">
+        <is>
+          <t>Very High — 100% hyperscale</t>
+        </is>
+      </c>
+      <c r="F33" s="43" t="inlineStr">
+        <is>
+          <t>15-20</t>
+        </is>
+      </c>
+      <c r="G33" s="44" t="inlineStr">
+        <is>
+          <t>Single-tenant, shell + core</t>
+        </is>
+      </c>
+      <c r="H33" s="43" t="inlineStr">
+        <is>
+          <t>~$3-5</t>
+        </is>
+      </c>
+      <c r="I33" s="52" t="n"/>
+      <c r="J33" s="52" t="n"/>
+    </row>
+    <row r="34" ht="20" customHeight="1">
+      <c r="A34" s="10" t="inlineStr">
+        <is>
+          <t>Digital Realty (DLR)</t>
+        </is>
+      </c>
+      <c r="B34" s="38" t="inlineStr">
+        <is>
+          <t>Meta</t>
+        </is>
+      </c>
+      <c r="C34" s="38" t="inlineStr">
+        <is>
+          <t>Oracle</t>
+        </is>
+      </c>
+      <c r="D34" s="38" t="inlineStr">
+        <is>
+          <t>Amazon / AWS</t>
+        </is>
+      </c>
+      <c r="E34" s="41" t="inlineStr">
+        <is>
+          <t>Moderate — diversified portfolio</t>
+        </is>
+      </c>
+      <c r="F34" s="38" t="inlineStr">
+        <is>
+          <t>7-15</t>
+        </is>
+      </c>
+      <c r="G34" s="41" t="inlineStr">
+        <is>
+          <t>Mix: colo + build-to-suit</t>
+        </is>
+      </c>
+      <c r="H34" s="38" t="inlineStr">
+        <is>
+          <t>~$2-4</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="20" customHeight="1">
+      <c r="A35" s="42" t="inlineStr">
+        <is>
+          <t>STACK Infrastructure</t>
+        </is>
+      </c>
+      <c r="B35" s="43" t="inlineStr">
+        <is>
+          <t>Amazon / AWS</t>
+        </is>
+      </c>
+      <c r="C35" s="43" t="inlineStr">
+        <is>
+          <t>Oracle</t>
+        </is>
+      </c>
+      <c r="D35" s="43" t="inlineStr">
+        <is>
+          <t>Microsoft</t>
+        </is>
+      </c>
+      <c r="E35" s="53" t="inlineStr">
+        <is>
+          <t>High — anchor-tenant campuses</t>
+        </is>
+      </c>
+      <c r="F35" s="43" t="inlineStr">
+        <is>
+          <t>15-25</t>
+        </is>
+      </c>
+      <c r="G35" s="44" t="inlineStr">
+        <is>
+          <t>Powered shell, triple-net</t>
+        </is>
+      </c>
+      <c r="H35" s="43" t="inlineStr">
+        <is>
+          <t>~$2-3</t>
+        </is>
+      </c>
+      <c r="I35" s="52" t="n"/>
+      <c r="J35" s="52" t="n"/>
+    </row>
+    <row r="36" ht="20" customHeight="1">
+      <c r="A36" s="10" t="inlineStr">
+        <is>
+          <t>Aligned (BlackRock AIP)</t>
+        </is>
+      </c>
+      <c r="B36" s="38" t="inlineStr">
+        <is>
+          <t>Microsoft</t>
+        </is>
+      </c>
+      <c r="C36" s="38" t="inlineStr">
+        <is>
+          <t>xAI</t>
+        </is>
+      </c>
+      <c r="D36" s="38" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E36" s="54" t="inlineStr">
+        <is>
+          <t>Very High — consortium-owned</t>
+        </is>
+      </c>
+      <c r="F36" s="38" t="inlineStr">
+        <is>
+          <t>10-20</t>
+        </is>
+      </c>
+      <c r="G36" s="41" t="inlineStr">
+        <is>
+          <t>Co-invested, build-to-suit</t>
+        </is>
+      </c>
+      <c r="H36" s="38" t="inlineStr">
+        <is>
+          <t>~$2-4</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="20" customHeight="1">
+      <c r="A37" s="42" t="inlineStr">
+        <is>
+          <t>Equinix (EQIX)</t>
+        </is>
+      </c>
+      <c r="B37" s="43" t="inlineStr">
+        <is>
+          <t>Amazon / AWS</t>
+        </is>
+      </c>
+      <c r="C37" s="43" t="inlineStr">
+        <is>
+          <t>Microsoft</t>
+        </is>
+      </c>
+      <c r="D37" s="43" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="E37" s="53" t="inlineStr">
+        <is>
+          <t>Low — highly diversified (10K+ customers)</t>
+        </is>
+      </c>
+      <c r="F37" s="43" t="inlineStr">
+        <is>
+          <t>3-5</t>
+        </is>
+      </c>
+      <c r="G37" s="44" t="inlineStr">
+        <is>
+          <t>Retail colo + interconnection</t>
+        </is>
+      </c>
+      <c r="H37" s="43" t="inlineStr">
+        <is>
+          <t>~$1-2</t>
+        </is>
+      </c>
+      <c r="I37" s="52" t="n"/>
+      <c r="J37" s="52" t="n"/>
+    </row>
+    <row r="38" ht="20" customHeight="1">
+      <c r="A38" s="10" t="inlineStr">
+        <is>
+          <t>CyrusOne (KKR/GIP)</t>
+        </is>
+      </c>
+      <c r="B38" s="38" t="inlineStr">
+        <is>
+          <t>Amazon / AWS</t>
+        </is>
+      </c>
+      <c r="C38" s="38" t="inlineStr">
+        <is>
+          <t>Microsoft</t>
+        </is>
+      </c>
+      <c r="D38" s="38" t="inlineStr">
+        <is>
+          <t>Enterprise mix</t>
+        </is>
+      </c>
+      <c r="E38" s="41" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="F38" s="38" t="inlineStr">
+        <is>
+          <t>10-15</t>
+        </is>
+      </c>
+      <c r="G38" s="41" t="inlineStr">
+        <is>
+          <t>Build-to-suit hyperscale</t>
+        </is>
+      </c>
+      <c r="H38" s="38" t="inlineStr">
+        <is>
+          <t>~$0.5-1</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="20" customHeight="1">
+      <c r="A39" s="42" t="inlineStr">
+        <is>
+          <t>Compass (Brookfield)</t>
+        </is>
+      </c>
+      <c r="B39" s="43" t="inlineStr">
+        <is>
+          <t>Undisclosed (Meta or MSFT)</t>
+        </is>
+      </c>
+      <c r="C39" s="43" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D39" s="43" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E39" s="54" t="inlineStr">
+        <is>
+          <t>Very High — single-tenant design</t>
+        </is>
+      </c>
+      <c r="F39" s="43" t="inlineStr">
+        <is>
+          <t>15-20</t>
+        </is>
+      </c>
+      <c r="G39" s="44" t="inlineStr">
+        <is>
+          <t>Single-tenant modular</t>
+        </is>
+      </c>
+      <c r="H39" s="43" t="inlineStr">
+        <is>
+          <t>~$1-2</t>
+        </is>
+      </c>
+      <c r="I39" s="52" t="n"/>
+      <c r="J39" s="52" t="n"/>
+    </row>
+    <row r="40" ht="20" customHeight="1">
+      <c r="A40" s="10" t="inlineStr">
+        <is>
+          <t>Crusoe Energy</t>
+        </is>
+      </c>
+      <c r="B40" s="38" t="inlineStr">
+        <is>
+          <t>Oracle</t>
+        </is>
+      </c>
+      <c r="C40" s="38" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D40" s="38" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E40" s="55" t="inlineStr">
+        <is>
+          <t>Extreme — single customer</t>
+        </is>
+      </c>
+      <c r="F40" s="38" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="G40" s="41" t="inlineStr">
+        <is>
+          <t>Build-to-suit, triple-net</t>
+        </is>
+      </c>
+      <c r="H40" s="38" t="inlineStr">
+        <is>
+          <t>~$1-2</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="20" customHeight="1">
+      <c r="A41" s="42" t="inlineStr">
+        <is>
+          <t>Hut 8</t>
+        </is>
+      </c>
+      <c r="B41" s="43" t="inlineStr">
+        <is>
+          <t>Google (via Fluidstack)</t>
+        </is>
+      </c>
+      <c r="C41" s="43" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D41" s="43" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E41" s="55" t="inlineStr">
+        <is>
+          <t>Extreme — single customer</t>
+        </is>
+      </c>
+      <c r="F41" s="43" t="inlineStr">
+        <is>
+          <t>15 (+15 renewal)</t>
+        </is>
+      </c>
+      <c r="G41" s="44" t="inlineStr">
+        <is>
+          <t>Triple-net IT lease</t>
+        </is>
+      </c>
+      <c r="H41" s="43" t="inlineStr">
+        <is>
+          <t>~$0.5</t>
+        </is>
+      </c>
+      <c r="I41" s="52" t="n"/>
+      <c r="J41" s="52" t="n"/>
+    </row>
+    <row r="42" ht="20" customHeight="1">
+      <c r="A42" s="10" t="inlineStr">
+        <is>
+          <t>Applied Digital</t>
+        </is>
+      </c>
+      <c r="B42" s="38" t="inlineStr">
+        <is>
+          <t>CoreWeave</t>
+        </is>
+      </c>
+      <c r="C42" s="38" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D42" s="38" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E42" s="55" t="inlineStr">
+        <is>
+          <t>Extreme — single customer</t>
+        </is>
+      </c>
+      <c r="F42" s="38" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="G42" s="41" t="inlineStr">
+        <is>
+          <t>Triple-net, GPU-ready</t>
+        </is>
+      </c>
+      <c r="H42" s="38" t="inlineStr">
+        <is>
+          <t>~$0.7</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="20" customHeight="1">
+      <c r="A43" s="42" t="inlineStr">
+        <is>
+          <t>EdgeConneX (EQT)</t>
+        </is>
+      </c>
+      <c r="B43" s="43" t="inlineStr">
+        <is>
+          <t>Mixed hyperscale + enterprise</t>
+        </is>
+      </c>
+      <c r="C43" s="43" t="inlineStr">
+        <is>
+          <t>Oracle</t>
+        </is>
+      </c>
+      <c r="D43" s="43" t="inlineStr">
+        <is>
+          <t>AWS / MSFT</t>
+        </is>
+      </c>
+      <c r="E43" s="44" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="F43" s="43" t="inlineStr">
+        <is>
+          <t>10-15</t>
+        </is>
+      </c>
+      <c r="G43" s="44" t="inlineStr">
+        <is>
+          <t>Build-to-suit colo</t>
+        </is>
+      </c>
+      <c r="H43" s="43" t="inlineStr">
+        <is>
+          <t>~$0.5-1</t>
+        </is>
+      </c>
+      <c r="I43" s="52" t="n"/>
+      <c r="J43" s="52" t="n"/>
+    </row>
+    <row r="44" ht="20" customHeight="1"/>
+    <row r="45" ht="20" customHeight="1">
+      <c r="A45" s="15" t="inlineStr">
+        <is>
+          <t>Sources &amp; Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="20" customHeight="1">
+      <c r="A46" s="16" t="inlineStr">
+        <is>
+          <t>Tenant relationships compiled from SEC filings, press releases, and industry reports (Q1 2026). Some relationships are inferred from public filings.</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="20" customHeight="1">
+      <c r="A47" s="16" t="inlineStr">
+        <is>
+          <t>Oracle future lease commitments ($261B) per Oracle FY Q2 2026 10-Q. Microsoft ($155B) and Meta ($104B) per Bloomberg/company filings Mar 2026.</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="20" customHeight="1">
+      <c r="A48" s="16" t="inlineStr">
+        <is>
+          <t>Moody's (Feb 2026): Big-5 hyperscalers hold $969B total undiscounted future lease commitments; $662B is off-balance-sheet (uncommenced).</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="20" customHeight="1">
+      <c r="A49" s="16" t="inlineStr">
+        <is>
+          <t>Crusoe → Oracle → Microsoft → OpenAI represents a multi-layered sublease chain; Stargate JV (Oracle/SoftBank/OpenAI) is a separate structure.</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="20" customHeight="1">
+      <c r="A50" s="16" t="inlineStr">
+        <is>
+          <t>Meta increasingly uses SPV structures (Pimco debt + Blue Owl equity) for build-to-suit DCs, retaining 20% co-ownership while keeping lease off-balance-sheet.</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="20" customHeight="1">
+      <c r="A51" s="16" t="inlineStr">
+        <is>
+          <t>Revenue concentration risk ratings are editorial assessments; 'Extreme' = &gt;80% revenue from a single customer, 'Very High' = &gt;60% from top 2.</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="20" customHeight="1">
+      <c r="A52" s="16" t="inlineStr">
+        <is>
+          <t>✓ = Confirmed tenant/customer relationship.  ~ = Suspected or indirect relationship.  Capacity figures are approximate operational + planned.</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="20" customHeight="1">
+      <c r="A53" s="16" t="inlineStr">
+        <is>
+          <t>Amazon's total future lease commitments are not separately disclosed but estimated at $80-100B based on on-B/S liabilities and industry analysis.</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="20" customHeight="1"/>
+  </sheetData>
+  <mergeCells count="13">
+    <mergeCell ref="A47:J47"/>
+    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="A46:J46"/>
+    <mergeCell ref="A22:J22"/>
+    <mergeCell ref="A30:J30"/>
+    <mergeCell ref="A53:J53"/>
+    <mergeCell ref="A50:J50"/>
+    <mergeCell ref="A4:J4"/>
+    <mergeCell ref="A48:J48"/>
+    <mergeCell ref="A51:J51"/>
+    <mergeCell ref="A2:J2"/>
+    <mergeCell ref="A52:J52"/>
+    <mergeCell ref="A49:J49"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:K39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -608,16 +2321,6 @@
           <t>Hyperscaler Capital Expenditure Comparison ($B)</t>
         </is>
       </c>
-      <c r="B1" s="1" t="n"/>
-      <c r="C1" s="1" t="n"/>
-      <c r="D1" s="1" t="n"/>
-      <c r="E1" s="1" t="n"/>
-      <c r="F1" s="1" t="n"/>
-      <c r="G1" s="1" t="n"/>
-      <c r="H1" s="1" t="n"/>
-      <c r="I1" s="1" t="n"/>
-      <c r="J1" s="1" t="n"/>
-      <c r="K1" s="1" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -625,16 +2328,6 @@
           <t>Includes property, equipment, and principal payments on finance leases  |  2026-2030 are estimates</t>
         </is>
       </c>
-      <c r="B2" s="2" t="n"/>
-      <c r="C2" s="2" t="n"/>
-      <c r="D2" s="2" t="n"/>
-      <c r="E2" s="2" t="n"/>
-      <c r="F2" s="2" t="n"/>
-      <c r="G2" s="2" t="n"/>
-      <c r="H2" s="2" t="n"/>
-      <c r="I2" s="2" t="n"/>
-      <c r="J2" s="2" t="n"/>
-      <c r="K2" s="2" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
@@ -1358,16 +3051,16 @@
           <t>Combined Big-4 Hyperscaler CapEx ($B)</t>
         </is>
       </c>
-      <c r="B24" s="3" t="n"/>
-      <c r="C24" s="3" t="n"/>
-      <c r="D24" s="3" t="n"/>
-      <c r="E24" s="3" t="n"/>
-      <c r="F24" s="3" t="n"/>
-      <c r="G24" s="3" t="n"/>
-      <c r="H24" s="3" t="n"/>
-      <c r="I24" s="3" t="n"/>
-      <c r="J24" s="3" t="n"/>
-      <c r="K24" s="3" t="n"/>
+      <c r="B24" s="56" t="n"/>
+      <c r="C24" s="56" t="n"/>
+      <c r="D24" s="56" t="n"/>
+      <c r="E24" s="56" t="n"/>
+      <c r="F24" s="56" t="n"/>
+      <c r="G24" s="56" t="n"/>
+      <c r="H24" s="56" t="n"/>
+      <c r="I24" s="56" t="n"/>
+      <c r="J24" s="56" t="n"/>
+      <c r="K24" s="57" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="10" t="inlineStr">
@@ -1460,16 +3153,16 @@
           <t>Year-over-Year CapEx Growth (%)</t>
         </is>
       </c>
-      <c r="B28" s="12" t="n"/>
-      <c r="C28" s="12" t="n"/>
-      <c r="D28" s="12" t="n"/>
-      <c r="E28" s="12" t="n"/>
-      <c r="F28" s="12" t="n"/>
-      <c r="G28" s="12" t="n"/>
-      <c r="H28" s="12" t="n"/>
-      <c r="I28" s="12" t="n"/>
-      <c r="J28" s="12" t="n"/>
-      <c r="K28" s="12" t="n"/>
+      <c r="B28" s="56" t="n"/>
+      <c r="C28" s="56" t="n"/>
+      <c r="D28" s="56" t="n"/>
+      <c r="E28" s="56" t="n"/>
+      <c r="F28" s="56" t="n"/>
+      <c r="G28" s="56" t="n"/>
+      <c r="H28" s="56" t="n"/>
+      <c r="I28" s="56" t="n"/>
+      <c r="J28" s="56" t="n"/>
+      <c r="K28" s="57" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="4" t="inlineStr">
@@ -1662,7 +3355,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1690,16 +3383,6 @@
           <t>Meta Platforms — Lease Obligations &amp; CapEx Deep Dive ($B)</t>
         </is>
       </c>
-      <c r="B1" s="1" t="n"/>
-      <c r="C1" s="1" t="n"/>
-      <c r="D1" s="1" t="n"/>
-      <c r="E1" s="1" t="n"/>
-      <c r="F1" s="1" t="n"/>
-      <c r="G1" s="1" t="n"/>
-      <c r="H1" s="1" t="n"/>
-      <c r="I1" s="1" t="n"/>
-      <c r="J1" s="1" t="n"/>
-      <c r="K1" s="1" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
@@ -2055,16 +3738,16 @@
           <t>These sit off-balance-sheet under GAAP until lease commences. Per Moody's Feb 2026 report.</t>
         </is>
       </c>
-      <c r="B13" s="9" t="n"/>
-      <c r="C13" s="9" t="n"/>
-      <c r="D13" s="9" t="n"/>
-      <c r="E13" s="9" t="n"/>
-      <c r="F13" s="9" t="n"/>
-      <c r="G13" s="9" t="n"/>
-      <c r="H13" s="9" t="n"/>
-      <c r="I13" s="9" t="n"/>
-      <c r="J13" s="9" t="n"/>
-      <c r="K13" s="9" t="n"/>
+      <c r="B13" s="56" t="n"/>
+      <c r="C13" s="56" t="n"/>
+      <c r="D13" s="56" t="n"/>
+      <c r="E13" s="56" t="n"/>
+      <c r="F13" s="56" t="n"/>
+      <c r="G13" s="56" t="n"/>
+      <c r="H13" s="56" t="n"/>
+      <c r="I13" s="56" t="n"/>
+      <c r="J13" s="56" t="n"/>
+      <c r="K13" s="57" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="9" t="n"/>
@@ -2730,7 +4413,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2758,16 +4441,6 @@
           <t>Meta Platforms — Lease Impact on Operating Margin</t>
         </is>
       </c>
-      <c r="B1" s="1" t="n"/>
-      <c r="C1" s="1" t="n"/>
-      <c r="D1" s="1" t="n"/>
-      <c r="E1" s="1" t="n"/>
-      <c r="F1" s="1" t="n"/>
-      <c r="G1" s="1" t="n"/>
-      <c r="H1" s="1" t="n"/>
-      <c r="I1" s="1" t="n"/>
-      <c r="J1" s="1" t="n"/>
-      <c r="K1" s="1" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -2775,16 +4448,6 @@
           <t>Scenario analysis: How growing lease obligations pressure operating margins through 2030</t>
         </is>
       </c>
-      <c r="B2" s="2" t="n"/>
-      <c r="C2" s="2" t="n"/>
-      <c r="D2" s="2" t="n"/>
-      <c r="E2" s="2" t="n"/>
-      <c r="F2" s="2" t="n"/>
-      <c r="G2" s="2" t="n"/>
-      <c r="H2" s="2" t="n"/>
-      <c r="I2" s="2" t="n"/>
-      <c r="J2" s="2" t="n"/>
-      <c r="K2" s="2" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
@@ -3344,16 +5007,16 @@
           <t>Scenario Analysis: Operating Margin Sensitivity to Lease Costs</t>
         </is>
       </c>
-      <c r="B20" s="3" t="n"/>
-      <c r="C20" s="3" t="n"/>
-      <c r="D20" s="3" t="n"/>
-      <c r="E20" s="3" t="n"/>
-      <c r="F20" s="3" t="n"/>
-      <c r="G20" s="3" t="n"/>
-      <c r="H20" s="3" t="n"/>
-      <c r="I20" s="3" t="n"/>
-      <c r="J20" s="3" t="n"/>
-      <c r="K20" s="3" t="n"/>
+      <c r="B20" s="56" t="n"/>
+      <c r="C20" s="56" t="n"/>
+      <c r="D20" s="56" t="n"/>
+      <c r="E20" s="56" t="n"/>
+      <c r="F20" s="56" t="n"/>
+      <c r="G20" s="56" t="n"/>
+      <c r="H20" s="56" t="n"/>
+      <c r="I20" s="56" t="n"/>
+      <c r="J20" s="56" t="n"/>
+      <c r="K20" s="57" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="10" t="inlineStr">
@@ -3549,16 +5212,16 @@
           <t>Incremental Margin Drag from Infrastructure Ramp</t>
         </is>
       </c>
-      <c r="B27" s="3" t="n"/>
-      <c r="C27" s="3" t="n"/>
-      <c r="D27" s="3" t="n"/>
-      <c r="E27" s="3" t="n"/>
-      <c r="F27" s="3" t="n"/>
-      <c r="G27" s="3" t="n"/>
-      <c r="H27" s="3" t="n"/>
-      <c r="I27" s="3" t="n"/>
-      <c r="J27" s="3" t="n"/>
-      <c r="K27" s="3" t="n"/>
+      <c r="B27" s="56" t="n"/>
+      <c r="C27" s="56" t="n"/>
+      <c r="D27" s="56" t="n"/>
+      <c r="E27" s="56" t="n"/>
+      <c r="F27" s="56" t="n"/>
+      <c r="G27" s="56" t="n"/>
+      <c r="H27" s="56" t="n"/>
+      <c r="I27" s="56" t="n"/>
+      <c r="J27" s="56" t="n"/>
+      <c r="K27" s="57" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="4" t="inlineStr">
@@ -3725,7 +5388,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3748,11 +5411,6 @@
           <t>Hyperscaler Lease &amp; Debt Comparison (End of 2025)</t>
         </is>
       </c>
-      <c r="B1" s="1" t="n"/>
-      <c r="C1" s="1" t="n"/>
-      <c r="D1" s="1" t="n"/>
-      <c r="E1" s="1" t="n"/>
-      <c r="F1" s="1" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">

--- a/meta_leases_capex_analysis.xlsx
+++ b/meta_leases_capex_analysis.xlsx
@@ -25,7 +25,7 @@
     <numFmt numFmtId="165" formatCode="0.0%"/>
     <numFmt numFmtId="166" formatCode="0.00x"/>
   </numFmts>
-  <fonts count="12">
+  <fonts count="14">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -92,8 +92,19 @@
       <b val="1"/>
       <sz val="9"/>
     </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="004A235A"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <color rgb="00999999"/>
+      <sz val="9"/>
+    </font>
   </fonts>
-  <fills count="11">
+  <fills count="13">
     <fill>
       <patternFill/>
     </fill>
@@ -154,6 +165,18 @@
         <bgColor rgb="00FCE4D6"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E2CCFF"/>
+        <bgColor rgb="00E2CCFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D9D9D9"/>
+        <bgColor rgb="00D9D9D9"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="6">
     <border>
@@ -201,7 +224,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="58">
+  <cellXfs count="67">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -356,6 +379,31 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="12" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -721,25 +769,26 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J53"/>
+  <dimension ref="A1:K71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
     <col width="14" customWidth="1" min="6" max="6"/>
     <col width="14" customWidth="1" min="7" max="7"/>
-    <col width="16" customWidth="1" min="8" max="8"/>
-    <col width="30" customWidth="1" min="9" max="9"/>
-    <col width="48" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="30" customWidth="1" min="10" max="10"/>
+    <col width="50" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
-    <row r="1" ht="20" customHeight="1">
+    <row r="1" ht="22" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hyperscaler-to-Landlord Data Center Lease Matrix</t>
+          <t>Hyperscaler &amp; Neocloud Data Center Lease Matrix</t>
         </is>
       </c>
       <c r="B1" s="1" t="n"/>
@@ -751,11 +800,12 @@
       <c r="H1" s="1" t="n"/>
       <c r="I1" s="1" t="n"/>
       <c r="J1" s="1" t="n"/>
-    </row>
-    <row r="2" ht="20" customHeight="1">
+      <c r="K1" s="1" t="n"/>
+    </row>
+    <row r="2" ht="22" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Who leases from whom  |  Confirmed relationships as of Q1 2026  |  ✓ = confirmed tenant, ~ = suspected/indirect</t>
+          <t>Who leases from whom  |  Q1 2026 data  |  ✓ = confirmed tenant  |  ~ = suspected / indirect  |  Neoclouds highlighted in purple</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -767,12 +817,13 @@
       <c r="H2" s="2" t="n"/>
       <c r="I2" s="2" t="n"/>
       <c r="J2" s="2" t="n"/>
-    </row>
-    <row r="3" ht="20" customHeight="1"/>
-    <row r="4" ht="20" customHeight="1">
+      <c r="K2" s="2" t="n"/>
+    </row>
+    <row r="3" ht="22" customHeight="1"/>
+    <row r="4" ht="22" customHeight="1">
       <c r="A4" s="36" t="inlineStr">
         <is>
-          <t>A. DATA CENTER OPERATOR / LANDLORD  ×  HYPERSCALER TENANT MATRIX</t>
+          <t>A. DATA CENTER OPERATOR / LANDLORD  ×  TENANT MATRIX (Hyperscalers + Neoclouds)</t>
         </is>
       </c>
       <c r="B4" s="36" t="n"/>
@@ -784,8 +835,9 @@
       <c r="H4" s="36" t="n"/>
       <c r="I4" s="36" t="n"/>
       <c r="J4" s="36" t="n"/>
-    </row>
-    <row r="5" ht="20" customHeight="1">
+      <c r="K4" s="36" t="n"/>
+    </row>
+    <row r="5" ht="22" customHeight="1">
       <c r="A5" s="37" t="inlineStr">
         <is>
           <t>DC Operator / Landlord</t>
@@ -793,7 +845,7 @@
       </c>
       <c r="B5" s="37" t="inlineStr">
         <is>
-          <t>Capacity (GW)</t>
+          <t>Capacity</t>
         </is>
       </c>
       <c r="C5" s="37" t="inlineStr">
@@ -808,7 +860,7 @@
       </c>
       <c r="E5" s="37" t="inlineStr">
         <is>
-          <t>Google / Alphabet</t>
+          <t>Google</t>
         </is>
       </c>
       <c r="F5" s="37" t="inlineStr">
@@ -823,24 +875,29 @@
       </c>
       <c r="H5" s="37" t="inlineStr">
         <is>
-          <t>CoreWeave / xAI</t>
+          <t>CoreWeave</t>
         </is>
       </c>
       <c r="I5" s="37" t="inlineStr">
         <is>
-          <t>Owner / Backer</t>
+          <t>Nebius</t>
         </is>
       </c>
       <c r="J5" s="37" t="inlineStr">
         <is>
+          <t>IREN</t>
+        </is>
+      </c>
+      <c r="K5" s="37" t="inlineStr">
+        <is>
           <t>Key Notes</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="20" customHeight="1">
+    <row r="6" ht="22" customHeight="1">
       <c r="A6" s="10" t="inlineStr">
         <is>
-          <t>QTS Realty Trust</t>
+          <t>QTS Realty (Blackstone)</t>
         </is>
       </c>
       <c r="B6" s="38" t="inlineStr">
@@ -874,18 +931,15 @@
         </is>
       </c>
       <c r="H6" s="38" t="inlineStr"/>
-      <c r="I6" s="41" t="inlineStr">
-        <is>
-          <t>Blackstone ($10B acq. 2021)</t>
-        </is>
-      </c>
-      <c r="J6" s="41" t="inlineStr">
-        <is>
-          <t>Largest by MW; AWS anchor in ATL, CHI, NJ. $12B+ investment pipeline.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="20" customHeight="1">
+      <c r="I6" s="38" t="inlineStr"/>
+      <c r="J6" s="38" t="inlineStr"/>
+      <c r="K6" s="41" t="inlineStr">
+        <is>
+          <t>Largest by MW. AWS anchor ATL/CHI/NJ. $12B+ pipeline. Acquired for $10B (2021).</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="22" customHeight="1">
       <c r="A7" s="42" t="inlineStr">
         <is>
           <t>Vantage Data Centers</t>
@@ -918,21 +972,18 @@
       </c>
       <c r="G7" s="43" t="inlineStr"/>
       <c r="H7" s="43" t="inlineStr"/>
-      <c r="I7" s="44" t="inlineStr">
-        <is>
-          <t>DigitalBridge / Silver Lake</t>
-        </is>
-      </c>
-      <c r="J7" s="44" t="inlineStr">
-        <is>
-          <t>100% hyperscale focus. Frontier Campus TX (1.4 GW), Port Washington WI (1.3 GW).</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="20" customHeight="1">
+      <c r="I7" s="43" t="inlineStr"/>
+      <c r="J7" s="43" t="inlineStr"/>
+      <c r="K7" s="44" t="inlineStr">
+        <is>
+          <t>100% hyperscale. Frontier TX (1.4 GW), Port Washington WI (1.3 GW). DigitalBridge/Silver Lake.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="22" customHeight="1">
       <c r="A8" s="10" t="inlineStr">
         <is>
-          <t>Digital Realty Trust (DLR)</t>
+          <t>Digital Realty (DLR)</t>
         </is>
       </c>
       <c r="B8" s="38" t="inlineStr">
@@ -966,18 +1017,15 @@
         </is>
       </c>
       <c r="H8" s="38" t="inlineStr"/>
-      <c r="I8" s="41" t="inlineStr">
-        <is>
-          <t>Public REIT (NYSE: DLR)</t>
-        </is>
-      </c>
-      <c r="J8" s="41" t="inlineStr">
-        <is>
-          <t>310 DCs, 42.5M sq ft. $817M backlog. Broadest tenant diversification.</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="20" customHeight="1">
+      <c r="I8" s="38" t="inlineStr"/>
+      <c r="J8" s="38" t="inlineStr"/>
+      <c r="K8" s="41" t="inlineStr">
+        <is>
+          <t>Public REIT. 310 DCs, 42.5M sq ft. $817M backlog. Broadest tenant diversification.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="22" customHeight="1">
       <c r="A9" s="42" t="inlineStr">
         <is>
           <t>STACK Infrastructure</t>
@@ -1010,21 +1058,18 @@
         </is>
       </c>
       <c r="H9" s="43" t="inlineStr"/>
-      <c r="I9" s="44" t="inlineStr">
-        <is>
-          <t>IPI Partners / Mubadala</t>
-        </is>
-      </c>
-      <c r="J9" s="44" t="inlineStr">
-        <is>
-          <t>$12B Amazon partnership in Louisiana. 24 global markets. GW-scale campuses.</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="20" customHeight="1">
+      <c r="I9" s="43" t="inlineStr"/>
+      <c r="J9" s="43" t="inlineStr"/>
+      <c r="K9" s="44" t="inlineStr">
+        <is>
+          <t>$12B Amazon partnership in Louisiana. IPI Partners / Mubadala. 24 global markets.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="22" customHeight="1">
       <c r="A10" s="10" t="inlineStr">
         <is>
-          <t>Aligned Data Centers</t>
+          <t>Aligned Data Centers (AIP)</t>
         </is>
       </c>
       <c r="B10" s="38" t="inlineStr">
@@ -1041,23 +1086,20 @@
       <c r="E10" s="38" t="inlineStr"/>
       <c r="F10" s="38" t="inlineStr"/>
       <c r="G10" s="38" t="inlineStr"/>
-      <c r="H10" s="39" t="inlineStr">
-        <is>
-          <t>✓ (xAI)</t>
-        </is>
-      </c>
-      <c r="I10" s="41" t="inlineStr">
-        <is>
-          <t>BlackRock AIP / Nvidia / MSFT / xAI</t>
-        </is>
-      </c>
-      <c r="J10" s="41" t="inlineStr">
-        <is>
-          <t>$40B acquisition (Oct 2025). 50 campuses. Largest DC deal in history.</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="20" customHeight="1">
+      <c r="H10" s="38" t="inlineStr"/>
+      <c r="I10" s="38" t="inlineStr"/>
+      <c r="J10" s="39" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="K10" s="41" t="inlineStr">
+        <is>
+          <t>$40B acq. by BlackRock/Nvidia/MSFT/xAI (Oct 2025). 50 campuses. Largest DC deal ever.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="22" customHeight="1">
       <c r="A11" s="42" t="inlineStr">
         <is>
           <t>Equinix (EQIX)</t>
@@ -1094,21 +1136,18 @@
         </is>
       </c>
       <c r="H11" s="43" t="inlineStr"/>
-      <c r="I11" s="44" t="inlineStr">
-        <is>
-          <t>Public REIT (NYSE: EQIX)</t>
-        </is>
-      </c>
-      <c r="J11" s="44" t="inlineStr">
-        <is>
-          <t>Interconnection-focused. 260+ DCs. 63% of Fortune 500. Direct cloud on-ramps.</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="20" customHeight="1">
+      <c r="I11" s="43" t="inlineStr"/>
+      <c r="J11" s="43" t="inlineStr"/>
+      <c r="K11" s="44" t="inlineStr">
+        <is>
+          <t>Interconnection leader. 260+ DCs. 63% of F500. Low tenant concentration risk.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="22" customHeight="1">
       <c r="A12" s="10" t="inlineStr">
         <is>
-          <t>CyrusOne</t>
+          <t>CyrusOne (KKR/GIP)</t>
         </is>
       </c>
       <c r="B12" s="38" t="inlineStr">
@@ -1130,21 +1169,18 @@
       <c r="F12" s="38" t="inlineStr"/>
       <c r="G12" s="38" t="inlineStr"/>
       <c r="H12" s="38" t="inlineStr"/>
-      <c r="I12" s="41" t="inlineStr">
-        <is>
-          <t>KKR / GIP (acq. 2022)</t>
-        </is>
-      </c>
-      <c r="J12" s="41" t="inlineStr">
+      <c r="I12" s="38" t="inlineStr"/>
+      <c r="J12" s="38" t="inlineStr"/>
+      <c r="K12" s="41" t="inlineStr">
         <is>
           <t>AWS &amp; MSFT London leases. Calpine energy partnership (400 MW TX).</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="20" customHeight="1">
+    <row r="13" ht="22" customHeight="1">
       <c r="A13" s="42" t="inlineStr">
         <is>
-          <t>Compass Datacenters</t>
+          <t>Compass (Brookfield/OTPP)</t>
         </is>
       </c>
       <c r="B13" s="43" t="inlineStr">
@@ -1166,206 +1202,188 @@
       </c>
       <c r="G13" s="43" t="inlineStr"/>
       <c r="H13" s="43" t="inlineStr"/>
-      <c r="I13" s="44" t="inlineStr">
-        <is>
-          <t>Brookfield Infra / OTPP</t>
-        </is>
-      </c>
-      <c r="J13" s="44" t="inlineStr">
-        <is>
-          <t>$10B Meridian MS campus. Tenant undisclosed (suspected Meta or MSFT).</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="20" customHeight="1">
+      <c r="I13" s="43" t="inlineStr"/>
+      <c r="J13" s="43" t="inlineStr"/>
+      <c r="K13" s="44" t="inlineStr">
+        <is>
+          <t>$10B Meridian MS campus. Tenant undisclosed (suspected Meta or MSFT). Single-tenant modular.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="22" customHeight="1">
       <c r="A14" s="10" t="inlineStr">
         <is>
-          <t>Crusoe Energy Systems</t>
+          <t>EdgeConneX (EQT)</t>
         </is>
       </c>
       <c r="B14" s="38" t="inlineStr">
         <is>
+          <t>1.0+ GW</t>
+        </is>
+      </c>
+      <c r="C14" s="39" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="D14" s="39" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="E14" s="39" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="F14" s="40" t="inlineStr">
+        <is>
+          <t>~</t>
+        </is>
+      </c>
+      <c r="G14" s="39" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="H14" s="38" t="inlineStr"/>
+      <c r="I14" s="38" t="inlineStr"/>
+      <c r="J14" s="38" t="inlineStr"/>
+      <c r="K14" s="41" t="inlineStr">
+        <is>
+          <t>80+ DCs, 60+ markets, 20+ countries. Cloud on-ramps for all majors.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="22" customHeight="1">
+      <c r="A15" s="42" t="inlineStr">
+        <is>
+          <t>Crusoe Energy</t>
+        </is>
+      </c>
+      <c r="B15" s="43" t="inlineStr">
+        <is>
           <t>1.2 GW</t>
         </is>
       </c>
-      <c r="C14" s="38" t="inlineStr"/>
-      <c r="D14" s="40" t="inlineStr">
+      <c r="C15" s="43" t="inlineStr"/>
+      <c r="D15" s="40" t="inlineStr">
         <is>
           <t>~</t>
         </is>
       </c>
-      <c r="E14" s="38" t="inlineStr"/>
-      <c r="F14" s="38" t="inlineStr"/>
-      <c r="G14" s="39" t="inlineStr">
+      <c r="E15" s="43" t="inlineStr"/>
+      <c r="F15" s="43" t="inlineStr"/>
+      <c r="G15" s="39" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="H14" s="38" t="inlineStr"/>
-      <c r="I14" s="41" t="inlineStr">
-        <is>
-          <t>Blue Owl / PE-backed</t>
-        </is>
-      </c>
-      <c r="J14" s="41" t="inlineStr">
-        <is>
-          <t>Abilene TX flagship. Oracle tenant → leases to MSFT → OpenAI. 15-yr lease.</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="20" customHeight="1">
-      <c r="A15" s="42" t="inlineStr">
-        <is>
-          <t>Hut 8 Corp</t>
-        </is>
-      </c>
-      <c r="B15" s="43" t="inlineStr">
+      <c r="H15" s="43" t="inlineStr"/>
+      <c r="I15" s="43" t="inlineStr"/>
+      <c r="J15" s="43" t="inlineStr"/>
+      <c r="K15" s="44" t="inlineStr">
+        <is>
+          <t>Abilene TX. Oracle tenant → MSFT → OpenAI sublease chain. Blue Owl JV.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="22" customHeight="1">
+      <c r="A16" s="10" t="inlineStr">
+        <is>
+          <t>Hut 8 Corp (HUT)</t>
+        </is>
+      </c>
+      <c r="B16" s="38" t="inlineStr">
         <is>
           <t>0.3 GW</t>
-        </is>
-      </c>
-      <c r="C15" s="43" t="inlineStr"/>
-      <c r="D15" s="43" t="inlineStr"/>
-      <c r="E15" s="39" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="F15" s="43" t="inlineStr"/>
-      <c r="G15" s="43" t="inlineStr"/>
-      <c r="H15" s="43" t="inlineStr"/>
-      <c r="I15" s="44" t="inlineStr">
-        <is>
-          <t>Public (NASDAQ: HUT)</t>
-        </is>
-      </c>
-      <c r="J15" s="44" t="inlineStr">
-        <is>
-          <t>$7B, 15-yr lease w/ Fluidstack (Google-backed). River Bend LA. 245 MW.</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="20" customHeight="1">
-      <c r="A16" s="10" t="inlineStr">
-        <is>
-          <t>Applied Digital</t>
-        </is>
-      </c>
-      <c r="B16" s="38" t="inlineStr">
-        <is>
-          <t>0.4 GW</t>
         </is>
       </c>
       <c r="C16" s="38" t="inlineStr"/>
       <c r="D16" s="38" t="inlineStr"/>
-      <c r="E16" s="38" t="inlineStr"/>
+      <c r="E16" s="39" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="F16" s="38" t="inlineStr"/>
       <c r="G16" s="38" t="inlineStr"/>
-      <c r="H16" s="39" t="inlineStr">
-        <is>
-          <t>✓ (CoreWeave)</t>
-        </is>
-      </c>
-      <c r="I16" s="41" t="inlineStr">
-        <is>
-          <t>Public (NASDAQ: APLD)</t>
-        </is>
-      </c>
-      <c r="J16" s="41" t="inlineStr">
-        <is>
-          <t>$11B contracted from CoreWeave. Polaris Forge ND campus. 400 MW.</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="20" customHeight="1">
+      <c r="H16" s="38" t="inlineStr"/>
+      <c r="I16" s="38" t="inlineStr"/>
+      <c r="J16" s="38" t="inlineStr"/>
+      <c r="K16" s="41" t="inlineStr">
+        <is>
+          <t>$7B/15-yr lease via Fluidstack (Google-backed). River Bend LA. 245 MW.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="22" customHeight="1">
       <c r="A17" s="42" t="inlineStr">
         <is>
-          <t>EdgeConneX</t>
+          <t>Applied Digital (APLD)</t>
         </is>
       </c>
       <c r="B17" s="43" t="inlineStr">
         <is>
-          <t>1.0+ GW</t>
-        </is>
-      </c>
-      <c r="C17" s="39" t="inlineStr">
+          <t>0.4 GW</t>
+        </is>
+      </c>
+      <c r="C17" s="43" t="inlineStr"/>
+      <c r="D17" s="43" t="inlineStr"/>
+      <c r="E17" s="43" t="inlineStr"/>
+      <c r="F17" s="43" t="inlineStr"/>
+      <c r="G17" s="43" t="inlineStr"/>
+      <c r="H17" s="39" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="D17" s="39" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="E17" s="39" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="F17" s="40" t="inlineStr">
-        <is>
-          <t>~</t>
-        </is>
-      </c>
-      <c r="G17" s="39" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="H17" s="43" t="inlineStr"/>
-      <c r="I17" s="44" t="inlineStr">
-        <is>
-          <t>EQT Partners</t>
-        </is>
-      </c>
-      <c r="J17" s="44" t="inlineStr">
-        <is>
-          <t>80+ DCs, 60+ markets, 20+ countries. Cloud on-ramps for all major providers.</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="20" customHeight="1">
+      <c r="I17" s="43" t="inlineStr"/>
+      <c r="J17" s="43" t="inlineStr"/>
+      <c r="K17" s="44" t="inlineStr">
+        <is>
+          <t>$11B contracted from CoreWeave. Polaris Forge ND (400 MW). 15-yr triple-net leases.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="22" customHeight="1">
       <c r="A18" s="10" t="inlineStr">
         <is>
-          <t>Meta SPV (Pimco / Blue Owl)</t>
+          <t>Core Scientific (CORZ)</t>
         </is>
       </c>
       <c r="B18" s="38" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1.3 GW</t>
         </is>
       </c>
       <c r="C18" s="38" t="inlineStr"/>
       <c r="D18" s="38" t="inlineStr"/>
       <c r="E18" s="38" t="inlineStr"/>
-      <c r="F18" s="39" t="inlineStr">
+      <c r="F18" s="38" t="inlineStr"/>
+      <c r="G18" s="38" t="inlineStr"/>
+      <c r="H18" s="39" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="G18" s="38" t="inlineStr"/>
-      <c r="H18" s="38" t="inlineStr"/>
-      <c r="I18" s="41" t="inlineStr">
-        <is>
-          <t>Meta 20% co-ownership</t>
-        </is>
-      </c>
-      <c r="J18" s="41" t="inlineStr">
-        <is>
-          <t>Louisiana Hyperion: $29B Pimco debt + $3B Blue Owl equity. Build-to-suit.</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="20" customHeight="1">
+      <c r="I18" s="38" t="inlineStr"/>
+      <c r="J18" s="38" t="inlineStr"/>
+      <c r="K18" s="41" t="inlineStr">
+        <is>
+          <t>Acquired by CoreWeave for $9B (Jul 2025). 10 US sites. Pipeline to 2.3 GW.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="22" customHeight="1">
       <c r="A19" s="42" t="inlineStr">
         <is>
-          <t>Stargate JV (Oracle-led)</t>
+          <t>Stargate JV</t>
         </is>
       </c>
       <c r="B19" s="43" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>4.5+ GW</t>
         </is>
       </c>
       <c r="C19" s="43" t="inlineStr"/>
@@ -1386,908 +1404,1720 @@
         </is>
       </c>
       <c r="H19" s="43" t="inlineStr"/>
-      <c r="I19" s="44" t="inlineStr">
-        <is>
-          <t>Oracle / SoftBank / OpenAI</t>
-        </is>
-      </c>
-      <c r="J19" s="44" t="inlineStr">
-        <is>
-          <t>Abilene TX mega-campus. MSFT &amp; Meta negotiating capacity. $500B vision.</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="20" customHeight="1"/>
-    <row r="21" ht="20" customHeight="1"/>
-    <row r="22" ht="20" customHeight="1">
-      <c r="A22" s="36" t="inlineStr">
-        <is>
-          <t>B. HYPERSCALER FUTURE LEASE COMMITMENTS (as of Q1 2026, $B)</t>
-        </is>
-      </c>
-      <c r="B22" s="36" t="n"/>
-      <c r="C22" s="36" t="n"/>
-      <c r="D22" s="36" t="n"/>
-      <c r="E22" s="36" t="n"/>
-      <c r="F22" s="36" t="n"/>
-      <c r="G22" s="36" t="n"/>
-      <c r="H22" s="36" t="n"/>
-      <c r="I22" s="36" t="n"/>
-      <c r="J22" s="36" t="n"/>
-    </row>
-    <row r="23" ht="20" customHeight="1">
-      <c r="A23" s="45" t="inlineStr">
+      <c r="I19" s="43" t="inlineStr"/>
+      <c r="J19" s="43" t="inlineStr"/>
+      <c r="K19" s="44" t="inlineStr">
+        <is>
+          <t>Oracle/SoftBank/OpenAI. Abilene TX mega-campus. MSFT &amp; Meta negotiating capacity.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="22" customHeight="1">
+      <c r="A20" s="10" t="inlineStr">
+        <is>
+          <t>Meta SPV (Pimco/Blue Owl)</t>
+        </is>
+      </c>
+      <c r="B20" s="38" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C20" s="38" t="inlineStr"/>
+      <c r="D20" s="38" t="inlineStr"/>
+      <c r="E20" s="38" t="inlineStr"/>
+      <c r="F20" s="39" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="G20" s="38" t="inlineStr"/>
+      <c r="H20" s="38" t="inlineStr"/>
+      <c r="I20" s="38" t="inlineStr"/>
+      <c r="J20" s="38" t="inlineStr"/>
+      <c r="K20" s="41" t="inlineStr">
+        <is>
+          <t>Louisiana Hyperion: $26B Pimco debt + $3B Blue Owl equity. Meta 20% co-ownership.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="22" customHeight="1">
+      <c r="A21" s="58" t="inlineStr">
+        <is>
+          <t>CoreWeave (CRWV)</t>
+        </is>
+      </c>
+      <c r="B21" s="59" t="inlineStr">
+        <is>
+          <t>1.9 GW</t>
+        </is>
+      </c>
+      <c r="C21" s="59" t="inlineStr"/>
+      <c r="D21" s="39" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="E21" s="39" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="F21" s="39" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="G21" s="59" t="inlineStr"/>
+      <c r="H21" s="60" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I21" s="60" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J21" s="59" t="inlineStr"/>
+      <c r="K21" s="61" t="inlineStr">
+        <is>
+          <t>43 DCs. Sells GPU cloud to OpenAI ($22.4B), Meta ($14.2B), MSFT, Google. Nvidia-backed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="22" customHeight="1">
+      <c r="A22" s="58" t="inlineStr">
+        <is>
+          <t>Nebius (NBIS)</t>
+        </is>
+      </c>
+      <c r="B22" s="59" t="inlineStr">
+        <is>
+          <t>0.2 GW</t>
+        </is>
+      </c>
+      <c r="C22" s="59" t="inlineStr"/>
+      <c r="D22" s="39" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="E22" s="59" t="inlineStr"/>
+      <c r="F22" s="39" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="G22" s="59" t="inlineStr"/>
+      <c r="H22" s="59" t="inlineStr"/>
+      <c r="I22" s="60" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J22" s="59" t="inlineStr"/>
+      <c r="K22" s="61" t="inlineStr">
+        <is>
+          <t>Meta ($27B+$3B deals), Microsoft (multi-B). Nvidia $2B investment. ARR $1.25B. Target 3 GW by end 2026.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="22" customHeight="1">
+      <c r="A23" s="58" t="inlineStr">
+        <is>
+          <t>IREN (formerly Iris Energy)</t>
+        </is>
+      </c>
+      <c r="B23" s="59" t="inlineStr">
+        <is>
+          <t>0.8 GW</t>
+        </is>
+      </c>
+      <c r="C23" s="59" t="inlineStr"/>
+      <c r="D23" s="39" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="E23" s="59" t="inlineStr"/>
+      <c r="F23" s="59" t="inlineStr"/>
+      <c r="G23" s="59" t="inlineStr"/>
+      <c r="H23" s="59" t="inlineStr"/>
+      <c r="I23" s="59" t="inlineStr"/>
+      <c r="J23" s="60" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K23" s="61" t="inlineStr">
+        <is>
+          <t>MSFT $9.7B/5-yr contract. 150K GPU target. Childress TX 750 MW. Owns sites freehold.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="22" customHeight="1"/>
+    <row r="25" ht="22" customHeight="1"/>
+    <row r="26" ht="22" customHeight="1">
+      <c r="A26" s="36" t="inlineStr">
+        <is>
+          <t>B. FUTURE LEASE &amp; CONTRACT COMMITMENTS — HYPERSCALERS + NEOCLOUDS (as of Q1 2026, $B)</t>
+        </is>
+      </c>
+      <c r="B26" s="36" t="n"/>
+      <c r="C26" s="36" t="n"/>
+      <c r="D26" s="36" t="n"/>
+      <c r="E26" s="36" t="n"/>
+      <c r="F26" s="36" t="n"/>
+      <c r="G26" s="36" t="n"/>
+      <c r="H26" s="36" t="n"/>
+      <c r="I26" s="36" t="n"/>
+      <c r="J26" s="36" t="n"/>
+      <c r="K26" s="36" t="n"/>
+    </row>
+    <row r="27" ht="22" customHeight="1">
+      <c r="A27" s="45" t="inlineStr">
+        <is>
+          <t>Company</t>
+        </is>
+      </c>
+      <c r="B27" s="37" t="inlineStr">
+        <is>
+          <t>Type</t>
+        </is>
+      </c>
+      <c r="C27" s="37" t="inlineStr">
+        <is>
+          <t>Total Future Commitments ($B)</t>
+        </is>
+      </c>
+      <c r="D27" s="37" t="inlineStr">
+        <is>
+          <t>On-B/S Lease Liab. ($B)</t>
+        </is>
+      </c>
+      <c r="E27" s="37" t="inlineStr">
+        <is>
+          <t>Off-B/S / Uncommenced ($B)</t>
+        </is>
+      </c>
+      <c r="F27" s="37" t="inlineStr">
+        <is>
+          <t>2025 Revenue ($B)</t>
+        </is>
+      </c>
+      <c r="G27" s="37" t="inlineStr">
+        <is>
+          <t>Commit. / Revenue</t>
+        </is>
+      </c>
+      <c r="H27" s="37" t="inlineStr">
+        <is>
+          <t>Primary Strategy</t>
+        </is>
+      </c>
+      <c r="I27" s="37" t="inlineStr">
+        <is>
+          <t>Key Partners / Customers</t>
+        </is>
+      </c>
+      <c r="J27" s="46" t="inlineStr"/>
+      <c r="K27" s="46" t="inlineStr"/>
+    </row>
+    <row r="28" ht="22" customHeight="1">
+      <c r="A28" s="10" t="inlineStr">
+        <is>
+          <t>Oracle</t>
+        </is>
+      </c>
+      <c r="B28" s="38" t="inlineStr">
         <is>
           <t>Hyperscaler</t>
         </is>
       </c>
-      <c r="B23" s="37" t="inlineStr">
-        <is>
-          <t>Total Future Lease Commitments ($B)</t>
-        </is>
-      </c>
-      <c r="C23" s="37" t="inlineStr">
-        <is>
-          <t>On-Balance-Sheet Lease Liab. ($B)</t>
-        </is>
-      </c>
-      <c r="D23" s="37" t="inlineStr">
-        <is>
-          <t>Off-B/S Uncommenced Leases ($B)</t>
-        </is>
-      </c>
-      <c r="E23" s="37" t="inlineStr">
-        <is>
-          <t>Lease Commit. / Revenue</t>
-        </is>
-      </c>
-      <c r="F23" s="37" t="inlineStr">
-        <is>
-          <t>Lease Commit. / Op. Income</t>
-        </is>
-      </c>
-      <c r="G23" s="37" t="inlineStr">
-        <is>
-          <t>Primary Lease Strategy</t>
-        </is>
-      </c>
-      <c r="H23" s="37" t="inlineStr">
-        <is>
-          <t>Key Landlord Partners</t>
-        </is>
-      </c>
-      <c r="I23" s="46" t="inlineStr"/>
-      <c r="J23" s="46" t="inlineStr"/>
-    </row>
-    <row r="24" ht="20" customHeight="1">
-      <c r="A24" s="10" t="inlineStr">
+      <c r="C28" s="47" t="n">
+        <v>261</v>
+      </c>
+      <c r="D28" s="48" t="n">
+        <v>13</v>
+      </c>
+      <c r="E28" s="47" t="n">
+        <v>248</v>
+      </c>
+      <c r="F28" s="48" t="n">
+        <v>60</v>
+      </c>
+      <c r="G28" s="38" t="inlineStr">
+        <is>
+          <t>4.4x</t>
+        </is>
+      </c>
+      <c r="H28" s="41" t="inlineStr">
+        <is>
+          <t>Aggressive 3rd-party leasing; Stargate anchor</t>
+        </is>
+      </c>
+      <c r="I28" s="41" t="inlineStr">
+        <is>
+          <t>Crusoe, EdgeConneX, Stargate JV</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="22" customHeight="1">
+      <c r="A29" s="42" t="inlineStr">
+        <is>
+          <t>Microsoft</t>
+        </is>
+      </c>
+      <c r="B29" s="43" t="inlineStr">
+        <is>
+          <t>Hyperscaler</t>
+        </is>
+      </c>
+      <c r="C29" s="50" t="n">
+        <v>155</v>
+      </c>
+      <c r="D29" s="50" t="n">
+        <v>50</v>
+      </c>
+      <c r="E29" s="50" t="n">
+        <v>105</v>
+      </c>
+      <c r="F29" s="50" t="n">
+        <v>281.7</v>
+      </c>
+      <c r="G29" s="43" t="inlineStr">
+        <is>
+          <t>0.6x</t>
+        </is>
+      </c>
+      <c r="H29" s="44" t="inlineStr">
+        <is>
+          <t>Mix owned + build-to-suit + co-invested (AIP)</t>
+        </is>
+      </c>
+      <c r="I29" s="44" t="inlineStr">
+        <is>
+          <t>Aligned, QTS, Vantage, CyrusOne, IREN, Nebius, CoreWeave</t>
+        </is>
+      </c>
+      <c r="J29" s="52" t="n"/>
+      <c r="K29" s="52" t="n"/>
+    </row>
+    <row r="30" ht="22" customHeight="1">
+      <c r="A30" s="10" t="inlineStr">
+        <is>
+          <t>Meta</t>
+        </is>
+      </c>
+      <c r="B30" s="38" t="inlineStr">
+        <is>
+          <t>Hyperscaler</t>
+        </is>
+      </c>
+      <c r="C30" s="48" t="n">
+        <v>104</v>
+      </c>
+      <c r="D30" s="48" t="n">
+        <v>26.1</v>
+      </c>
+      <c r="E30" s="48" t="n">
+        <v>78</v>
+      </c>
+      <c r="F30" s="48" t="n">
+        <v>201</v>
+      </c>
+      <c r="G30" s="38" t="inlineStr">
+        <is>
+          <t>0.5x</t>
+        </is>
+      </c>
+      <c r="H30" s="41" t="inlineStr">
+        <is>
+          <t>SPV-financed build-to-suit; growing 3rd-party</t>
+        </is>
+      </c>
+      <c r="I30" s="41" t="inlineStr">
+        <is>
+          <t>Pimco/Blue Owl SPV, Digital Realty, Vantage, CoreWeave, Nebius</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="22" customHeight="1">
+      <c r="A31" s="42" t="inlineStr">
+        <is>
+          <t>Google / Alphabet</t>
+        </is>
+      </c>
+      <c r="B31" s="43" t="inlineStr">
+        <is>
+          <t>Hyperscaler</t>
+        </is>
+      </c>
+      <c r="C31" s="50" t="n">
+        <v>42.6</v>
+      </c>
+      <c r="D31" s="50" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="E31" s="50" t="n">
+        <v>20.1</v>
+      </c>
+      <c r="F31" s="50" t="n">
+        <v>402.8</v>
+      </c>
+      <c r="G31" s="43" t="inlineStr">
+        <is>
+          <t>0.1x</t>
+        </is>
+      </c>
+      <c r="H31" s="44" t="inlineStr">
+        <is>
+          <t>Mostly owned; selective leasing for speed</t>
+        </is>
+      </c>
+      <c r="I31" s="44" t="inlineStr">
+        <is>
+          <t>Hut 8 (Fluidstack), Digital Realty, Vantage, QTS, CoreWeave</t>
+        </is>
+      </c>
+      <c r="J31" s="52" t="n"/>
+      <c r="K31" s="52" t="n"/>
+    </row>
+    <row r="32" ht="22" customHeight="1">
+      <c r="A32" s="10" t="inlineStr">
+        <is>
+          <t>Amazon / AWS</t>
+        </is>
+      </c>
+      <c r="B32" s="38" t="inlineStr">
+        <is>
+          <t>Hyperscaler</t>
+        </is>
+      </c>
+      <c r="C32" s="38" t="inlineStr">
+        <is>
+          <t>~80–100</t>
+        </is>
+      </c>
+      <c r="D32" s="48" t="n">
+        <v>160</v>
+      </c>
+      <c r="E32" s="38" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F32" s="48" t="n">
+        <v>716.9</v>
+      </c>
+      <c r="G32" s="38" t="inlineStr">
+        <is>
+          <t>~0.1x</t>
+        </is>
+      </c>
+      <c r="H32" s="41" t="inlineStr">
+        <is>
+          <t>Mix owned mega-campuses + colocation at scale</t>
+        </is>
+      </c>
+      <c r="I32" s="41" t="inlineStr">
+        <is>
+          <t>QTS, STACK, Vantage, Digital Realty, EdgeConneX</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="22" customHeight="1">
+      <c r="A33" s="62" t="inlineStr">
+        <is>
+          <t>CoreWeave</t>
+        </is>
+      </c>
+      <c r="B33" s="59" t="inlineStr">
+        <is>
+          <t>Neocloud</t>
+        </is>
+      </c>
+      <c r="C33" s="59" t="inlineStr">
+        <is>
+          <t>~60.7 (RPO)</t>
+        </is>
+      </c>
+      <c r="D33" s="59" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="E33" s="59" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F33" s="63" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="G33" s="59" t="inlineStr">
+        <is>
+          <t>~11.9x</t>
+        </is>
+      </c>
+      <c r="H33" s="61" t="inlineStr">
+        <is>
+          <t>Lease DCs → add GPUs → sell compute. Nvidia-backed</t>
+        </is>
+      </c>
+      <c r="I33" s="61" t="inlineStr">
+        <is>
+          <t>Tenants: Applied Digital, Core Scientific. Customers: OpenAI, Meta, MSFT, Google</t>
+        </is>
+      </c>
+      <c r="J33" s="64" t="n"/>
+      <c r="K33" s="64" t="n"/>
+    </row>
+    <row r="34" ht="22" customHeight="1">
+      <c r="A34" s="62" t="inlineStr">
+        <is>
+          <t>Nebius</t>
+        </is>
+      </c>
+      <c r="B34" s="59" t="inlineStr">
+        <is>
+          <t>Neocloud</t>
+        </is>
+      </c>
+      <c r="C34" s="59" t="inlineStr">
+        <is>
+          <t>~30+ (contracted)</t>
+        </is>
+      </c>
+      <c r="D34" s="59" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="E34" s="59" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F34" s="63" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="G34" s="59" t="inlineStr">
+        <is>
+          <t>~57x</t>
+        </is>
+      </c>
+      <c r="H34" s="61" t="inlineStr">
+        <is>
+          <t>Build-to-own + colocation. Nvidia $2B investment</t>
+        </is>
+      </c>
+      <c r="I34" s="61" t="inlineStr">
+        <is>
+          <t>Customers: Meta ($27B+$3B), Microsoft. Landlords: Patmos (KC). Mostly self-built</t>
+        </is>
+      </c>
+      <c r="J34" s="64" t="n"/>
+      <c r="K34" s="64" t="n"/>
+    </row>
+    <row r="35" ht="22" customHeight="1">
+      <c r="A35" s="62" t="inlineStr">
+        <is>
+          <t>IREN</t>
+        </is>
+      </c>
+      <c r="B35" s="59" t="inlineStr">
+        <is>
+          <t>Neocloud</t>
+        </is>
+      </c>
+      <c r="C35" s="59" t="inlineStr">
+        <is>
+          <t>~9.7 (MSFT contract)</t>
+        </is>
+      </c>
+      <c r="D35" s="59" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="E35" s="59" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F35" s="63" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="G35" s="59" t="inlineStr">
+        <is>
+          <t>~10x</t>
+        </is>
+      </c>
+      <c r="H35" s="61" t="inlineStr">
+        <is>
+          <t>Owner-operator. Freehold sites. GPU-as-a-service</t>
+        </is>
+      </c>
+      <c r="I35" s="61" t="inlineStr">
+        <is>
+          <t>Customers: Microsoft ($9.7B), Together AI, Fluidstack, Fireworks AI</t>
+        </is>
+      </c>
+      <c r="J35" s="64" t="n"/>
+      <c r="K35" s="64" t="n"/>
+    </row>
+    <row r="36" ht="22" customHeight="1"/>
+    <row r="37" ht="22" customHeight="1">
+      <c r="A37" s="36" t="inlineStr">
+        <is>
+          <t>C. TOP CUSTOMERS / TENANTS BY OPERATOR (Ranked by Estimated Revenue Contribution)</t>
+        </is>
+      </c>
+      <c r="B37" s="36" t="n"/>
+      <c r="C37" s="36" t="n"/>
+      <c r="D37" s="36" t="n"/>
+      <c r="E37" s="36" t="n"/>
+      <c r="F37" s="36" t="n"/>
+      <c r="G37" s="36" t="n"/>
+      <c r="H37" s="36" t="n"/>
+      <c r="I37" s="36" t="n"/>
+      <c r="J37" s="36" t="n"/>
+      <c r="K37" s="36" t="n"/>
+    </row>
+    <row r="38" ht="22" customHeight="1">
+      <c r="A38" s="45" t="inlineStr">
+        <is>
+          <t>DC Operator / Provider</t>
+        </is>
+      </c>
+      <c r="B38" s="37" t="inlineStr">
+        <is>
+          <t>#1 Customer</t>
+        </is>
+      </c>
+      <c r="C38" s="37" t="inlineStr">
+        <is>
+          <t>#2 Customer</t>
+        </is>
+      </c>
+      <c r="D38" s="37" t="inlineStr">
+        <is>
+          <t>#3 Customer</t>
+        </is>
+      </c>
+      <c r="E38" s="37" t="inlineStr">
+        <is>
+          <t>Concentration Risk</t>
+        </is>
+      </c>
+      <c r="F38" s="37" t="inlineStr">
+        <is>
+          <t>Avg Lease Term</t>
+        </is>
+      </c>
+      <c r="G38" s="37" t="inlineStr">
+        <is>
+          <t>Lease / Contract Structure</t>
+        </is>
+      </c>
+      <c r="H38" s="37" t="inlineStr">
+        <is>
+          <t>Est. Annual Rev from Top 3 ($B)</t>
+        </is>
+      </c>
+      <c r="I38" s="37" t="inlineStr">
+        <is>
+          <t>Owner / Backer</t>
+        </is>
+      </c>
+      <c r="J38" s="46" t="inlineStr"/>
+      <c r="K38" s="46" t="inlineStr"/>
+    </row>
+    <row r="39" ht="22" customHeight="1">
+      <c r="A39" s="10" t="inlineStr">
+        <is>
+          <t>QTS (Blackstone)</t>
+        </is>
+      </c>
+      <c r="B39" s="38" t="inlineStr">
+        <is>
+          <t>Amazon / AWS</t>
+        </is>
+      </c>
+      <c r="C39" s="38" t="inlineStr">
+        <is>
+          <t>Microsoft</t>
+        </is>
+      </c>
+      <c r="D39" s="38" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="E39" s="53" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F39" s="38" t="inlineStr">
+        <is>
+          <t>10–20 yrs</t>
+        </is>
+      </c>
+      <c r="G39" s="41" t="inlineStr">
+        <is>
+          <t>Triple-net, build-to-suit</t>
+        </is>
+      </c>
+      <c r="H39" s="38" t="inlineStr">
+        <is>
+          <t>$4–6</t>
+        </is>
+      </c>
+      <c r="I39" s="41" t="inlineStr">
+        <is>
+          <t>Blackstone ($10B acq.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="22" customHeight="1">
+      <c r="A40" s="42" t="inlineStr">
+        <is>
+          <t>Vantage</t>
+        </is>
+      </c>
+      <c r="B40" s="43" t="inlineStr">
+        <is>
+          <t>Microsoft</t>
+        </is>
+      </c>
+      <c r="C40" s="43" t="inlineStr">
+        <is>
+          <t>Meta</t>
+        </is>
+      </c>
+      <c r="D40" s="43" t="inlineStr">
+        <is>
+          <t>Amazon / AWS</t>
+        </is>
+      </c>
+      <c r="E40" s="54" t="inlineStr">
+        <is>
+          <t>Very High</t>
+        </is>
+      </c>
+      <c r="F40" s="43" t="inlineStr">
+        <is>
+          <t>15–20 yrs</t>
+        </is>
+      </c>
+      <c r="G40" s="44" t="inlineStr">
+        <is>
+          <t>Single-tenant, shell + core</t>
+        </is>
+      </c>
+      <c r="H40" s="43" t="inlineStr">
+        <is>
+          <t>$3–5</t>
+        </is>
+      </c>
+      <c r="I40" s="44" t="inlineStr">
+        <is>
+          <t>DigitalBridge / Silver Lake</t>
+        </is>
+      </c>
+      <c r="J40" s="52" t="n"/>
+      <c r="K40" s="52" t="n"/>
+    </row>
+    <row r="41" ht="22" customHeight="1">
+      <c r="A41" s="10" t="inlineStr">
+        <is>
+          <t>Digital Realty (DLR)</t>
+        </is>
+      </c>
+      <c r="B41" s="38" t="inlineStr">
+        <is>
+          <t>Meta</t>
+        </is>
+      </c>
+      <c r="C41" s="38" t="inlineStr">
         <is>
           <t>Oracle</t>
         </is>
       </c>
-      <c r="B24" s="47" t="n">
-        <v>261</v>
-      </c>
-      <c r="C24" s="48" t="n">
-        <v>13</v>
-      </c>
-      <c r="D24" s="47" t="n">
-        <v>248</v>
-      </c>
-      <c r="E24" s="49" t="n">
-        <v>4.35</v>
-      </c>
-      <c r="F24" s="49" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="G24" s="41" t="inlineStr">
-        <is>
-          <t>Aggressive third-party leasing; Stargate anchor</t>
-        </is>
-      </c>
-      <c r="H24" s="41" t="inlineStr">
-        <is>
-          <t>Crusoe, Stargate JV, EdgeConneX</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="20" customHeight="1">
-      <c r="A25" s="42" t="inlineStr">
+      <c r="D41" s="38" t="inlineStr">
+        <is>
+          <t>Amazon / AWS</t>
+        </is>
+      </c>
+      <c r="E41" s="41" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="F41" s="38" t="inlineStr">
+        <is>
+          <t>7–15 yrs</t>
+        </is>
+      </c>
+      <c r="G41" s="41" t="inlineStr">
+        <is>
+          <t>Mix: colo + build-to-suit</t>
+        </is>
+      </c>
+      <c r="H41" s="38" t="inlineStr">
+        <is>
+          <t>$2–4</t>
+        </is>
+      </c>
+      <c r="I41" s="41" t="inlineStr">
+        <is>
+          <t>Public REIT (NYSE: DLR)</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="22" customHeight="1">
+      <c r="A42" s="42" t="inlineStr">
+        <is>
+          <t>STACK Infrastructure</t>
+        </is>
+      </c>
+      <c r="B42" s="43" t="inlineStr">
+        <is>
+          <t>Amazon / AWS</t>
+        </is>
+      </c>
+      <c r="C42" s="43" t="inlineStr">
+        <is>
+          <t>Oracle</t>
+        </is>
+      </c>
+      <c r="D42" s="43" t="inlineStr">
         <is>
           <t>Microsoft</t>
         </is>
       </c>
-      <c r="B25" s="50" t="n">
-        <v>155</v>
-      </c>
-      <c r="C25" s="50" t="n">
-        <v>50</v>
-      </c>
-      <c r="D25" s="50" t="n">
-        <v>105</v>
-      </c>
-      <c r="E25" s="51" t="n">
-        <v>0.55</v>
-      </c>
-      <c r="F25" s="51" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="G25" s="44" t="inlineStr">
-        <is>
-          <t>Mix of owned + build-to-suit + co-invested (AIP/Aligned)</t>
-        </is>
-      </c>
-      <c r="H25" s="44" t="inlineStr">
-        <is>
-          <t>Aligned, QTS, Vantage, CyrusOne, Compass</t>
-        </is>
-      </c>
-      <c r="I25" s="52" t="n"/>
-      <c r="J25" s="52" t="n"/>
-    </row>
-    <row r="26" ht="20" customHeight="1">
-      <c r="A26" s="10" t="inlineStr">
-        <is>
-          <t>Meta</t>
-        </is>
-      </c>
-      <c r="B26" s="48" t="n">
-        <v>104</v>
-      </c>
-      <c r="C26" s="48" t="n">
-        <v>26.1</v>
-      </c>
-      <c r="D26" s="48" t="n">
-        <v>78</v>
-      </c>
-      <c r="E26" s="49" t="n">
-        <v>0.52</v>
-      </c>
-      <c r="F26" s="49" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="G26" s="41" t="inlineStr">
-        <is>
-          <t>SPV-financed build-to-suit; growing third-party leasing</t>
-        </is>
-      </c>
-      <c r="H26" s="41" t="inlineStr">
-        <is>
-          <t>Pimco/Blue Owl SPV, Digital Realty, Vantage, EdgeConneX</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="20" customHeight="1">
-      <c r="A27" s="42" t="inlineStr">
-        <is>
-          <t>Google / Alphabet</t>
-        </is>
-      </c>
-      <c r="B27" s="50" t="n">
-        <v>42.6</v>
-      </c>
-      <c r="C27" s="50" t="n">
-        <v>22.5</v>
-      </c>
-      <c r="D27" s="50" t="n">
-        <v>20.1</v>
-      </c>
-      <c r="E27" s="51" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="F27" s="51" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="G27" s="44" t="inlineStr">
-        <is>
-          <t>Mostly owned; selective leasing for speed-to-capacity</t>
-        </is>
-      </c>
-      <c r="H27" s="44" t="inlineStr">
-        <is>
-          <t>Hut 8 (Fluidstack), Digital Realty, Vantage, QTS</t>
-        </is>
-      </c>
-      <c r="I27" s="52" t="n"/>
-      <c r="J27" s="52" t="n"/>
-    </row>
-    <row r="28" ht="20" customHeight="1">
-      <c r="A28" s="10" t="inlineStr">
+      <c r="E42" s="53" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F42" s="43" t="inlineStr">
+        <is>
+          <t>15–25 yrs</t>
+        </is>
+      </c>
+      <c r="G42" s="44" t="inlineStr">
+        <is>
+          <t>Powered shell, triple-net</t>
+        </is>
+      </c>
+      <c r="H42" s="43" t="inlineStr">
+        <is>
+          <t>$2–3</t>
+        </is>
+      </c>
+      <c r="I42" s="44" t="inlineStr">
+        <is>
+          <t>IPI Partners / Mubadala</t>
+        </is>
+      </c>
+      <c r="J42" s="52" t="n"/>
+      <c r="K42" s="52" t="n"/>
+    </row>
+    <row r="43" ht="22" customHeight="1">
+      <c r="A43" s="10" t="inlineStr">
+        <is>
+          <t>Aligned (BlackRock AIP)</t>
+        </is>
+      </c>
+      <c r="B43" s="38" t="inlineStr">
+        <is>
+          <t>Microsoft</t>
+        </is>
+      </c>
+      <c r="C43" s="38" t="inlineStr">
+        <is>
+          <t>xAI</t>
+        </is>
+      </c>
+      <c r="D43" s="38" t="inlineStr">
+        <is>
+          <t>IREN</t>
+        </is>
+      </c>
+      <c r="E43" s="54" t="inlineStr">
+        <is>
+          <t>Very High</t>
+        </is>
+      </c>
+      <c r="F43" s="38" t="inlineStr">
+        <is>
+          <t>10–20 yrs</t>
+        </is>
+      </c>
+      <c r="G43" s="41" t="inlineStr">
+        <is>
+          <t>Co-invested, build-to-suit</t>
+        </is>
+      </c>
+      <c r="H43" s="38" t="inlineStr">
+        <is>
+          <t>$2–4</t>
+        </is>
+      </c>
+      <c r="I43" s="41" t="inlineStr">
+        <is>
+          <t>BlackRock / Nvidia / MSFT / xAI</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="22" customHeight="1">
+      <c r="A44" s="42" t="inlineStr">
+        <is>
+          <t>Equinix (EQIX)</t>
+        </is>
+      </c>
+      <c r="B44" s="43" t="inlineStr">
         <is>
           <t>Amazon / AWS</t>
         </is>
       </c>
-      <c r="B28" s="38" t="inlineStr">
-        <is>
-          <t>~80-100</t>
-        </is>
-      </c>
-      <c r="C28" s="48" t="n">
-        <v>160</v>
-      </c>
-      <c r="D28" s="38" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="E28" s="38" t="inlineStr">
-        <is>
-          <t>~0.13</t>
-        </is>
-      </c>
-      <c r="F28" s="38" t="inlineStr">
-        <is>
-          <t>~1.2</t>
-        </is>
-      </c>
-      <c r="G28" s="41" t="inlineStr">
-        <is>
-          <t>Mix of owned mega-campuses + colocation at scale</t>
-        </is>
-      </c>
-      <c r="H28" s="41" t="inlineStr">
-        <is>
-          <t>QTS, STACK, Vantage, Digital Realty, EdgeConneX</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="20" customHeight="1"/>
-    <row r="30" ht="20" customHeight="1">
-      <c r="A30" s="36" t="inlineStr">
-        <is>
-          <t>C. TOP CUSTOMERS / TENANTS BY DATA CENTER OPERATOR (Ranked by Estimated Revenue Contribution)</t>
-        </is>
-      </c>
-      <c r="B30" s="36" t="n"/>
-      <c r="C30" s="36" t="n"/>
-      <c r="D30" s="36" t="n"/>
-      <c r="E30" s="36" t="n"/>
-      <c r="F30" s="36" t="n"/>
-      <c r="G30" s="36" t="n"/>
-      <c r="H30" s="36" t="n"/>
-      <c r="I30" s="36" t="n"/>
-      <c r="J30" s="36" t="n"/>
-    </row>
-    <row r="31" ht="20" customHeight="1">
-      <c r="A31" s="37" t="inlineStr">
-        <is>
-          <t>DC Operator</t>
-        </is>
-      </c>
-      <c r="B31" s="37" t="inlineStr">
-        <is>
-          <t>#1 Customer</t>
-        </is>
-      </c>
-      <c r="C31" s="37" t="inlineStr">
-        <is>
-          <t>#2 Customer</t>
-        </is>
-      </c>
-      <c r="D31" s="37" t="inlineStr">
-        <is>
-          <t>#3 Customer</t>
-        </is>
-      </c>
-      <c r="E31" s="37" t="inlineStr">
-        <is>
-          <t>Revenue Concentration Risk</t>
-        </is>
-      </c>
-      <c r="F31" s="37" t="inlineStr">
-        <is>
-          <t>Avg Lease Term (Yrs)</t>
-        </is>
-      </c>
-      <c r="G31" s="37" t="inlineStr">
-        <is>
-          <t>Lease Structure</t>
-        </is>
-      </c>
-      <c r="H31" s="37" t="inlineStr">
-        <is>
-          <t>Est. Annual Rent from Top 3 ($B)</t>
-        </is>
-      </c>
-      <c r="I31" s="46" t="inlineStr"/>
-      <c r="J31" s="46" t="inlineStr"/>
-    </row>
-    <row r="32" ht="20" customHeight="1">
-      <c r="A32" s="10" t="inlineStr">
-        <is>
-          <t>QTS (Blackstone)</t>
-        </is>
-      </c>
-      <c r="B32" s="38" t="inlineStr">
+      <c r="C44" s="43" t="inlineStr">
+        <is>
+          <t>Microsoft</t>
+        </is>
+      </c>
+      <c r="D44" s="43" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="E44" s="65" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="F44" s="43" t="inlineStr">
+        <is>
+          <t>3–5 yrs</t>
+        </is>
+      </c>
+      <c r="G44" s="44" t="inlineStr">
+        <is>
+          <t>Retail colo + interconnection</t>
+        </is>
+      </c>
+      <c r="H44" s="43" t="inlineStr">
+        <is>
+          <t>$1–2</t>
+        </is>
+      </c>
+      <c r="I44" s="44" t="inlineStr">
+        <is>
+          <t>Public REIT (NYSE: EQIX)</t>
+        </is>
+      </c>
+      <c r="J44" s="52" t="n"/>
+      <c r="K44" s="52" t="n"/>
+    </row>
+    <row r="45" ht="22" customHeight="1">
+      <c r="A45" s="10" t="inlineStr">
+        <is>
+          <t>CyrusOne (KKR/GIP)</t>
+        </is>
+      </c>
+      <c r="B45" s="38" t="inlineStr">
         <is>
           <t>Amazon / AWS</t>
         </is>
       </c>
-      <c r="C32" s="38" t="inlineStr">
+      <c r="C45" s="38" t="inlineStr">
         <is>
           <t>Microsoft</t>
         </is>
       </c>
-      <c r="D32" s="38" t="inlineStr">
-        <is>
-          <t>Google</t>
-        </is>
-      </c>
-      <c r="E32" s="53" t="inlineStr">
-        <is>
-          <t>High — dominated by 2-3 hyperscalers</t>
-        </is>
-      </c>
-      <c r="F32" s="38" t="inlineStr">
-        <is>
-          <t>10-20</t>
-        </is>
-      </c>
-      <c r="G32" s="41" t="inlineStr">
-        <is>
-          <t>Triple-net, build-to-suit</t>
-        </is>
-      </c>
-      <c r="H32" s="38" t="inlineStr">
-        <is>
-          <t>~$4-6</t>
-        </is>
-      </c>
-    </row>
-    <row r="33" ht="20" customHeight="1">
-      <c r="A33" s="42" t="inlineStr">
-        <is>
-          <t>Vantage</t>
-        </is>
-      </c>
-      <c r="B33" s="43" t="inlineStr">
+      <c r="D45" s="38" t="inlineStr">
+        <is>
+          <t>Enterprise mix</t>
+        </is>
+      </c>
+      <c r="E45" s="41" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="F45" s="38" t="inlineStr">
+        <is>
+          <t>10–15 yrs</t>
+        </is>
+      </c>
+      <c r="G45" s="41" t="inlineStr">
+        <is>
+          <t>Build-to-suit hyperscale</t>
+        </is>
+      </c>
+      <c r="H45" s="38" t="inlineStr">
+        <is>
+          <t>$0.5–1</t>
+        </is>
+      </c>
+      <c r="I45" s="41" t="inlineStr">
+        <is>
+          <t>KKR / GIP</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="22" customHeight="1">
+      <c r="A46" s="42" t="inlineStr">
+        <is>
+          <t>Compass (Brookfield)</t>
+        </is>
+      </c>
+      <c r="B46" s="43" t="inlineStr">
+        <is>
+          <t>Undisclosed (Meta or MSFT)</t>
+        </is>
+      </c>
+      <c r="C46" s="43" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D46" s="43" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E46" s="54" t="inlineStr">
+        <is>
+          <t>Very High</t>
+        </is>
+      </c>
+      <c r="F46" s="43" t="inlineStr">
+        <is>
+          <t>15–20 yrs</t>
+        </is>
+      </c>
+      <c r="G46" s="44" t="inlineStr">
+        <is>
+          <t>Single-tenant modular</t>
+        </is>
+      </c>
+      <c r="H46" s="43" t="inlineStr">
+        <is>
+          <t>$1–2</t>
+        </is>
+      </c>
+      <c r="I46" s="44" t="inlineStr">
+        <is>
+          <t>Brookfield Infra / OTPP</t>
+        </is>
+      </c>
+      <c r="J46" s="52" t="n"/>
+      <c r="K46" s="52" t="n"/>
+    </row>
+    <row r="47" ht="22" customHeight="1">
+      <c r="A47" s="10" t="inlineStr">
+        <is>
+          <t>Crusoe Energy</t>
+        </is>
+      </c>
+      <c r="B47" s="38" t="inlineStr">
+        <is>
+          <t>Oracle</t>
+        </is>
+      </c>
+      <c r="C47" s="38" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D47" s="38" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E47" s="55" t="inlineStr">
+        <is>
+          <t>Extreme</t>
+        </is>
+      </c>
+      <c r="F47" s="38" t="inlineStr">
+        <is>
+          <t>15 yrs</t>
+        </is>
+      </c>
+      <c r="G47" s="41" t="inlineStr">
+        <is>
+          <t>Build-to-suit, triple-net</t>
+        </is>
+      </c>
+      <c r="H47" s="38" t="inlineStr">
+        <is>
+          <t>$1–2</t>
+        </is>
+      </c>
+      <c r="I47" s="41" t="inlineStr">
+        <is>
+          <t>Blue Owl / PE-backed</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="22" customHeight="1">
+      <c r="A48" s="42" t="inlineStr">
+        <is>
+          <t>Hut 8 (HUT)</t>
+        </is>
+      </c>
+      <c r="B48" s="43" t="inlineStr">
+        <is>
+          <t>Google (via Fluidstack)</t>
+        </is>
+      </c>
+      <c r="C48" s="43" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D48" s="43" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E48" s="55" t="inlineStr">
+        <is>
+          <t>Extreme</t>
+        </is>
+      </c>
+      <c r="F48" s="43" t="inlineStr">
+        <is>
+          <t>15 (+15 renewal)</t>
+        </is>
+      </c>
+      <c r="G48" s="44" t="inlineStr">
+        <is>
+          <t>Triple-net IT lease</t>
+        </is>
+      </c>
+      <c r="H48" s="43" t="inlineStr">
+        <is>
+          <t>$0.5</t>
+        </is>
+      </c>
+      <c r="I48" s="44" t="inlineStr">
+        <is>
+          <t>Public (NASDAQ: HUT)</t>
+        </is>
+      </c>
+      <c r="J48" s="52" t="n"/>
+      <c r="K48" s="52" t="n"/>
+    </row>
+    <row r="49" ht="22" customHeight="1">
+      <c r="A49" s="10" t="inlineStr">
+        <is>
+          <t>Applied Digital (APLD)</t>
+        </is>
+      </c>
+      <c r="B49" s="38" t="inlineStr">
+        <is>
+          <t>CoreWeave</t>
+        </is>
+      </c>
+      <c r="C49" s="38" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D49" s="38" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E49" s="55" t="inlineStr">
+        <is>
+          <t>Extreme</t>
+        </is>
+      </c>
+      <c r="F49" s="38" t="inlineStr">
+        <is>
+          <t>15 yrs</t>
+        </is>
+      </c>
+      <c r="G49" s="41" t="inlineStr">
+        <is>
+          <t>Triple-net, GPU-ready shell</t>
+        </is>
+      </c>
+      <c r="H49" s="38" t="inlineStr">
+        <is>
+          <t>$0.7</t>
+        </is>
+      </c>
+      <c r="I49" s="41" t="inlineStr">
+        <is>
+          <t>Public (NASDAQ: APLD)</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="22" customHeight="1">
+      <c r="A50" s="42" t="inlineStr">
+        <is>
+          <t>Core Scientific (CORZ)</t>
+        </is>
+      </c>
+      <c r="B50" s="43" t="inlineStr">
+        <is>
+          <t>CoreWeave</t>
+        </is>
+      </c>
+      <c r="C50" s="43" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D50" s="43" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E50" s="55" t="inlineStr">
+        <is>
+          <t>Extreme</t>
+        </is>
+      </c>
+      <c r="F50" s="43" t="inlineStr">
+        <is>
+          <t>12–15 yrs</t>
+        </is>
+      </c>
+      <c r="G50" s="44" t="inlineStr">
+        <is>
+          <t>Acquired by CoreWeave ($9B)</t>
+        </is>
+      </c>
+      <c r="H50" s="43" t="inlineStr">
+        <is>
+          <t>$0.5–1</t>
+        </is>
+      </c>
+      <c r="I50" s="44" t="inlineStr">
+        <is>
+          <t>CoreWeave (acquired Jul 2025)</t>
+        </is>
+      </c>
+      <c r="J50" s="52" t="n"/>
+      <c r="K50" s="52" t="n"/>
+    </row>
+    <row r="51" ht="22" customHeight="1">
+      <c r="A51" s="10" t="inlineStr">
+        <is>
+          <t>EdgeConneX (EQT)</t>
+        </is>
+      </c>
+      <c r="B51" s="38" t="inlineStr">
+        <is>
+          <t>Mixed hyperscale</t>
+        </is>
+      </c>
+      <c r="C51" s="38" t="inlineStr">
+        <is>
+          <t>Oracle</t>
+        </is>
+      </c>
+      <c r="D51" s="38" t="inlineStr">
+        <is>
+          <t>AWS / MSFT</t>
+        </is>
+      </c>
+      <c r="E51" s="41" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="F51" s="38" t="inlineStr">
+        <is>
+          <t>10–15 yrs</t>
+        </is>
+      </c>
+      <c r="G51" s="41" t="inlineStr">
+        <is>
+          <t>Build-to-suit colo</t>
+        </is>
+      </c>
+      <c r="H51" s="38" t="inlineStr">
+        <is>
+          <t>$0.5–1</t>
+        </is>
+      </c>
+      <c r="I51" s="41" t="inlineStr">
+        <is>
+          <t>EQT Partners</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="22" customHeight="1">
+      <c r="A52" s="62" t="inlineStr">
+        <is>
+          <t>CoreWeave (CRWV)</t>
+        </is>
+      </c>
+      <c r="B52" s="59" t="inlineStr">
+        <is>
+          <t>OpenAI ($22.4B)</t>
+        </is>
+      </c>
+      <c r="C52" s="59" t="inlineStr">
+        <is>
+          <t>Meta ($14.2B)</t>
+        </is>
+      </c>
+      <c r="D52" s="59" t="inlineStr">
         <is>
           <t>Microsoft</t>
         </is>
       </c>
-      <c r="C33" s="43" t="inlineStr">
-        <is>
-          <t>Meta</t>
-        </is>
-      </c>
-      <c r="D33" s="43" t="inlineStr">
-        <is>
-          <t>Amazon / AWS</t>
-        </is>
-      </c>
-      <c r="E33" s="54" t="inlineStr">
-        <is>
-          <t>Very High — 100% hyperscale</t>
-        </is>
-      </c>
-      <c r="F33" s="43" t="inlineStr">
-        <is>
-          <t>15-20</t>
-        </is>
-      </c>
-      <c r="G33" s="44" t="inlineStr">
-        <is>
-          <t>Single-tenant, shell + core</t>
-        </is>
-      </c>
-      <c r="H33" s="43" t="inlineStr">
-        <is>
-          <t>~$3-5</t>
-        </is>
-      </c>
-      <c r="I33" s="52" t="n"/>
-      <c r="J33" s="52" t="n"/>
-    </row>
-    <row r="34" ht="20" customHeight="1">
-      <c r="A34" s="10" t="inlineStr">
-        <is>
-          <t>Digital Realty (DLR)</t>
-        </is>
-      </c>
-      <c r="B34" s="38" t="inlineStr">
-        <is>
-          <t>Meta</t>
-        </is>
-      </c>
-      <c r="C34" s="38" t="inlineStr">
-        <is>
-          <t>Oracle</t>
-        </is>
-      </c>
-      <c r="D34" s="38" t="inlineStr">
-        <is>
-          <t>Amazon / AWS</t>
-        </is>
-      </c>
-      <c r="E34" s="41" t="inlineStr">
-        <is>
-          <t>Moderate — diversified portfolio</t>
-        </is>
-      </c>
-      <c r="F34" s="38" t="inlineStr">
-        <is>
-          <t>7-15</t>
-        </is>
-      </c>
-      <c r="G34" s="41" t="inlineStr">
-        <is>
-          <t>Mix: colo + build-to-suit</t>
-        </is>
-      </c>
-      <c r="H34" s="38" t="inlineStr">
-        <is>
-          <t>~$2-4</t>
-        </is>
-      </c>
-    </row>
-    <row r="35" ht="20" customHeight="1">
-      <c r="A35" s="42" t="inlineStr">
-        <is>
-          <t>STACK Infrastructure</t>
-        </is>
-      </c>
-      <c r="B35" s="43" t="inlineStr">
-        <is>
-          <t>Amazon / AWS</t>
-        </is>
-      </c>
-      <c r="C35" s="43" t="inlineStr">
-        <is>
-          <t>Oracle</t>
-        </is>
-      </c>
-      <c r="D35" s="43" t="inlineStr">
-        <is>
-          <t>Microsoft</t>
-        </is>
-      </c>
-      <c r="E35" s="53" t="inlineStr">
-        <is>
-          <t>High — anchor-tenant campuses</t>
-        </is>
-      </c>
-      <c r="F35" s="43" t="inlineStr">
-        <is>
-          <t>15-25</t>
-        </is>
-      </c>
-      <c r="G35" s="44" t="inlineStr">
-        <is>
-          <t>Powered shell, triple-net</t>
-        </is>
-      </c>
-      <c r="H35" s="43" t="inlineStr">
-        <is>
-          <t>~$2-3</t>
-        </is>
-      </c>
-      <c r="I35" s="52" t="n"/>
-      <c r="J35" s="52" t="n"/>
-    </row>
-    <row r="36" ht="20" customHeight="1">
-      <c r="A36" s="10" t="inlineStr">
-        <is>
-          <t>Aligned (BlackRock AIP)</t>
-        </is>
-      </c>
-      <c r="B36" s="38" t="inlineStr">
-        <is>
-          <t>Microsoft</t>
-        </is>
-      </c>
-      <c r="C36" s="38" t="inlineStr">
-        <is>
-          <t>xAI</t>
-        </is>
-      </c>
-      <c r="D36" s="38" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E36" s="54" t="inlineStr">
-        <is>
-          <t>Very High — consortium-owned</t>
-        </is>
-      </c>
-      <c r="F36" s="38" t="inlineStr">
-        <is>
-          <t>10-20</t>
-        </is>
-      </c>
-      <c r="G36" s="41" t="inlineStr">
-        <is>
-          <t>Co-invested, build-to-suit</t>
-        </is>
-      </c>
-      <c r="H36" s="38" t="inlineStr">
-        <is>
-          <t>~$2-4</t>
-        </is>
-      </c>
-    </row>
-    <row r="37" ht="20" customHeight="1">
-      <c r="A37" s="42" t="inlineStr">
-        <is>
-          <t>Equinix (EQIX)</t>
-        </is>
-      </c>
-      <c r="B37" s="43" t="inlineStr">
-        <is>
-          <t>Amazon / AWS</t>
-        </is>
-      </c>
-      <c r="C37" s="43" t="inlineStr">
-        <is>
-          <t>Microsoft</t>
-        </is>
-      </c>
-      <c r="D37" s="43" t="inlineStr">
-        <is>
-          <t>Google</t>
-        </is>
-      </c>
-      <c r="E37" s="53" t="inlineStr">
-        <is>
-          <t>Low — highly diversified (10K+ customers)</t>
-        </is>
-      </c>
-      <c r="F37" s="43" t="inlineStr">
-        <is>
-          <t>3-5</t>
-        </is>
-      </c>
-      <c r="G37" s="44" t="inlineStr">
-        <is>
-          <t>Retail colo + interconnection</t>
-        </is>
-      </c>
-      <c r="H37" s="43" t="inlineStr">
-        <is>
-          <t>~$1-2</t>
-        </is>
-      </c>
-      <c r="I37" s="52" t="n"/>
-      <c r="J37" s="52" t="n"/>
-    </row>
-    <row r="38" ht="20" customHeight="1">
-      <c r="A38" s="10" t="inlineStr">
-        <is>
-          <t>CyrusOne (KKR/GIP)</t>
-        </is>
-      </c>
-      <c r="B38" s="38" t="inlineStr">
-        <is>
-          <t>Amazon / AWS</t>
-        </is>
-      </c>
-      <c r="C38" s="38" t="inlineStr">
-        <is>
-          <t>Microsoft</t>
-        </is>
-      </c>
-      <c r="D38" s="38" t="inlineStr">
-        <is>
-          <t>Enterprise mix</t>
-        </is>
-      </c>
-      <c r="E38" s="41" t="inlineStr">
-        <is>
-          <t>Moderate</t>
-        </is>
-      </c>
-      <c r="F38" s="38" t="inlineStr">
-        <is>
-          <t>10-15</t>
-        </is>
-      </c>
-      <c r="G38" s="41" t="inlineStr">
-        <is>
-          <t>Build-to-suit hyperscale</t>
-        </is>
-      </c>
-      <c r="H38" s="38" t="inlineStr">
-        <is>
-          <t>~$0.5-1</t>
-        </is>
-      </c>
-    </row>
-    <row r="39" ht="20" customHeight="1">
-      <c r="A39" s="42" t="inlineStr">
-        <is>
-          <t>Compass (Brookfield)</t>
-        </is>
-      </c>
-      <c r="B39" s="43" t="inlineStr">
-        <is>
-          <t>Undisclosed (Meta or MSFT)</t>
-        </is>
-      </c>
-      <c r="C39" s="43" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D39" s="43" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E39" s="54" t="inlineStr">
-        <is>
-          <t>Very High — single-tenant design</t>
-        </is>
-      </c>
-      <c r="F39" s="43" t="inlineStr">
-        <is>
-          <t>15-20</t>
-        </is>
-      </c>
-      <c r="G39" s="44" t="inlineStr">
-        <is>
-          <t>Single-tenant modular</t>
-        </is>
-      </c>
-      <c r="H39" s="43" t="inlineStr">
-        <is>
-          <t>~$1-2</t>
-        </is>
-      </c>
-      <c r="I39" s="52" t="n"/>
-      <c r="J39" s="52" t="n"/>
-    </row>
-    <row r="40" ht="20" customHeight="1">
-      <c r="A40" s="10" t="inlineStr">
-        <is>
-          <t>Crusoe Energy</t>
-        </is>
-      </c>
-      <c r="B40" s="38" t="inlineStr">
-        <is>
-          <t>Oracle</t>
-        </is>
-      </c>
-      <c r="C40" s="38" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D40" s="38" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E40" s="55" t="inlineStr">
-        <is>
-          <t>Extreme — single customer</t>
-        </is>
-      </c>
-      <c r="F40" s="38" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="G40" s="41" t="inlineStr">
-        <is>
-          <t>Build-to-suit, triple-net</t>
-        </is>
-      </c>
-      <c r="H40" s="38" t="inlineStr">
-        <is>
-          <t>~$1-2</t>
-        </is>
-      </c>
-    </row>
-    <row r="41" ht="20" customHeight="1">
-      <c r="A41" s="42" t="inlineStr">
-        <is>
-          <t>Hut 8</t>
-        </is>
-      </c>
-      <c r="B41" s="43" t="inlineStr">
-        <is>
-          <t>Google (via Fluidstack)</t>
-        </is>
-      </c>
-      <c r="C41" s="43" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D41" s="43" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E41" s="55" t="inlineStr">
-        <is>
-          <t>Extreme — single customer</t>
-        </is>
-      </c>
-      <c r="F41" s="43" t="inlineStr">
-        <is>
-          <t>15 (+15 renewal)</t>
-        </is>
-      </c>
-      <c r="G41" s="44" t="inlineStr">
-        <is>
-          <t>Triple-net IT lease</t>
-        </is>
-      </c>
-      <c r="H41" s="43" t="inlineStr">
-        <is>
-          <t>~$0.5</t>
-        </is>
-      </c>
-      <c r="I41" s="52" t="n"/>
-      <c r="J41" s="52" t="n"/>
-    </row>
-    <row r="42" ht="20" customHeight="1">
-      <c r="A42" s="10" t="inlineStr">
-        <is>
-          <t>Applied Digital</t>
-        </is>
-      </c>
-      <c r="B42" s="38" t="inlineStr">
-        <is>
-          <t>CoreWeave</t>
-        </is>
-      </c>
-      <c r="C42" s="38" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D42" s="38" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E42" s="55" t="inlineStr">
-        <is>
-          <t>Extreme — single customer</t>
-        </is>
-      </c>
-      <c r="F42" s="38" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="G42" s="41" t="inlineStr">
-        <is>
-          <t>Triple-net, GPU-ready</t>
-        </is>
-      </c>
-      <c r="H42" s="38" t="inlineStr">
-        <is>
-          <t>~$0.7</t>
-        </is>
-      </c>
-    </row>
-    <row r="43" ht="20" customHeight="1">
-      <c r="A43" s="42" t="inlineStr">
-        <is>
-          <t>EdgeConneX (EQT)</t>
-        </is>
-      </c>
-      <c r="B43" s="43" t="inlineStr">
-        <is>
-          <t>Mixed hyperscale + enterprise</t>
-        </is>
-      </c>
-      <c r="C43" s="43" t="inlineStr">
-        <is>
-          <t>Oracle</t>
-        </is>
-      </c>
-      <c r="D43" s="43" t="inlineStr">
-        <is>
-          <t>AWS / MSFT</t>
-        </is>
-      </c>
-      <c r="E43" s="44" t="inlineStr">
-        <is>
-          <t>Moderate</t>
-        </is>
-      </c>
-      <c r="F43" s="43" t="inlineStr">
-        <is>
-          <t>10-15</t>
-        </is>
-      </c>
-      <c r="G43" s="44" t="inlineStr">
-        <is>
-          <t>Build-to-suit colo</t>
-        </is>
-      </c>
-      <c r="H43" s="43" t="inlineStr">
-        <is>
-          <t>~$0.5-1</t>
-        </is>
-      </c>
-      <c r="I43" s="52" t="n"/>
-      <c r="J43" s="52" t="n"/>
-    </row>
-    <row r="44" ht="20" customHeight="1"/>
-    <row r="45" ht="20" customHeight="1">
-      <c r="A45" s="15" t="inlineStr">
+      <c r="E52" s="53" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F52" s="59" t="inlineStr">
+        <is>
+          <t>5 yrs (compute)</t>
+        </is>
+      </c>
+      <c r="G52" s="61" t="inlineStr">
+        <is>
+          <t>GPU-aaS, take-or-pay</t>
+        </is>
+      </c>
+      <c r="H52" s="59" t="inlineStr">
+        <is>
+          <t>$3–5</t>
+        </is>
+      </c>
+      <c r="I52" s="61" t="inlineStr">
+        <is>
+          <t>Public (NASDAQ: CRWV). Nvidia-backed</t>
+        </is>
+      </c>
+      <c r="J52" s="64" t="n"/>
+      <c r="K52" s="64" t="n"/>
+    </row>
+    <row r="53" ht="22" customHeight="1">
+      <c r="A53" s="62" t="inlineStr">
+        <is>
+          <t>Nebius (NBIS)</t>
+        </is>
+      </c>
+      <c r="B53" s="59" t="inlineStr">
+        <is>
+          <t>Meta ($27B+$3B)</t>
+        </is>
+      </c>
+      <c r="C53" s="59" t="inlineStr">
+        <is>
+          <t>Microsoft (multi-B)</t>
+        </is>
+      </c>
+      <c r="D53" s="59" t="inlineStr">
+        <is>
+          <t>Enterprise / AI startups</t>
+        </is>
+      </c>
+      <c r="E53" s="54" t="inlineStr">
+        <is>
+          <t>Very High</t>
+        </is>
+      </c>
+      <c r="F53" s="59" t="inlineStr">
+        <is>
+          <t>5 yrs (infra delivery)</t>
+        </is>
+      </c>
+      <c r="G53" s="61" t="inlineStr">
+        <is>
+          <t>Full-stack AI cloud</t>
+        </is>
+      </c>
+      <c r="H53" s="59" t="inlineStr">
+        <is>
+          <t>$0.5–1</t>
+        </is>
+      </c>
+      <c r="I53" s="61" t="inlineStr">
+        <is>
+          <t>Public (NASDAQ: NBIS). Nvidia $2B</t>
+        </is>
+      </c>
+      <c r="J53" s="64" t="n"/>
+      <c r="K53" s="64" t="n"/>
+    </row>
+    <row r="54" ht="22" customHeight="1">
+      <c r="A54" s="62" t="inlineStr">
+        <is>
+          <t>IREN</t>
+        </is>
+      </c>
+      <c r="B54" s="59" t="inlineStr">
+        <is>
+          <t>Microsoft ($9.7B)</t>
+        </is>
+      </c>
+      <c r="C54" s="59" t="inlineStr">
+        <is>
+          <t>Together AI</t>
+        </is>
+      </c>
+      <c r="D54" s="59" t="inlineStr">
+        <is>
+          <t>Fluidstack / Fireworks AI</t>
+        </is>
+      </c>
+      <c r="E54" s="55" t="inlineStr">
+        <is>
+          <t>Extreme</t>
+        </is>
+      </c>
+      <c r="F54" s="59" t="inlineStr">
+        <is>
+          <t>5 yrs (MSFT)</t>
+        </is>
+      </c>
+      <c r="G54" s="61" t="inlineStr">
+        <is>
+          <t>GPU cloud + colocation</t>
+        </is>
+      </c>
+      <c r="H54" s="59" t="inlineStr">
+        <is>
+          <t>$1–2</t>
+        </is>
+      </c>
+      <c r="I54" s="61" t="inlineStr">
+        <is>
+          <t>Public (NASDAQ: IREN)</t>
+        </is>
+      </c>
+      <c r="J54" s="64" t="n"/>
+      <c r="K54" s="64" t="n"/>
+    </row>
+    <row r="55" ht="22" customHeight="1"/>
+    <row r="56" ht="22" customHeight="1">
+      <c r="A56" s="36" t="inlineStr">
+        <is>
+          <t>D. NEOCLOUD SUPPLY CHAIN: WHO THEY LEASE FROM → WHO THEY SELL TO</t>
+        </is>
+      </c>
+      <c r="B56" s="36" t="n"/>
+      <c r="C56" s="36" t="n"/>
+      <c r="D56" s="36" t="n"/>
+      <c r="E56" s="36" t="n"/>
+      <c r="F56" s="36" t="n"/>
+      <c r="G56" s="36" t="n"/>
+      <c r="H56" s="36" t="n"/>
+      <c r="I56" s="36" t="n"/>
+      <c r="J56" s="36" t="n"/>
+      <c r="K56" s="36" t="n"/>
+    </row>
+    <row r="57" ht="22" customHeight="1">
+      <c r="A57" s="45" t="inlineStr">
+        <is>
+          <t>Neocloud Provider</t>
+        </is>
+      </c>
+      <c r="B57" s="37" t="inlineStr">
+        <is>
+          <t>2025 Revenue ($B)</t>
+        </is>
+      </c>
+      <c r="C57" s="37" t="inlineStr">
+        <is>
+          <t>GPU Fleet</t>
+        </is>
+      </c>
+      <c r="D57" s="37" t="inlineStr">
+        <is>
+          <t>Leases DC Space From</t>
+        </is>
+      </c>
+      <c r="E57" s="37" t="inlineStr">
+        <is>
+          <t>Sells Compute To</t>
+        </is>
+      </c>
+      <c r="F57" s="37" t="inlineStr">
+        <is>
+          <t>Largest Contract ($B)</t>
+        </is>
+      </c>
+      <c r="G57" s="37" t="inlineStr">
+        <is>
+          <t>Nvidia Relationship</t>
+        </is>
+      </c>
+      <c r="H57" s="37" t="inlineStr">
+        <is>
+          <t>Capacity (MW)</t>
+        </is>
+      </c>
+      <c r="I57" s="37" t="inlineStr">
+        <is>
+          <t>2026E ARR Target ($B)</t>
+        </is>
+      </c>
+      <c r="J57" s="46" t="inlineStr"/>
+      <c r="K57" s="46" t="inlineStr"/>
+    </row>
+    <row r="58" ht="80" customHeight="1">
+      <c r="A58" s="58" t="inlineStr">
+        <is>
+          <t>CoreWeave (CRWV)</t>
+        </is>
+      </c>
+      <c r="B58" s="63" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="C58" s="59" t="inlineStr">
+        <is>
+          <t>250K+ GPUs</t>
+        </is>
+      </c>
+      <c r="D58" s="66" t="inlineStr">
+        <is>
+          <t>Applied Digital (400 MW)
+Core Scientific (1.3 GW, acquired)
+Digital Crossroads (180 MW)
+Chirisa (Lancaster PA, 300 MW)</t>
+        </is>
+      </c>
+      <c r="E58" s="66" t="inlineStr">
+        <is>
+          <t>OpenAI ($22.4B)
+Meta ($14.2B)
+Microsoft
+Google Cloud
+IBM</t>
+        </is>
+      </c>
+      <c r="F58" s="63" t="n">
+        <v>22.4</v>
+      </c>
+      <c r="G58" s="66" t="inlineStr">
+        <is>
+          <t>Largest customer (62% of 2024 rev). Guarantees leases. $6.3B compute backstop.</t>
+        </is>
+      </c>
+      <c r="H58" s="61" t="inlineStr">
+        <is>
+          <t>1,900</t>
+        </is>
+      </c>
+      <c r="I58" s="59" t="inlineStr">
+        <is>
+          <t>~10–12</t>
+        </is>
+      </c>
+      <c r="J58" s="64" t="n"/>
+      <c r="K58" s="64" t="n"/>
+    </row>
+    <row r="59" ht="80" customHeight="1">
+      <c r="A59" s="58" t="inlineStr">
+        <is>
+          <t>Nebius (NBIS)</t>
+        </is>
+      </c>
+      <c r="B59" s="63" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="C59" s="59" t="inlineStr">
+        <is>
+          <t>~30K+ GPUs</t>
+        </is>
+      </c>
+      <c r="D59" s="66" t="inlineStr">
+        <is>
+          <t>Patmos (Kansas City, colocation)
+Self-built: Vineland NJ (300 MW)
+Planned: Independence MO (800 MW)
+Mega Or (Israel, 80 MW)</t>
+        </is>
+      </c>
+      <c r="E59" s="66" t="inlineStr">
+        <is>
+          <t>Meta ($27B + $3B deals)
+Microsoft (multi-billion)
+AI startups &amp; enterprises</t>
+        </is>
+      </c>
+      <c r="F59" s="63" t="n">
+        <v>27</v>
+      </c>
+      <c r="G59" s="66" t="inlineStr">
+        <is>
+          <t>$2B strategic investment (Mar 2026). Full-stack partnership through Rubin platform.</t>
+        </is>
+      </c>
+      <c r="H59" s="61" t="inlineStr">
+        <is>
+          <t>170 (active)
+3,000+ (target end 2026)</t>
+        </is>
+      </c>
+      <c r="I59" s="59" t="inlineStr">
+        <is>
+          <t>7–9</t>
+        </is>
+      </c>
+      <c r="J59" s="64" t="n"/>
+      <c r="K59" s="64" t="n"/>
+    </row>
+    <row r="60" ht="80" customHeight="1">
+      <c r="A60" s="58" t="inlineStr">
+        <is>
+          <t>IREN</t>
+        </is>
+      </c>
+      <c r="B60" s="63" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="C60" s="59" t="inlineStr">
+        <is>
+          <t>~50K GPUs (target 150K)</t>
+        </is>
+      </c>
+      <c r="D60" s="66" t="inlineStr">
+        <is>
+          <t>Self-owned freehold sites:
+• Childress TX (750 MW)
+• Sweetwater TX
+• Mackenzie BC
+• Canal Flats BC</t>
+        </is>
+      </c>
+      <c r="E60" s="66" t="inlineStr">
+        <is>
+          <t>Microsoft ($9.7B / 5-yr)
+Together AI
+Fluidstack
+Fireworks AI
+Hume</t>
+        </is>
+      </c>
+      <c r="F60" s="63" t="n">
+        <v>9.699999999999999</v>
+      </c>
+      <c r="G60" s="66" t="inlineStr">
+        <is>
+          <t>Purchases Nvidia B300 GPUs. Not equity-backed by Nvidia.</t>
+        </is>
+      </c>
+      <c r="H60" s="61" t="inlineStr">
+        <is>
+          <t>810 (operational)
+2,100 (under construction)</t>
+        </is>
+      </c>
+      <c r="I60" s="59" t="inlineStr">
+        <is>
+          <t>3.4–3.7</t>
+        </is>
+      </c>
+      <c r="J60" s="64" t="n"/>
+      <c r="K60" s="64" t="n"/>
+    </row>
+    <row r="61" ht="22" customHeight="1"/>
+    <row r="62" ht="22" customHeight="1">
+      <c r="A62" s="15" t="inlineStr">
         <is>
           <t>Sources &amp; Notes</t>
         </is>
       </c>
     </row>
-    <row r="46" ht="20" customHeight="1">
-      <c r="A46" s="16" t="inlineStr">
-        <is>
-          <t>Tenant relationships compiled from SEC filings, press releases, and industry reports (Q1 2026). Some relationships are inferred from public filings.</t>
-        </is>
-      </c>
-    </row>
-    <row r="47" ht="20" customHeight="1">
-      <c r="A47" s="16" t="inlineStr">
-        <is>
-          <t>Oracle future lease commitments ($261B) per Oracle FY Q2 2026 10-Q. Microsoft ($155B) and Meta ($104B) per Bloomberg/company filings Mar 2026.</t>
-        </is>
-      </c>
-    </row>
-    <row r="48" ht="20" customHeight="1">
-      <c r="A48" s="16" t="inlineStr">
-        <is>
-          <t>Moody's (Feb 2026): Big-5 hyperscalers hold $969B total undiscounted future lease commitments; $662B is off-balance-sheet (uncommenced).</t>
-        </is>
-      </c>
-    </row>
-    <row r="49" ht="20" customHeight="1">
-      <c r="A49" s="16" t="inlineStr">
-        <is>
-          <t>Crusoe → Oracle → Microsoft → OpenAI represents a multi-layered sublease chain; Stargate JV (Oracle/SoftBank/OpenAI) is a separate structure.</t>
-        </is>
-      </c>
-    </row>
-    <row r="50" ht="20" customHeight="1">
-      <c r="A50" s="16" t="inlineStr">
-        <is>
-          <t>Meta increasingly uses SPV structures (Pimco debt + Blue Owl equity) for build-to-suit DCs, retaining 20% co-ownership while keeping lease off-balance-sheet.</t>
-        </is>
-      </c>
-    </row>
-    <row r="51" ht="20" customHeight="1">
-      <c r="A51" s="16" t="inlineStr">
-        <is>
-          <t>Revenue concentration risk ratings are editorial assessments; 'Extreme' = &gt;80% revenue from a single customer, 'Very High' = &gt;60% from top 2.</t>
-        </is>
-      </c>
-    </row>
-    <row r="52" ht="20" customHeight="1">
-      <c r="A52" s="16" t="inlineStr">
-        <is>
-          <t>✓ = Confirmed tenant/customer relationship.  ~ = Suspected or indirect relationship.  Capacity figures are approximate operational + planned.</t>
-        </is>
-      </c>
-    </row>
-    <row r="53" ht="20" customHeight="1">
-      <c r="A53" s="16" t="inlineStr">
-        <is>
-          <t>Amazon's total future lease commitments are not separately disclosed but estimated at $80-100B based on on-B/S liabilities and industry analysis.</t>
-        </is>
-      </c>
-    </row>
-    <row r="54" ht="20" customHeight="1"/>
+    <row r="63" ht="22" customHeight="1">
+      <c r="A63" s="16" t="inlineStr">
+        <is>
+          <t>Tenant relationships compiled from SEC filings (10-K, 10-Q, S-1), press releases, and industry reports as of Q1 2026.</t>
+        </is>
+      </c>
+    </row>
+    <row r="64" ht="22" customHeight="1">
+      <c r="A64" s="16" t="inlineStr">
+        <is>
+          <t>Oracle future lease commitments ($261B) per 10-Q. Microsoft ($155B) and Meta ($104B) per Bloomberg/company filings Mar 2026.</t>
+        </is>
+      </c>
+    </row>
+    <row r="65" ht="22" customHeight="1">
+      <c r="A65" s="16" t="inlineStr">
+        <is>
+          <t>Moody's (Feb 2026): Big-5 hyperscalers hold $969B total undiscounted future lease commitments; $662B uncommenced (off-balance-sheet).</t>
+        </is>
+      </c>
+    </row>
+    <row r="66" ht="22" customHeight="1">
+      <c r="A66" s="16" t="inlineStr">
+        <is>
+          <t>CoreWeave RPO of $60.7B (Dec 2025 10-K). Revenue $5.1B (2025). Acquired Core Scientific for $9B (Jul 2025). IPO Mar 2025.</t>
+        </is>
+      </c>
+    </row>
+    <row r="67" ht="22" customHeight="1">
+      <c r="A67" s="16" t="inlineStr">
+        <is>
+          <t>Nebius: Meta $27B deal (Mar 2026) + $3B deal (Nov 2025). Microsoft multi-B deal (Sep 2025). Nvidia $2B investment (Mar 2026). Revenue $530M (2025).</t>
+        </is>
+      </c>
+    </row>
+    <row r="68" ht="22" customHeight="1">
+      <c r="A68" s="16" t="inlineStr">
+        <is>
+          <t>IREN: Microsoft $9.7B/5-yr contract (Nov 2025). Revenue ~$960M annualized. Owns all sites freehold. Formerly Iris Energy. 150K GPU target by end 2026.</t>
+        </is>
+      </c>
+    </row>
+    <row r="69" ht="22" customHeight="1">
+      <c r="A69" s="16" t="inlineStr">
+        <is>
+          <t>Crusoe → Oracle → Microsoft → OpenAI is a multi-layered sublease chain; Stargate JV (Oracle/SoftBank/OpenAI) is a separate structure.</t>
+        </is>
+      </c>
+    </row>
+    <row r="70" ht="22" customHeight="1">
+      <c r="A70" s="16" t="inlineStr">
+        <is>
+          <t>✓ = Confirmed tenant/customer.  ~ = Suspected or indirect.  — = Self (not applicable).  Purple rows = neocloud providers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="71" ht="22" customHeight="1">
+      <c r="A71" s="16" t="inlineStr">
+        <is>
+          <t>Concentration risk: Extreme (&gt;80% from 1 customer), Very High (&gt;60% from top 2), High (&gt;40% from top 2), Moderate, Low.</t>
+        </is>
+      </c>
+    </row>
+    <row r="72" ht="22" customHeight="1"/>
   </sheetData>
-  <mergeCells count="13">
-    <mergeCell ref="A47:J47"/>
-    <mergeCell ref="A1:J1"/>
-    <mergeCell ref="A46:J46"/>
-    <mergeCell ref="A22:J22"/>
-    <mergeCell ref="A30:J30"/>
-    <mergeCell ref="A53:J53"/>
-    <mergeCell ref="A50:J50"/>
-    <mergeCell ref="A4:J4"/>
-    <mergeCell ref="A48:J48"/>
-    <mergeCell ref="A51:J51"/>
-    <mergeCell ref="A2:J2"/>
-    <mergeCell ref="A52:J52"/>
-    <mergeCell ref="A49:J49"/>
+  <mergeCells count="15">
+    <mergeCell ref="A70:K70"/>
+    <mergeCell ref="A69:K69"/>
+    <mergeCell ref="A4:K4"/>
+    <mergeCell ref="A26:K26"/>
+    <mergeCell ref="A64:K64"/>
+    <mergeCell ref="A65:K65"/>
+    <mergeCell ref="A2:K2"/>
+    <mergeCell ref="A63:K63"/>
+    <mergeCell ref="A71:K71"/>
+    <mergeCell ref="A68:K68"/>
+    <mergeCell ref="A66:K66"/>
+    <mergeCell ref="A1:K1"/>
+    <mergeCell ref="A37:K37"/>
+    <mergeCell ref="A56:K56"/>
+    <mergeCell ref="A67:K67"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/meta_leases_capex_analysis.xlsx
+++ b/meta_leases_capex_analysis.xlsx
@@ -8,10 +8,11 @@
   </bookViews>
   <sheets>
     <sheet name="Lease Matrix" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="CapEx Comparison" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Meta Leases Detail" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Margin Impact" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Peer Lease Comparison" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Uncommenced Leases &amp; CapEx" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="CapEx Comparison" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Meta Leases Detail" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Margin Impact" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Peer Lease Comparison" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -20,10 +21,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="#,##0.0"/>
     <numFmt numFmtId="165" formatCode="0.0%"/>
     <numFmt numFmtId="166" formatCode="0.00x"/>
+    <numFmt numFmtId="167" formatCode="0.0x"/>
   </numFmts>
   <fonts count="14">
     <font>
@@ -224,7 +226,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="67">
+  <cellXfs count="90">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -403,6 +405,63 @@
     </xf>
     <xf numFmtId="0" fontId="8" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="6" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="6" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="4" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -791,16 +850,6 @@
           <t>Hyperscaler &amp; Neocloud Data Center Lease Matrix</t>
         </is>
       </c>
-      <c r="B1" s="1" t="n"/>
-      <c r="C1" s="1" t="n"/>
-      <c r="D1" s="1" t="n"/>
-      <c r="E1" s="1" t="n"/>
-      <c r="F1" s="1" t="n"/>
-      <c r="G1" s="1" t="n"/>
-      <c r="H1" s="1" t="n"/>
-      <c r="I1" s="1" t="n"/>
-      <c r="J1" s="1" t="n"/>
-      <c r="K1" s="1" t="n"/>
     </row>
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
@@ -808,16 +857,6 @@
           <t>Who leases from whom  |  Q1 2026 data  |  ✓ = confirmed tenant  |  ~ = suspected / indirect  |  Neoclouds highlighted in purple</t>
         </is>
       </c>
-      <c r="B2" s="2" t="n"/>
-      <c r="C2" s="2" t="n"/>
-      <c r="D2" s="2" t="n"/>
-      <c r="E2" s="2" t="n"/>
-      <c r="F2" s="2" t="n"/>
-      <c r="G2" s="2" t="n"/>
-      <c r="H2" s="2" t="n"/>
-      <c r="I2" s="2" t="n"/>
-      <c r="J2" s="2" t="n"/>
-      <c r="K2" s="2" t="n"/>
     </row>
     <row r="3" ht="22" customHeight="1"/>
     <row r="4" ht="22" customHeight="1">
@@ -826,16 +865,6 @@
           <t>A. DATA CENTER OPERATOR / LANDLORD  ×  TENANT MATRIX (Hyperscalers + Neoclouds)</t>
         </is>
       </c>
-      <c r="B4" s="36" t="n"/>
-      <c r="C4" s="36" t="n"/>
-      <c r="D4" s="36" t="n"/>
-      <c r="E4" s="36" t="n"/>
-      <c r="F4" s="36" t="n"/>
-      <c r="G4" s="36" t="n"/>
-      <c r="H4" s="36" t="n"/>
-      <c r="I4" s="36" t="n"/>
-      <c r="J4" s="36" t="n"/>
-      <c r="K4" s="36" t="n"/>
     </row>
     <row r="5" ht="22" customHeight="1">
       <c r="A5" s="37" t="inlineStr">
@@ -1564,16 +1593,6 @@
           <t>B. FUTURE LEASE &amp; CONTRACT COMMITMENTS — HYPERSCALERS + NEOCLOUDS (as of Q1 2026, $B)</t>
         </is>
       </c>
-      <c r="B26" s="36" t="n"/>
-      <c r="C26" s="36" t="n"/>
-      <c r="D26" s="36" t="n"/>
-      <c r="E26" s="36" t="n"/>
-      <c r="F26" s="36" t="n"/>
-      <c r="G26" s="36" t="n"/>
-      <c r="H26" s="36" t="n"/>
-      <c r="I26" s="36" t="n"/>
-      <c r="J26" s="36" t="n"/>
-      <c r="K26" s="36" t="n"/>
     </row>
     <row r="27" ht="22" customHeight="1">
       <c r="A27" s="45" t="inlineStr">
@@ -1975,16 +1994,6 @@
           <t>C. TOP CUSTOMERS / TENANTS BY OPERATOR (Ranked by Estimated Revenue Contribution)</t>
         </is>
       </c>
-      <c r="B37" s="36" t="n"/>
-      <c r="C37" s="36" t="n"/>
-      <c r="D37" s="36" t="n"/>
-      <c r="E37" s="36" t="n"/>
-      <c r="F37" s="36" t="n"/>
-      <c r="G37" s="36" t="n"/>
-      <c r="H37" s="36" t="n"/>
-      <c r="I37" s="36" t="n"/>
-      <c r="J37" s="36" t="n"/>
-      <c r="K37" s="36" t="n"/>
     </row>
     <row r="38" ht="22" customHeight="1">
       <c r="A38" s="45" t="inlineStr">
@@ -2812,16 +2821,6 @@
           <t>D. NEOCLOUD SUPPLY CHAIN: WHO THEY LEASE FROM → WHO THEY SELL TO</t>
         </is>
       </c>
-      <c r="B56" s="36" t="n"/>
-      <c r="C56" s="36" t="n"/>
-      <c r="D56" s="36" t="n"/>
-      <c r="E56" s="36" t="n"/>
-      <c r="F56" s="36" t="n"/>
-      <c r="G56" s="36" t="n"/>
-      <c r="H56" s="36" t="n"/>
-      <c r="I56" s="36" t="n"/>
-      <c r="J56" s="36" t="n"/>
-      <c r="K56" s="36" t="n"/>
     </row>
     <row r="57" ht="22" customHeight="1">
       <c r="A57" s="45" t="inlineStr">
@@ -3129,6 +3128,1680 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:H78"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="38" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Hyperscaler Uncommenced Leases &amp; Capital Expenditure Comparison ($B)</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="n"/>
+      <c r="C1" s="1" t="n"/>
+      <c r="D1" s="1" t="n"/>
+      <c r="E1" s="1" t="n"/>
+      <c r="F1" s="1" t="n"/>
+      <c r="G1" s="1" t="n"/>
+      <c r="H1" s="1" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Data as of end-2025 unless noted  |  Moody's Feb 2026: Big-5 hold $662B in off-B/S uncommenced leases (113% of combined adjusted debt)</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="2" t="n"/>
+      <c r="D2" s="2" t="n"/>
+      <c r="E2" s="2" t="n"/>
+      <c r="F2" s="2" t="n"/>
+      <c r="G2" s="2" t="n"/>
+      <c r="H2" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="36" t="inlineStr">
+        <is>
+          <t>TABLE 1: UNCOMMENCED (OFF-BALANCE-SHEET) LEASES vs ON-BALANCE-SHEET LEASE LIABILITIES</t>
+        </is>
+      </c>
+      <c r="B4" s="36" t="n"/>
+      <c r="C4" s="36" t="n"/>
+      <c r="D4" s="36" t="n"/>
+      <c r="E4" s="36" t="n"/>
+      <c r="F4" s="36" t="n"/>
+      <c r="G4" s="36" t="n"/>
+      <c r="H4" s="36" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="45" t="inlineStr">
+        <is>
+          <t>Metric</t>
+        </is>
+      </c>
+      <c r="B5" s="37" t="inlineStr">
+        <is>
+          <t>Oracle</t>
+        </is>
+      </c>
+      <c r="C5" s="37" t="inlineStr">
+        <is>
+          <t>Microsoft</t>
+        </is>
+      </c>
+      <c r="D5" s="37" t="inlineStr">
+        <is>
+          <t>Amazon</t>
+        </is>
+      </c>
+      <c r="E5" s="37" t="inlineStr">
+        <is>
+          <t>Meta</t>
+        </is>
+      </c>
+      <c r="F5" s="37" t="inlineStr">
+        <is>
+          <t>Alphabet / Google</t>
+        </is>
+      </c>
+      <c r="G5" s="37" t="inlineStr">
+        <is>
+          <t>Big-5 Total</t>
+        </is>
+      </c>
+      <c r="H5" s="46" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="10" t="inlineStr">
+        <is>
+          <t>Uncommenced leases (off-B/S) ($B)</t>
+        </is>
+      </c>
+      <c r="B6" s="23" t="n">
+        <v>248</v>
+      </c>
+      <c r="C6" s="23" t="n">
+        <v>105</v>
+      </c>
+      <c r="D6" s="23" t="n">
+        <v>190</v>
+      </c>
+      <c r="E6" s="23" t="n">
+        <v>78</v>
+      </c>
+      <c r="F6" s="23" t="n">
+        <v>42.6</v>
+      </c>
+      <c r="G6" s="23" t="n">
+        <v>663.6</v>
+      </c>
+      <c r="H6" s="67" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>On-B/S operating lease liabilities ($B)</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="C7" s="5" t="n">
+        <v>32</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>88</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>25.2</v>
+      </c>
+      <c r="F7" s="5" t="n">
+        <v>18</v>
+      </c>
+      <c r="G7" s="5" t="n">
+        <v>172.2</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>On-B/S finance lease liabilities ($B)</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>18</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>72</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F8" s="5" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="G8" s="5" t="n">
+        <v>99.40000000000001</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="10" t="inlineStr">
+        <is>
+          <t>Total on-B/S lease liabilities ($B)</t>
+        </is>
+      </c>
+      <c r="B9" s="18" t="n">
+        <v>13</v>
+      </c>
+      <c r="C9" s="18" t="n">
+        <v>50</v>
+      </c>
+      <c r="D9" s="18" t="n">
+        <v>160</v>
+      </c>
+      <c r="E9" s="18" t="n">
+        <v>26.1</v>
+      </c>
+      <c r="F9" s="18" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="G9" s="18" t="n">
+        <v>271.6</v>
+      </c>
+      <c r="H9" s="68" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="10" t="inlineStr">
+        <is>
+          <t>Total lease exposure (on + off B/S) ($B)</t>
+        </is>
+      </c>
+      <c r="B10" s="69" t="n">
+        <v>261</v>
+      </c>
+      <c r="C10" s="69" t="n">
+        <v>155</v>
+      </c>
+      <c r="D10" s="69" t="n">
+        <v>350</v>
+      </c>
+      <c r="E10" s="69" t="n">
+        <v>104.1</v>
+      </c>
+      <c r="F10" s="69" t="n">
+        <v>65.09999999999999</v>
+      </c>
+      <c r="G10" s="69" t="n">
+        <v>935.2</v>
+      </c>
+      <c r="H10" s="70" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="9" t="n"/>
+      <c r="B11" s="9" t="n"/>
+      <c r="C11" s="9" t="n"/>
+      <c r="D11" s="9" t="n"/>
+      <c r="E11" s="9" t="n"/>
+      <c r="F11" s="9" t="n"/>
+      <c r="G11" s="9" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>2025 Revenue ($B)</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="n">
+        <v>60.4</v>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>281.7</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>716.9</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>201</v>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>402.8</v>
+      </c>
+      <c r="G12" s="5" t="n">
+        <v>1662.8</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="10" t="inlineStr">
+        <is>
+          <t>Total lease exposure / Revenue</t>
+        </is>
+      </c>
+      <c r="B13" s="71" t="n">
+        <v>4.321192052980132</v>
+      </c>
+      <c r="C13" s="72" t="n">
+        <v>0.5502307419240327</v>
+      </c>
+      <c r="D13" s="72" t="n">
+        <v>0.488213139907937</v>
+      </c>
+      <c r="E13" s="72" t="n">
+        <v>0.517910447761194</v>
+      </c>
+      <c r="F13" s="72" t="n">
+        <v>0.1616186693147964</v>
+      </c>
+      <c r="G13" s="72" t="n">
+        <v>0.5624248255953813</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>Uncommenced leases / Revenue</t>
+        </is>
+      </c>
+      <c r="B14" s="73" t="n">
+        <v>4.105960264900662</v>
+      </c>
+      <c r="C14" s="74" t="n">
+        <v>0.3727369542066028</v>
+      </c>
+      <c r="D14" s="74" t="n">
+        <v>0.2650299902357372</v>
+      </c>
+      <c r="E14" s="74" t="n">
+        <v>0.3880597014925373</v>
+      </c>
+      <c r="F14" s="74" t="n">
+        <v>0.105759682224429</v>
+      </c>
+      <c r="G14" s="74" t="n">
+        <v>0.3990858792398365</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>2025 Operating Income ($B)</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="n">
+        <v>16</v>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>128.5</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>80</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>83.3</v>
+      </c>
+      <c r="F15" s="5" t="n">
+        <v>129</v>
+      </c>
+      <c r="G15" s="5" t="n">
+        <v>436.8</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="10" t="inlineStr">
+        <is>
+          <t>Total lease exposure / Op. Income</t>
+        </is>
+      </c>
+      <c r="B16" s="71" t="n">
+        <v>16.3125</v>
+      </c>
+      <c r="C16" s="72" t="n">
+        <v>1.206225680933852</v>
+      </c>
+      <c r="D16" s="71" t="n">
+        <v>4.375</v>
+      </c>
+      <c r="E16" s="72" t="n">
+        <v>1.249699879951981</v>
+      </c>
+      <c r="F16" s="72" t="n">
+        <v>0.5046511627906977</v>
+      </c>
+      <c r="G16" s="72" t="n">
+        <v>2.141025641025641</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>Long-term debt ($B)</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="n">
+        <v>106</v>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>47</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>76</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>58.7</v>
+      </c>
+      <c r="F17" s="5" t="n">
+        <v>12</v>
+      </c>
+      <c r="G17" s="5" t="n">
+        <v>299.7</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="10" t="inlineStr">
+        <is>
+          <t>(Total lease + debt) / Revenue</t>
+        </is>
+      </c>
+      <c r="B18" s="71" t="n">
+        <v>6.076158940397351</v>
+      </c>
+      <c r="C18" s="72" t="n">
+        <v>0.7170749023784168</v>
+      </c>
+      <c r="D18" s="72" t="n">
+        <v>0.5942251360022318</v>
+      </c>
+      <c r="E18" s="72" t="n">
+        <v>0.809950248756219</v>
+      </c>
+      <c r="F18" s="72" t="n">
+        <v>0.1914101290963257</v>
+      </c>
+      <c r="G18" s="72" t="n">
+        <v>0.7426629781092134</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>Share of $662B uncommenced total</t>
+        </is>
+      </c>
+      <c r="B19" s="75" t="n">
+        <v>0.3746223564954683</v>
+      </c>
+      <c r="C19" s="75" t="n">
+        <v>0.1586102719033233</v>
+      </c>
+      <c r="D19" s="75" t="n">
+        <v>0.2870090634441088</v>
+      </c>
+      <c r="E19" s="75" t="n">
+        <v>0.1178247734138973</v>
+      </c>
+      <c r="F19" s="75" t="n">
+        <v>0.06435045317220545</v>
+      </c>
+      <c r="G19" s="75" t="n">
+        <v>1.002416918429003</v>
+      </c>
+      <c r="H19" s="68" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>Uncommenced lease start period</t>
+        </is>
+      </c>
+      <c r="B20" s="76" t="inlineStr">
+        <is>
+          <t>FY2026–FY2028</t>
+        </is>
+      </c>
+      <c r="C20" s="76" t="inlineStr">
+        <is>
+          <t>FY2026–FY2031</t>
+        </is>
+      </c>
+      <c r="D20" s="76" t="inlineStr">
+        <is>
+          <t>2026–2031</t>
+        </is>
+      </c>
+      <c r="E20" s="76" t="inlineStr">
+        <is>
+          <t>2026–2030</t>
+        </is>
+      </c>
+      <c r="F20" s="76" t="inlineStr">
+        <is>
+          <t>2025–2031</t>
+        </is>
+      </c>
+      <c r="G20" s="9" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>Typical lease term (years)</t>
+        </is>
+      </c>
+      <c r="B21" s="76" t="inlineStr">
+        <is>
+          <t>15–19</t>
+        </is>
+      </c>
+      <c r="C21" s="76" t="inlineStr">
+        <is>
+          <t>10–25</t>
+        </is>
+      </c>
+      <c r="D21" s="76" t="inlineStr">
+        <is>
+          <t>10–20</t>
+        </is>
+      </c>
+      <c r="E21" s="76" t="inlineStr">
+        <is>
+          <t>10–25</t>
+        </is>
+      </c>
+      <c r="F21" s="76" t="inlineStr">
+        <is>
+          <t>1–25</t>
+        </is>
+      </c>
+      <c r="G21" s="9" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>Est. annual lease payment at maturity ($B)</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="n">
+        <v>14.6</v>
+      </c>
+      <c r="C22" s="13" t="inlineStr">
+        <is>
+          <t>~8–10</t>
+        </is>
+      </c>
+      <c r="D22" s="13" t="inlineStr">
+        <is>
+          <t>~12–15</t>
+        </is>
+      </c>
+      <c r="E22" s="13" t="inlineStr">
+        <is>
+          <t>~5–7</t>
+        </is>
+      </c>
+      <c r="F22" s="13" t="inlineStr">
+        <is>
+          <t>~3–4</t>
+        </is>
+      </c>
+      <c r="G22" s="13" t="inlineStr">
+        <is>
+          <t>~43–51</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="36" t="inlineStr">
+        <is>
+          <t>TABLE 2: CAPITAL EXPENDITURE BY HYPERSCALER ($B) — INCLUDING FINANCE LEASE PRINCIPAL PAYMENTS</t>
+        </is>
+      </c>
+      <c r="B24" s="36" t="n"/>
+      <c r="C24" s="36" t="n"/>
+      <c r="D24" s="36" t="n"/>
+      <c r="E24" s="36" t="n"/>
+      <c r="F24" s="36" t="n"/>
+      <c r="G24" s="36" t="n"/>
+      <c r="H24" s="36" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="45" t="inlineStr">
+        <is>
+          <t>Metric</t>
+        </is>
+      </c>
+      <c r="B25" s="37" t="inlineStr">
+        <is>
+          <t>Oracle</t>
+        </is>
+      </c>
+      <c r="C25" s="37" t="inlineStr">
+        <is>
+          <t>Microsoft</t>
+        </is>
+      </c>
+      <c r="D25" s="37" t="inlineStr">
+        <is>
+          <t>Amazon</t>
+        </is>
+      </c>
+      <c r="E25" s="37" t="inlineStr">
+        <is>
+          <t>Meta</t>
+        </is>
+      </c>
+      <c r="F25" s="37" t="inlineStr">
+        <is>
+          <t>Alphabet / Google</t>
+        </is>
+      </c>
+      <c r="G25" s="37" t="inlineStr">
+        <is>
+          <t>Big-5 Total</t>
+        </is>
+      </c>
+      <c r="H25" s="46" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>2023 CapEx ($B)</t>
+        </is>
+      </c>
+      <c r="B26" s="77" t="n">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="C26" s="77" t="n">
+        <v>32.2</v>
+      </c>
+      <c r="D26" s="77" t="n">
+        <v>53.7</v>
+      </c>
+      <c r="E26" s="77" t="n">
+        <v>28.1</v>
+      </c>
+      <c r="F26" s="77" t="n">
+        <v>32.3</v>
+      </c>
+      <c r="G26" s="77" t="n">
+        <v>154.6</v>
+      </c>
+      <c r="H26" s="52" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>2024 CapEx ($B)</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="C27" s="5" t="n">
+        <v>55.7</v>
+      </c>
+      <c r="D27" s="5" t="n">
+        <v>83.2</v>
+      </c>
+      <c r="E27" s="5" t="n">
+        <v>39.2</v>
+      </c>
+      <c r="F27" s="5" t="n">
+        <v>52.5</v>
+      </c>
+      <c r="G27" s="5" t="n">
+        <v>243.1</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="10" t="inlineStr">
+        <is>
+          <t>2025 CapEx ($B)</t>
+        </is>
+      </c>
+      <c r="B28" s="78" t="n">
+        <v>35</v>
+      </c>
+      <c r="C28" s="78" t="n">
+        <v>95</v>
+      </c>
+      <c r="D28" s="78" t="n">
+        <v>131.8</v>
+      </c>
+      <c r="E28" s="78" t="n">
+        <v>72.2</v>
+      </c>
+      <c r="F28" s="78" t="n">
+        <v>91.40000000000001</v>
+      </c>
+      <c r="G28" s="78" t="n">
+        <v>425.4</v>
+      </c>
+      <c r="H28" s="52" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="10" t="inlineStr">
+        <is>
+          <t>2026E CapEx — Guidance ($B)</t>
+        </is>
+      </c>
+      <c r="B29" s="18" t="n">
+        <v>50</v>
+      </c>
+      <c r="C29" s="18" t="n">
+        <v>145</v>
+      </c>
+      <c r="D29" s="18" t="n">
+        <v>200</v>
+      </c>
+      <c r="E29" s="18" t="n">
+        <v>125</v>
+      </c>
+      <c r="F29" s="18" t="n">
+        <v>180</v>
+      </c>
+      <c r="G29" s="18" t="n">
+        <v>700</v>
+      </c>
+      <c r="H29" s="68" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="79" t="inlineStr">
+        <is>
+          <t>Year-over-Year CapEx Growth</t>
+        </is>
+      </c>
+      <c r="B30" s="80" t="n"/>
+      <c r="C30" s="80" t="n"/>
+      <c r="D30" s="80" t="n"/>
+      <c r="E30" s="80" t="n"/>
+      <c r="F30" s="80" t="n"/>
+      <c r="G30" s="80" t="n"/>
+      <c r="H30" s="81" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t>2024 vs 2023 growth</t>
+        </is>
+      </c>
+      <c r="B31" s="14" t="n">
+        <v>0.506024096385542</v>
+      </c>
+      <c r="C31" s="14" t="n">
+        <v>0.7298136645962732</v>
+      </c>
+      <c r="D31" s="14" t="n">
+        <v>0.5493482309124766</v>
+      </c>
+      <c r="E31" s="14" t="n">
+        <v>0.395017793594306</v>
+      </c>
+      <c r="F31" s="14" t="n">
+        <v>0.6253869969040249</v>
+      </c>
+      <c r="G31" s="14" t="n">
+        <v>0.572445019404916</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t>2025 vs 2024 growth</t>
+        </is>
+      </c>
+      <c r="B32" s="82" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="C32" s="82" t="n">
+        <v>0.7055655296229801</v>
+      </c>
+      <c r="D32" s="82" t="n">
+        <v>0.5841346153846154</v>
+      </c>
+      <c r="E32" s="82" t="n">
+        <v>0.8418367346938775</v>
+      </c>
+      <c r="F32" s="82" t="n">
+        <v>0.740952380952381</v>
+      </c>
+      <c r="G32" s="82" t="n">
+        <v>0.7498971616618675</v>
+      </c>
+      <c r="H32" s="52" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="10" t="inlineStr">
+        <is>
+          <t>2026E vs 2025 growth</t>
+        </is>
+      </c>
+      <c r="B33" s="30" t="n">
+        <v>0.4285714285714286</v>
+      </c>
+      <c r="C33" s="30" t="n">
+        <v>0.5263157894736843</v>
+      </c>
+      <c r="D33" s="30" t="n">
+        <v>0.5174506828528072</v>
+      </c>
+      <c r="E33" s="30" t="n">
+        <v>0.7313019390581716</v>
+      </c>
+      <c r="F33" s="30" t="n">
+        <v>0.9693654266958422</v>
+      </c>
+      <c r="G33" s="30" t="n">
+        <v>0.6455101081335215</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="79" t="inlineStr">
+        <is>
+          <t>CapEx Intensity (CapEx / Revenue)</t>
+        </is>
+      </c>
+      <c r="B34" s="80" t="n"/>
+      <c r="C34" s="80" t="n"/>
+      <c r="D34" s="80" t="n"/>
+      <c r="E34" s="80" t="n"/>
+      <c r="F34" s="80" t="n"/>
+      <c r="G34" s="80" t="n"/>
+      <c r="H34" s="81" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="4" t="inlineStr">
+        <is>
+          <t>2025 CapEx / Revenue</t>
+        </is>
+      </c>
+      <c r="B35" s="82" t="n">
+        <v>0.5794701986754967</v>
+      </c>
+      <c r="C35" s="82" t="n">
+        <v>0.3372381966631168</v>
+      </c>
+      <c r="D35" s="82" t="n">
+        <v>0.1838471195424746</v>
+      </c>
+      <c r="E35" s="82" t="n">
+        <v>0.3592039800995025</v>
+      </c>
+      <c r="F35" s="82" t="n">
+        <v>0.2269116186693148</v>
+      </c>
+      <c r="G35" s="82" t="n">
+        <v>0.2558335337984123</v>
+      </c>
+      <c r="H35" s="52" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="10" t="inlineStr">
+        <is>
+          <t>2026E CapEx / Revenue (est.)</t>
+        </is>
+      </c>
+      <c r="B36" s="29" t="n">
+        <v>0.7142857142857143</v>
+      </c>
+      <c r="C36" s="30" t="n">
+        <v>0.453125</v>
+      </c>
+      <c r="D36" s="30" t="n">
+        <v>0.2475247524752475</v>
+      </c>
+      <c r="E36" s="30" t="n">
+        <v>0.5040322580645161</v>
+      </c>
+      <c r="F36" s="30" t="n">
+        <v>0.3870967741935484</v>
+      </c>
+      <c r="G36" s="30" t="n">
+        <v>0.3663003663003663</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="79" t="inlineStr">
+        <is>
+          <t>Cumulative CapEx (2023-2026E)</t>
+        </is>
+      </c>
+      <c r="B37" s="80" t="n"/>
+      <c r="C37" s="80" t="n"/>
+      <c r="D37" s="80" t="n"/>
+      <c r="E37" s="80" t="n"/>
+      <c r="F37" s="80" t="n"/>
+      <c r="G37" s="80" t="n"/>
+      <c r="H37" s="81" t="n"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="10" t="inlineStr">
+        <is>
+          <t>Cumulative 2023–2026E CapEx ($B)</t>
+        </is>
+      </c>
+      <c r="B38" s="18" t="n">
+        <v>105.8</v>
+      </c>
+      <c r="C38" s="18" t="n">
+        <v>327.9</v>
+      </c>
+      <c r="D38" s="18" t="n">
+        <v>468.7</v>
+      </c>
+      <c r="E38" s="18" t="n">
+        <v>264.5</v>
+      </c>
+      <c r="F38" s="18" t="n">
+        <v>356.2</v>
+      </c>
+      <c r="G38" s="18" t="n">
+        <v>1523.1</v>
+      </c>
+      <c r="H38" s="68" t="n"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="4" t="inlineStr">
+        <is>
+          <t>Share of cumulative total</t>
+        </is>
+      </c>
+      <c r="B39" s="14" t="n">
+        <v>0.06946359398594971</v>
+      </c>
+      <c r="C39" s="14" t="n">
+        <v>0.2152846168997439</v>
+      </c>
+      <c r="D39" s="14" t="n">
+        <v>0.3077276606920097</v>
+      </c>
+      <c r="E39" s="14" t="n">
+        <v>0.1736589849648743</v>
+      </c>
+      <c r="F39" s="14" t="n">
+        <v>0.2338651434574224</v>
+      </c>
+      <c r="G39" s="14" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="36" t="inlineStr">
+        <is>
+          <t>TABLE 3: COMBINED LEASE + CAPEX INFRASTRUCTURE BURDEN</t>
+        </is>
+      </c>
+      <c r="B41" s="36" t="n"/>
+      <c r="C41" s="36" t="n"/>
+      <c r="D41" s="36" t="n"/>
+      <c r="E41" s="36" t="n"/>
+      <c r="F41" s="36" t="n"/>
+      <c r="G41" s="36" t="n"/>
+      <c r="H41" s="36" t="n"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="45" t="inlineStr">
+        <is>
+          <t>Metric</t>
+        </is>
+      </c>
+      <c r="B42" s="37" t="inlineStr">
+        <is>
+          <t>Oracle</t>
+        </is>
+      </c>
+      <c r="C42" s="37" t="inlineStr">
+        <is>
+          <t>Microsoft</t>
+        </is>
+      </c>
+      <c r="D42" s="37" t="inlineStr">
+        <is>
+          <t>Amazon</t>
+        </is>
+      </c>
+      <c r="E42" s="37" t="inlineStr">
+        <is>
+          <t>Meta</t>
+        </is>
+      </c>
+      <c r="F42" s="37" t="inlineStr">
+        <is>
+          <t>Alphabet / Google</t>
+        </is>
+      </c>
+      <c r="G42" s="37" t="inlineStr">
+        <is>
+          <t>Big-5 Total</t>
+        </is>
+      </c>
+      <c r="H42" s="46" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="4" t="inlineStr">
+        <is>
+          <t>2026E CapEx ($B)</t>
+        </is>
+      </c>
+      <c r="B43" s="5" t="n">
+        <v>50</v>
+      </c>
+      <c r="C43" s="5" t="n">
+        <v>145</v>
+      </c>
+      <c r="D43" s="5" t="n">
+        <v>200</v>
+      </c>
+      <c r="E43" s="5" t="n">
+        <v>125</v>
+      </c>
+      <c r="F43" s="5" t="n">
+        <v>180</v>
+      </c>
+      <c r="G43" s="5" t="n">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="4" t="inlineStr">
+        <is>
+          <t>+ Uncommenced lease obligations ($B)</t>
+        </is>
+      </c>
+      <c r="B44" s="77" t="n">
+        <v>248</v>
+      </c>
+      <c r="C44" s="77" t="n">
+        <v>105</v>
+      </c>
+      <c r="D44" s="77" t="n">
+        <v>190</v>
+      </c>
+      <c r="E44" s="77" t="n">
+        <v>78</v>
+      </c>
+      <c r="F44" s="77" t="n">
+        <v>42.6</v>
+      </c>
+      <c r="G44" s="77" t="n">
+        <v>663.6</v>
+      </c>
+      <c r="H44" s="52" t="n"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="4" t="inlineStr">
+        <is>
+          <t>+ On-B/S lease liabilities ($B)</t>
+        </is>
+      </c>
+      <c r="B45" s="5" t="n">
+        <v>13</v>
+      </c>
+      <c r="C45" s="5" t="n">
+        <v>50</v>
+      </c>
+      <c r="D45" s="5" t="n">
+        <v>160</v>
+      </c>
+      <c r="E45" s="5" t="n">
+        <v>26.1</v>
+      </c>
+      <c r="F45" s="5" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="G45" s="5" t="n">
+        <v>271.6</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="10">
+        <f> Total infra commitment ($B)</f>
+        <v/>
+      </c>
+      <c r="B46" s="69" t="n">
+        <v>311</v>
+      </c>
+      <c r="C46" s="69" t="n">
+        <v>300</v>
+      </c>
+      <c r="D46" s="69" t="n">
+        <v>550</v>
+      </c>
+      <c r="E46" s="69" t="n">
+        <v>229.1</v>
+      </c>
+      <c r="F46" s="69" t="n">
+        <v>245.1</v>
+      </c>
+      <c r="G46" s="69" t="n">
+        <v>1635.2</v>
+      </c>
+      <c r="H46" s="70" t="n"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="9" t="n"/>
+      <c r="B47" s="9" t="n"/>
+      <c r="C47" s="9" t="n"/>
+      <c r="D47" s="9" t="n"/>
+      <c r="E47" s="9" t="n"/>
+      <c r="F47" s="9" t="n"/>
+      <c r="G47" s="9" t="n"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="4" t="inlineStr">
+        <is>
+          <t>2026E Revenue ($B)</t>
+        </is>
+      </c>
+      <c r="B48" s="5" t="n">
+        <v>70</v>
+      </c>
+      <c r="C48" s="5" t="n">
+        <v>320</v>
+      </c>
+      <c r="D48" s="5" t="n">
+        <v>808</v>
+      </c>
+      <c r="E48" s="5" t="n">
+        <v>248</v>
+      </c>
+      <c r="F48" s="5" t="n">
+        <v>465</v>
+      </c>
+      <c r="G48" s="5" t="n">
+        <v>1911</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="10" t="inlineStr">
+        <is>
+          <t>Total infra commitment / Revenue</t>
+        </is>
+      </c>
+      <c r="B49" s="71" t="n">
+        <v>4.442857142857143</v>
+      </c>
+      <c r="C49" s="72" t="n">
+        <v>0.9375</v>
+      </c>
+      <c r="D49" s="72" t="n">
+        <v>0.6806930693069307</v>
+      </c>
+      <c r="E49" s="72" t="n">
+        <v>0.9237903225806451</v>
+      </c>
+      <c r="F49" s="72" t="n">
+        <v>0.5270967741935484</v>
+      </c>
+      <c r="G49" s="72" t="n">
+        <v>0.8556776556776556</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="10" t="inlineStr">
+        <is>
+          <t>Total infra commitment / 2025 Op. Income</t>
+        </is>
+      </c>
+      <c r="B50" s="71" t="n">
+        <v>19.4375</v>
+      </c>
+      <c r="C50" s="72" t="n">
+        <v>2.334630350194553</v>
+      </c>
+      <c r="D50" s="71" t="n">
+        <v>6.875</v>
+      </c>
+      <c r="E50" s="72" t="n">
+        <v>2.750300120048019</v>
+      </c>
+      <c r="F50" s="72" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="G50" s="72" t="n">
+        <v>3.743589743589743</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="4" t="inlineStr">
+        <is>
+          <t>2025 Free Cash Flow ($B)</t>
+        </is>
+      </c>
+      <c r="B51" s="77" t="n">
+        <v>10</v>
+      </c>
+      <c r="C51" s="77" t="n">
+        <v>74</v>
+      </c>
+      <c r="D51" s="77" t="n">
+        <v>36</v>
+      </c>
+      <c r="E51" s="77" t="n">
+        <v>52</v>
+      </c>
+      <c r="F51" s="77" t="n">
+        <v>73</v>
+      </c>
+      <c r="G51" s="77" t="n">
+        <v>245</v>
+      </c>
+      <c r="H51" s="52" t="n"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="10" t="inlineStr">
+        <is>
+          <t>Total infra commitment / FCF</t>
+        </is>
+      </c>
+      <c r="B52" s="71" t="n">
+        <v>31.1</v>
+      </c>
+      <c r="C52" s="72" t="n">
+        <v>4.054054054054054</v>
+      </c>
+      <c r="D52" s="71" t="n">
+        <v>15.27777777777778</v>
+      </c>
+      <c r="E52" s="72" t="n">
+        <v>4.405769230769231</v>
+      </c>
+      <c r="F52" s="72" t="n">
+        <v>3.357534246575343</v>
+      </c>
+      <c r="G52" s="72" t="n">
+        <v>6.674285714285713</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="10" t="inlineStr">
+        <is>
+          <t>Has third-party cloud business?</t>
+        </is>
+      </c>
+      <c r="B53" s="83" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="C53" s="84" t="inlineStr">
+        <is>
+          <t>Yes (Azure)</t>
+        </is>
+      </c>
+      <c r="D53" s="84" t="inlineStr">
+        <is>
+          <t>Yes (AWS)</t>
+        </is>
+      </c>
+      <c r="E53" s="83" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F53" s="84" t="inlineStr">
+        <is>
+          <t>Yes (GCP)</t>
+        </is>
+      </c>
+      <c r="G53" s="84" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="4" t="inlineStr">
+        <is>
+          <t>Credit Rating (Moody's/S&amp;P equiv.)</t>
+        </is>
+      </c>
+      <c r="B54" s="85" t="inlineStr">
+        <is>
+          <t>BBB</t>
+        </is>
+      </c>
+      <c r="C54" s="76" t="inlineStr">
+        <is>
+          <t>AAA</t>
+        </is>
+      </c>
+      <c r="D54" s="76" t="inlineStr">
+        <is>
+          <t>AA</t>
+        </is>
+      </c>
+      <c r="E54" s="76" t="inlineStr">
+        <is>
+          <t>AA-</t>
+        </is>
+      </c>
+      <c r="F54" s="76" t="inlineStr">
+        <is>
+          <t>AA+</t>
+        </is>
+      </c>
+      <c r="G54" s="76" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="36" t="inlineStr">
+        <is>
+          <t>TABLE 4: LEASE vs OWN STRATEGY BY HYPERSCALER</t>
+        </is>
+      </c>
+      <c r="B56" s="36" t="n"/>
+      <c r="C56" s="36" t="n"/>
+      <c r="D56" s="36" t="n"/>
+      <c r="E56" s="36" t="n"/>
+      <c r="F56" s="36" t="n"/>
+      <c r="G56" s="36" t="n"/>
+      <c r="H56" s="36" t="n"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="45" t="inlineStr">
+        <is>
+          <t>Dimension</t>
+        </is>
+      </c>
+      <c r="B57" s="37" t="inlineStr">
+        <is>
+          <t>Oracle</t>
+        </is>
+      </c>
+      <c r="C57" s="37" t="inlineStr">
+        <is>
+          <t>Microsoft</t>
+        </is>
+      </c>
+      <c r="D57" s="37" t="inlineStr">
+        <is>
+          <t>Amazon</t>
+        </is>
+      </c>
+      <c r="E57" s="37" t="inlineStr">
+        <is>
+          <t>Meta</t>
+        </is>
+      </c>
+      <c r="F57" s="37" t="inlineStr">
+        <is>
+          <t>Alphabet / Google</t>
+        </is>
+      </c>
+      <c r="G57" s="46" t="inlineStr"/>
+      <c r="H57" s="46" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="10" t="inlineStr">
+        <is>
+          <t>Primary DC strategy</t>
+        </is>
+      </c>
+      <c r="B58" s="86" t="inlineStr">
+        <is>
+          <t>Lease-heavy</t>
+        </is>
+      </c>
+      <c r="C58" s="86" t="inlineStr">
+        <is>
+          <t>Mix own + lease</t>
+        </is>
+      </c>
+      <c r="D58" s="86" t="inlineStr">
+        <is>
+          <t>Mix own + lease</t>
+        </is>
+      </c>
+      <c r="E58" s="86" t="inlineStr">
+        <is>
+          <t>Own + SPV lease</t>
+        </is>
+      </c>
+      <c r="F58" s="86" t="inlineStr">
+        <is>
+          <t>Mostly own</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="10" t="inlineStr">
+        <is>
+          <t>Lease model</t>
+        </is>
+      </c>
+      <c r="B59" s="76" t="inlineStr">
+        <is>
+          <t>3rd-party triple-net</t>
+        </is>
+      </c>
+      <c r="C59" s="76" t="inlineStr">
+        <is>
+          <t>Build-to-suit + AIP co-invest</t>
+        </is>
+      </c>
+      <c r="D59" s="76" t="inlineStr">
+        <is>
+          <t>Colocation at scale</t>
+        </is>
+      </c>
+      <c r="E59" s="76" t="inlineStr">
+        <is>
+          <t>SPV-financed B2S</t>
+        </is>
+      </c>
+      <c r="F59" s="76" t="inlineStr">
+        <is>
+          <t>Selective colocation</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="10" t="inlineStr">
+        <is>
+          <t>Key lease driver</t>
+        </is>
+      </c>
+      <c r="B60" s="86" t="inlineStr">
+        <is>
+          <t>OpenAI / Stargate</t>
+        </is>
+      </c>
+      <c r="C60" s="86" t="inlineStr">
+        <is>
+          <t>AI capacity race</t>
+        </is>
+      </c>
+      <c r="D60" s="86" t="inlineStr">
+        <is>
+          <t>AWS expansion</t>
+        </is>
+      </c>
+      <c r="E60" s="86" t="inlineStr">
+        <is>
+          <t>AI infra buildout</t>
+        </is>
+      </c>
+      <c r="F60" s="86" t="inlineStr">
+        <is>
+          <t>Speed to capacity</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="10" t="inlineStr">
+        <is>
+          <t>Owns data center buildings?</t>
+        </is>
+      </c>
+      <c r="B61" s="76" t="inlineStr">
+        <is>
+          <t>Minimal</t>
+        </is>
+      </c>
+      <c r="C61" s="76" t="inlineStr">
+        <is>
+          <t>Significant</t>
+        </is>
+      </c>
+      <c r="D61" s="76" t="inlineStr">
+        <is>
+          <t>Significant</t>
+        </is>
+      </c>
+      <c r="E61" s="76" t="inlineStr">
+        <is>
+          <t>Significant</t>
+        </is>
+      </c>
+      <c r="F61" s="76" t="inlineStr">
+        <is>
+          <t>Significant</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="10" t="inlineStr">
+        <is>
+          <t>Finance lease emphasis</t>
+        </is>
+      </c>
+      <c r="B62" s="86" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="C62" s="86" t="inlineStr">
+        <is>
+          <t>Growing</t>
+        </is>
+      </c>
+      <c r="D62" s="86" t="inlineStr">
+        <is>
+          <t>Very High ($72B)</t>
+        </is>
+      </c>
+      <c r="E62" s="86" t="inlineStr">
+        <is>
+          <t>Low (growing)</t>
+        </is>
+      </c>
+      <c r="F62" s="86" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="10" t="inlineStr">
+        <is>
+          <t>Off-B/S risk level</t>
+        </is>
+      </c>
+      <c r="B63" s="83" t="inlineStr">
+        <is>
+          <t>EXTREME</t>
+        </is>
+      </c>
+      <c r="C63" s="87" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="D63" s="87" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="E63" s="88" t="inlineStr">
+        <is>
+          <t>MODERATE–HIGH</t>
+        </is>
+      </c>
+      <c r="F63" s="89" t="inlineStr">
+        <is>
+          <t>LOW–MODERATE</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="10" t="inlineStr">
+        <is>
+          <t>Lease term preference</t>
+        </is>
+      </c>
+      <c r="B64" s="86" t="inlineStr">
+        <is>
+          <t>15–19 years</t>
+        </is>
+      </c>
+      <c r="C64" s="86" t="inlineStr">
+        <is>
+          <t>10–25 years</t>
+        </is>
+      </c>
+      <c r="D64" s="86" t="inlineStr">
+        <is>
+          <t>10–20 years</t>
+        </is>
+      </c>
+      <c r="E64" s="86" t="inlineStr">
+        <is>
+          <t>10–25 years</t>
+        </is>
+      </c>
+      <c r="F64" s="86" t="inlineStr">
+        <is>
+          <t>1–25 years</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="10" t="inlineStr">
+        <is>
+          <t>Power secured (GW est.)</t>
+        </is>
+      </c>
+      <c r="B65" s="76" t="inlineStr">
+        <is>
+          <t>~4.5+ (Stargate)</t>
+        </is>
+      </c>
+      <c r="C65" s="76" t="inlineStr">
+        <is>
+          <t>~10+ (Brookfield)</t>
+        </is>
+      </c>
+      <c r="D65" s="76" t="inlineStr">
+        <is>
+          <t>~10+</t>
+        </is>
+      </c>
+      <c r="E65" s="76" t="inlineStr">
+        <is>
+          <t>~4–5</t>
+        </is>
+      </c>
+      <c r="F65" s="76" t="inlineStr">
+        <is>
+          <t>~5–6</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="15" t="inlineStr">
+        <is>
+          <t>Sources &amp; Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="16" t="inlineStr">
+        <is>
+          <t>Moody's Ratings (Feb 2026): Big-5 hyperscalers hold $969B total undiscounted future lease commitments; $662B uncommenced (off-balance-sheet).</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="16" t="inlineStr">
+        <is>
+          <t>Oracle $248B uncommenced per 10-Q (Nov 30, 2025). Average annual payment at maturity ~$14.6B, vs $22.3B annual operating cash flow.</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="16" t="inlineStr">
+        <is>
+          <t>Microsoft $155B total future lease commitments per Bloomberg (Mar 2026). CNBC (Oct 2024) reported &gt;$100B uncommenced.</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="16" t="inlineStr">
+        <is>
+          <t>Meta $104B total future commitments per Bloomberg (Mar 2026); on-B/S $26.1B per 10-K (Dec 2025). Difference (~$78B) is uncommenced.</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="16" t="inlineStr">
+        <is>
+          <t>Alphabet $42.6B uncommenced per 10-Q (Q3 2025), up from $23.9B in Q2 2025. Commencing 2025–2031 with terms of 1–25 years.</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="16" t="inlineStr">
+        <is>
+          <t>Amazon does not separately disclose uncommenced leases. ~$190B estimated as residual from $662B Moody's total minus other four companies.</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="16" t="inlineStr">
+        <is>
+          <t>CapEx figures include property, equipment, and principal payments on finance leases. 2026E from company guidance (mid-points where ranges given).</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="16" t="inlineStr">
+        <is>
+          <t>Oracle FY ends May 31; figures approximated to calendar year. Microsoft FY ends June 30; CY2025 estimated from quarterly data.</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="16" t="inlineStr">
+        <is>
+          <t>Free cash flow figures are approximate and reflect 2025 actuals or LTM. FCF is after capex and before dividends/buybacks.</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="16" t="inlineStr">
+        <is>
+          <t>Oracle and Meta are the only two Big-5 without a scaled third-party cloud business, making their infrastructure commitment riskier on a return basis.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="19">
+    <mergeCell ref="A77:H77"/>
+    <mergeCell ref="A24:H24"/>
+    <mergeCell ref="A73:H73"/>
+    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A70:H70"/>
+    <mergeCell ref="A78:H78"/>
+    <mergeCell ref="A69:H69"/>
+    <mergeCell ref="A34:G34"/>
+    <mergeCell ref="A30:G30"/>
+    <mergeCell ref="A41:H41"/>
+    <mergeCell ref="A75:H75"/>
+    <mergeCell ref="A74:H74"/>
+    <mergeCell ref="A56:H56"/>
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A71:H71"/>
+    <mergeCell ref="A76:H76"/>
+    <mergeCell ref="A37:G37"/>
+    <mergeCell ref="A4:H4"/>
+    <mergeCell ref="A72:H72"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:K39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -4185,7 +5858,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -5243,7 +6916,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -6218,7 +7891,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>

--- a/meta_leases_capex_analysis.xlsx
+++ b/meta_leases_capex_analysis.xlsx
@@ -9,10 +9,11 @@
   <sheets>
     <sheet name="Lease Matrix" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Uncommenced Leases &amp; CapEx" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="CapEx Comparison" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Meta Leases Detail" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Margin Impact" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Peer Lease Comparison" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Off-BS Debt &amp; PE Pacts" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="CapEx Comparison" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Meta Leases Detail" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Margin Impact" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Peer Lease Comparison" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -226,7 +227,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="90">
+  <cellXfs count="106">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -462,6 +463,54 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -3147,13 +3196,6 @@
           <t>Hyperscaler Uncommenced Leases &amp; Capital Expenditure Comparison ($B)</t>
         </is>
       </c>
-      <c r="B1" s="1" t="n"/>
-      <c r="C1" s="1" t="n"/>
-      <c r="D1" s="1" t="n"/>
-      <c r="E1" s="1" t="n"/>
-      <c r="F1" s="1" t="n"/>
-      <c r="G1" s="1" t="n"/>
-      <c r="H1" s="1" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -3161,13 +3203,6 @@
           <t>Data as of end-2025 unless noted  |  Moody's Feb 2026: Big-5 hold $662B in off-B/S uncommenced leases (113% of combined adjusted debt)</t>
         </is>
       </c>
-      <c r="B2" s="2" t="n"/>
-      <c r="C2" s="2" t="n"/>
-      <c r="D2" s="2" t="n"/>
-      <c r="E2" s="2" t="n"/>
-      <c r="F2" s="2" t="n"/>
-      <c r="G2" s="2" t="n"/>
-      <c r="H2" s="2" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="36" t="inlineStr">
@@ -3175,13 +3210,6 @@
           <t>TABLE 1: UNCOMMENCED (OFF-BALANCE-SHEET) LEASES vs ON-BALANCE-SHEET LEASE LIABILITIES</t>
         </is>
       </c>
-      <c r="B4" s="36" t="n"/>
-      <c r="C4" s="36" t="n"/>
-      <c r="D4" s="36" t="n"/>
-      <c r="E4" s="36" t="n"/>
-      <c r="F4" s="36" t="n"/>
-      <c r="G4" s="36" t="n"/>
-      <c r="H4" s="36" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="45" t="inlineStr">
@@ -3666,13 +3694,6 @@
           <t>TABLE 2: CAPITAL EXPENDITURE BY HYPERSCALER ($B) — INCLUDING FINANCE LEASE PRINCIPAL PAYMENTS</t>
         </is>
       </c>
-      <c r="B24" s="36" t="n"/>
-      <c r="C24" s="36" t="n"/>
-      <c r="D24" s="36" t="n"/>
-      <c r="E24" s="36" t="n"/>
-      <c r="F24" s="36" t="n"/>
-      <c r="G24" s="36" t="n"/>
-      <c r="H24" s="36" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="45" t="inlineStr">
@@ -3821,12 +3842,12 @@
           <t>Year-over-Year CapEx Growth</t>
         </is>
       </c>
-      <c r="B30" s="80" t="n"/>
-      <c r="C30" s="80" t="n"/>
-      <c r="D30" s="80" t="n"/>
-      <c r="E30" s="80" t="n"/>
-      <c r="F30" s="80" t="n"/>
-      <c r="G30" s="80" t="n"/>
+      <c r="B30" s="56" t="n"/>
+      <c r="C30" s="56" t="n"/>
+      <c r="D30" s="56" t="n"/>
+      <c r="E30" s="56" t="n"/>
+      <c r="F30" s="56" t="n"/>
+      <c r="G30" s="57" t="n"/>
       <c r="H30" s="81" t="n"/>
     </row>
     <row r="31">
@@ -3911,12 +3932,12 @@
           <t>CapEx Intensity (CapEx / Revenue)</t>
         </is>
       </c>
-      <c r="B34" s="80" t="n"/>
-      <c r="C34" s="80" t="n"/>
-      <c r="D34" s="80" t="n"/>
-      <c r="E34" s="80" t="n"/>
-      <c r="F34" s="80" t="n"/>
-      <c r="G34" s="80" t="n"/>
+      <c r="B34" s="56" t="n"/>
+      <c r="C34" s="56" t="n"/>
+      <c r="D34" s="56" t="n"/>
+      <c r="E34" s="56" t="n"/>
+      <c r="F34" s="56" t="n"/>
+      <c r="G34" s="57" t="n"/>
       <c r="H34" s="81" t="n"/>
     </row>
     <row r="35">
@@ -3976,12 +3997,12 @@
           <t>Cumulative CapEx (2023-2026E)</t>
         </is>
       </c>
-      <c r="B37" s="80" t="n"/>
-      <c r="C37" s="80" t="n"/>
-      <c r="D37" s="80" t="n"/>
-      <c r="E37" s="80" t="n"/>
-      <c r="F37" s="80" t="n"/>
-      <c r="G37" s="80" t="n"/>
+      <c r="B37" s="56" t="n"/>
+      <c r="C37" s="56" t="n"/>
+      <c r="D37" s="56" t="n"/>
+      <c r="E37" s="56" t="n"/>
+      <c r="F37" s="56" t="n"/>
+      <c r="G37" s="57" t="n"/>
       <c r="H37" s="81" t="n"/>
     </row>
     <row r="38">
@@ -4041,13 +4062,6 @@
           <t>TABLE 3: COMBINED LEASE + CAPEX INFRASTRUCTURE BURDEN</t>
         </is>
       </c>
-      <c r="B41" s="36" t="n"/>
-      <c r="C41" s="36" t="n"/>
-      <c r="D41" s="36" t="n"/>
-      <c r="E41" s="36" t="n"/>
-      <c r="F41" s="36" t="n"/>
-      <c r="G41" s="36" t="n"/>
-      <c r="H41" s="36" t="n"/>
     </row>
     <row r="42">
       <c r="A42" s="45" t="inlineStr">
@@ -4395,13 +4409,6 @@
           <t>TABLE 4: LEASE vs OWN STRATEGY BY HYPERSCALER</t>
         </is>
       </c>
-      <c r="B56" s="36" t="n"/>
-      <c r="C56" s="36" t="n"/>
-      <c r="D56" s="36" t="n"/>
-      <c r="E56" s="36" t="n"/>
-      <c r="F56" s="36" t="n"/>
-      <c r="G56" s="36" t="n"/>
-      <c r="H56" s="36" t="n"/>
     </row>
     <row r="57">
       <c r="A57" s="45" t="inlineStr">
@@ -4802,6 +4809,1843 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:I77"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="28" customWidth="1" min="1" max="1"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="28" customWidth="1" min="6" max="6"/>
+    <col width="28" customWidth="1" min="7" max="7"/>
+    <col width="24" customWidth="1" min="8" max="8"/>
+    <col width="28" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Off-Balance-Sheet Debt &amp; Private Equity / Credit Partnerships by Hyperscaler</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="n"/>
+      <c r="C1" s="1" t="n"/>
+      <c r="D1" s="1" t="n"/>
+      <c r="E1" s="1" t="n"/>
+      <c r="F1" s="1" t="n"/>
+      <c r="G1" s="1" t="n"/>
+      <c r="H1" s="1" t="n"/>
+      <c r="I1" s="1" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Big-5 hyperscalers carry an estimated $1.65T of off-B/S debt, exceeding their ~$1.35T of on-B/S debt (CCIR Research / TEXXR)  |  Data as of mid-2026</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="2" t="n"/>
+      <c r="D2" s="2" t="n"/>
+      <c r="E2" s="2" t="n"/>
+      <c r="F2" s="2" t="n"/>
+      <c r="G2" s="2" t="n"/>
+      <c r="H2" s="2" t="n"/>
+      <c r="I2" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="36" t="inlineStr">
+        <is>
+          <t>TABLE 1: OFF-BALANCE-SHEET SPV / JV DEAL REGISTER BY HYPERSCALER</t>
+        </is>
+      </c>
+      <c r="B4" s="36" t="n"/>
+      <c r="C4" s="36" t="n"/>
+      <c r="D4" s="36" t="n"/>
+      <c r="E4" s="36" t="n"/>
+      <c r="F4" s="36" t="n"/>
+      <c r="G4" s="36" t="n"/>
+      <c r="H4" s="36" t="n"/>
+      <c r="I4" s="36" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="37" t="inlineStr">
+        <is>
+          <t>Hyperscaler</t>
+        </is>
+      </c>
+      <c r="B5" s="37" t="inlineStr">
+        <is>
+          <t>Deal / Vehicle Name</t>
+        </is>
+      </c>
+      <c r="C5" s="37" t="inlineStr">
+        <is>
+          <t>Debt Amount ($B)</t>
+        </is>
+      </c>
+      <c r="D5" s="37" t="inlineStr">
+        <is>
+          <t>Equity ($B)</t>
+        </is>
+      </c>
+      <c r="E5" s="37" t="inlineStr">
+        <is>
+          <t>Total ($B)</t>
+        </is>
+      </c>
+      <c r="F5" s="37" t="inlineStr">
+        <is>
+          <t>PE / Credit Partners</t>
+        </is>
+      </c>
+      <c r="G5" s="37" t="inlineStr">
+        <is>
+          <t>Structure</t>
+        </is>
+      </c>
+      <c r="H5" s="37" t="inlineStr">
+        <is>
+          <t>Counterparty / Tenant</t>
+        </is>
+      </c>
+      <c r="I5" s="37" t="inlineStr">
+        <is>
+          <t>Key Terms &amp; Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="48" customHeight="1">
+      <c r="A6" s="90" t="inlineStr">
+        <is>
+          <t>Meta</t>
+        </is>
+      </c>
+      <c r="B6" s="91" t="inlineStr">
+        <is>
+          <t>Hyperion / Beignet LLC (Louisiana)</t>
+        </is>
+      </c>
+      <c r="C6" s="48" t="n">
+        <v>27.3</v>
+      </c>
+      <c r="D6" s="48" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="E6" s="48" t="n">
+        <v>29.8</v>
+      </c>
+      <c r="F6" s="91" t="inlineStr">
+        <is>
+          <t>Blue Owl (80% equity), PIMCO ($18B), BlackRock ($3B)</t>
+        </is>
+      </c>
+      <c r="G6" s="91" t="inlineStr">
+        <is>
+          <t>SPV project bond; A+ rated; 4-yr rolling lease</t>
+        </is>
+      </c>
+      <c r="H6" s="91" t="inlineStr">
+        <is>
+          <t>Meta (20% equity, developer, operator, sole tenant)</t>
+        </is>
+      </c>
+      <c r="I6" s="91" t="inlineStr">
+        <is>
+          <t>Largest-ever private credit DC deal. 2.06 GW campus. RVG ~$28B. Max exposure ~$46B. 6.58% coupon. Maturity 2049. Morgan Stanley sole bookrunner.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="48" customHeight="1">
+      <c r="A7" s="90" t="inlineStr">
+        <is>
+          <t>Meta</t>
+        </is>
+      </c>
+      <c r="B7" s="91" t="inlineStr">
+        <is>
+          <t>Texas DC SPV (reported)</t>
+        </is>
+      </c>
+      <c r="C7" s="48" t="n">
+        <v>13</v>
+      </c>
+      <c r="D7" s="38" t="n"/>
+      <c r="E7" s="48" t="n">
+        <v>13</v>
+      </c>
+      <c r="F7" s="91" t="inlineStr">
+        <is>
+          <t>Blue Owl (reported lead)</t>
+        </is>
+      </c>
+      <c r="G7" s="91" t="inlineStr">
+        <is>
+          <t>SPV leaseback (in preparation)</t>
+        </is>
+      </c>
+      <c r="H7" s="91" t="inlineStr">
+        <is>
+          <t>Meta (tenant)</t>
+        </is>
+      </c>
+      <c r="I7" s="91" t="inlineStr">
+        <is>
+          <t>Second SPV following Hyperion template. Not yet confirmed at publication.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="48" customHeight="1">
+      <c r="A8" s="90" t="inlineStr">
+        <is>
+          <t>Meta</t>
+        </is>
+      </c>
+      <c r="B8" s="91" t="inlineStr">
+        <is>
+          <t>2024 Leaseback Consortium</t>
+        </is>
+      </c>
+      <c r="C8" s="48" t="n">
+        <v>26</v>
+      </c>
+      <c r="D8" s="48" t="n">
+        <v>3</v>
+      </c>
+      <c r="E8" s="48" t="n">
+        <v>29</v>
+      </c>
+      <c r="F8" s="91" t="inlineStr">
+        <is>
+          <t>Apollo, Brookfield, KKR, Carlyle AlpInvest, PIMCO</t>
+        </is>
+      </c>
+      <c r="G8" s="91" t="inlineStr">
+        <is>
+          <t>Sale-leaseback; private credit consortium</t>
+        </is>
+      </c>
+      <c r="H8" s="91" t="inlineStr">
+        <is>
+          <t>Meta (tenant, operator)</t>
+        </is>
+      </c>
+      <c r="I8" s="91" t="inlineStr">
+        <is>
+          <t>Closed 2024. PE consortium finances construction, owns assets. Meta leases back long-term.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="48" customHeight="1">
+      <c r="A9" s="90" t="inlineStr">
+        <is>
+          <t>Meta</t>
+        </is>
+      </c>
+      <c r="B9" s="91" t="inlineStr">
+        <is>
+          <t>El Paso DC (reported)</t>
+        </is>
+      </c>
+      <c r="C9" s="48" t="n">
+        <v>12</v>
+      </c>
+      <c r="D9" s="38" t="n"/>
+      <c r="E9" s="48" t="n">
+        <v>12</v>
+      </c>
+      <c r="F9" s="91" t="inlineStr">
+        <is>
+          <t>BlackRock (reported lead arranger)</t>
+        </is>
+      </c>
+      <c r="G9" s="91" t="inlineStr">
+        <is>
+          <t>Debt sale / project finance</t>
+        </is>
+      </c>
+      <c r="H9" s="91" t="inlineStr">
+        <is>
+          <t>Meta (tenant)</t>
+        </is>
+      </c>
+      <c r="I9" s="91" t="inlineStr">
+        <is>
+          <t>Reported by FT. Not confirmed. Would add to BlackRock's Meta-linked exposure.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="48" customHeight="1">
+      <c r="A10" s="92" t="inlineStr">
+        <is>
+          <t>Oracle</t>
+        </is>
+      </c>
+      <c r="B10" s="91" t="inlineStr">
+        <is>
+          <t>Stargate — Abilene TX (Crusoe)</t>
+        </is>
+      </c>
+      <c r="C10" s="48" t="n">
+        <v>10</v>
+      </c>
+      <c r="D10" s="48" t="n">
+        <v>3</v>
+      </c>
+      <c r="E10" s="48" t="n">
+        <v>13</v>
+      </c>
+      <c r="F10" s="91" t="inlineStr">
+        <is>
+          <t>Blue Owl, JPMorgan</t>
+        </is>
+      </c>
+      <c r="G10" s="91" t="inlineStr">
+        <is>
+          <t>SPV; Blue Owl equity + JPM debt</t>
+        </is>
+      </c>
+      <c r="H10" s="91" t="inlineStr">
+        <is>
+          <t>Oracle (tenant) → MSFT → OpenAI</t>
+        </is>
+      </c>
+      <c r="I10" s="91" t="inlineStr">
+        <is>
+          <t>Crusoe-developed campus. 15-yr lease. Multi-layered sublease chain to OpenAI.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="48" customHeight="1">
+      <c r="A11" s="92" t="inlineStr">
+        <is>
+          <t>Oracle</t>
+        </is>
+      </c>
+      <c r="B11" s="91" t="inlineStr">
+        <is>
+          <t>Stargate — TX &amp; WI campuses</t>
+        </is>
+      </c>
+      <c r="C11" s="48" t="n">
+        <v>38</v>
+      </c>
+      <c r="D11" s="38" t="n"/>
+      <c r="E11" s="48" t="n">
+        <v>38</v>
+      </c>
+      <c r="F11" s="91" t="inlineStr">
+        <is>
+          <t>JPMorgan (lead), syndicate banks</t>
+        </is>
+      </c>
+      <c r="G11" s="91" t="inlineStr">
+        <is>
+          <t>Syndicated construction loans via SPVs</t>
+        </is>
+      </c>
+      <c r="H11" s="91" t="inlineStr">
+        <is>
+          <t>Oracle (anchor tenant)</t>
+        </is>
+      </c>
+      <c r="I11" s="91" t="inlineStr">
+        <is>
+          <t>JPM encountering diminished syndication interest. Banks wary of Oracle concentration.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="48" customHeight="1">
+      <c r="A12" s="92" t="inlineStr">
+        <is>
+          <t>Oracle</t>
+        </is>
+      </c>
+      <c r="B12" s="91" t="inlineStr">
+        <is>
+          <t>Stargate — New Mexico</t>
+        </is>
+      </c>
+      <c r="C12" s="48" t="n">
+        <v>18</v>
+      </c>
+      <c r="D12" s="38" t="n"/>
+      <c r="E12" s="48" t="n">
+        <v>18</v>
+      </c>
+      <c r="F12" s="91" t="inlineStr">
+        <is>
+          <t>SMBC, MUFG, BNP Paribas, Goldman Sachs + regional lenders</t>
+        </is>
+      </c>
+      <c r="G12" s="91" t="inlineStr">
+        <is>
+          <t>Project finance loan consortium</t>
+        </is>
+      </c>
+      <c r="H12" s="91" t="inlineStr">
+        <is>
+          <t>Oracle (anchor tenant)</t>
+        </is>
+      </c>
+      <c r="I12" s="91" t="inlineStr">
+        <is>
+          <t>4 international banks + regional consortium. EdgeConneX / Stack developer.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="48" customHeight="1">
+      <c r="A13" s="92" t="inlineStr">
+        <is>
+          <t>Oracle</t>
+        </is>
+      </c>
+      <c r="B13" s="91" t="inlineStr">
+        <is>
+          <t>Stargate — additional pipeline</t>
+        </is>
+      </c>
+      <c r="C13" s="38" t="inlineStr">
+        <is>
+          <t>~13+</t>
+        </is>
+      </c>
+      <c r="D13" s="38" t="n"/>
+      <c r="E13" s="38" t="inlineStr">
+        <is>
+          <t>~13+</t>
+        </is>
+      </c>
+      <c r="F13" s="91" t="inlineStr">
+        <is>
+          <t>Various (pipeline)</t>
+        </is>
+      </c>
+      <c r="G13" s="91" t="inlineStr">
+        <is>
+          <t>SPV project finance</t>
+        </is>
+      </c>
+      <c r="H13" s="91" t="inlineStr">
+        <is>
+          <t>Oracle (anchor tenant)</t>
+        </is>
+      </c>
+      <c r="I13" s="91" t="inlineStr">
+        <is>
+          <t>Total reported SPV debt across Stargate campuses ~$72B+. All off Oracle's B/S. Borrows at 7.5% vs own bonds at high-6%.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="48" customHeight="1">
+      <c r="A14" s="93" t="inlineStr">
+        <is>
+          <t>Microsoft</t>
+        </is>
+      </c>
+      <c r="B14" s="91" t="inlineStr">
+        <is>
+          <t>AI Infrastructure Partnership (AIP)</t>
+        </is>
+      </c>
+      <c r="C14" s="38" t="n"/>
+      <c r="D14" s="38" t="inlineStr">
+        <is>
+          <t>~$30B target</t>
+        </is>
+      </c>
+      <c r="E14" s="38" t="inlineStr">
+        <is>
+          <t>Up to $100B</t>
+        </is>
+      </c>
+      <c r="F14" s="91" t="inlineStr">
+        <is>
+          <t>BlackRock / GIP, MGX, Nvidia, xAI, Kuwait IA, Temasek</t>
+        </is>
+      </c>
+      <c r="G14" s="91" t="inlineStr">
+        <is>
+          <t>PE consortium; equity co-investment vehicle</t>
+        </is>
+      </c>
+      <c r="H14" s="91" t="inlineStr">
+        <is>
+          <t>Microsoft (sponsor + offtake)</t>
+        </is>
+      </c>
+      <c r="I14" s="91" t="inlineStr">
+        <is>
+          <t>Formed Sep 2024. First deal: $40B Aligned acquisition (closed Jul 2026) + $5B growth capex. AIP's borrowing is not on MSFT's B/S.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="48" customHeight="1">
+      <c r="A15" s="93" t="inlineStr">
+        <is>
+          <t>Microsoft</t>
+        </is>
+      </c>
+      <c r="B15" s="91" t="inlineStr">
+        <is>
+          <t>Neocloud contract-backed debt (indirect)</t>
+        </is>
+      </c>
+      <c r="C15" s="38" t="n"/>
+      <c r="D15" s="38" t="n"/>
+      <c r="E15" s="38" t="inlineStr">
+        <is>
+          <t>~$25B+</t>
+        </is>
+      </c>
+      <c r="F15" s="91" t="inlineStr">
+        <is>
+          <t>Various PE/credit lenders to CoreWeave, IREN</t>
+        </is>
+      </c>
+      <c r="G15" s="91" t="inlineStr">
+        <is>
+          <t>Indirect: MSFT offtake underwrites neocloud debt</t>
+        </is>
+      </c>
+      <c r="H15" s="91" t="inlineStr">
+        <is>
+          <t>CoreWeave ($22.4B RPO), IREN ($9.7B contract)</t>
+        </is>
+      </c>
+      <c r="I15" s="91" t="inlineStr">
+        <is>
+          <t>Neoclouds raise debt against MSFT contracts. Not MSFT's obligation but economically linked.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="48" customHeight="1">
+      <c r="A16" s="94" t="inlineStr">
+        <is>
+          <t>Amazon</t>
+        </is>
+      </c>
+      <c r="B16" s="91" t="inlineStr">
+        <is>
+          <t>No significant SPV / off-BS structures</t>
+        </is>
+      </c>
+      <c r="C16" s="38" t="n"/>
+      <c r="D16" s="38" t="n"/>
+      <c r="E16" s="38" t="n"/>
+      <c r="F16" s="91" t="inlineStr">
+        <is>
+          <t>N/A — Amazon funds on-balance-sheet</t>
+        </is>
+      </c>
+      <c r="G16" s="91" t="inlineStr">
+        <is>
+          <t>Direct bond issuance + operating cash flow</t>
+        </is>
+      </c>
+      <c r="H16" s="91" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I16" s="91" t="inlineStr">
+        <is>
+          <t>Raised $79B in bonds in 2026 ($25B in Jul). LT debt: $119B. Does NOT use SPV structures. Builds own DC campuses (Project Rainier for Anthropic).</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="48" customHeight="1">
+      <c r="A17" s="94" t="inlineStr">
+        <is>
+          <t>Amazon</t>
+        </is>
+      </c>
+      <c r="B17" s="91" t="inlineStr">
+        <is>
+          <t>Equity investments (not off-BS debt)</t>
+        </is>
+      </c>
+      <c r="C17" s="38" t="n"/>
+      <c r="D17" s="38" t="n"/>
+      <c r="E17" s="38" t="inlineStr">
+        <is>
+          <t>~$70B committed</t>
+        </is>
+      </c>
+      <c r="F17" s="91" t="inlineStr">
+        <is>
+          <t>N/A — strategic equity</t>
+        </is>
+      </c>
+      <c r="G17" s="91" t="inlineStr">
+        <is>
+          <t>$15B invested in OpenAI + $35B equity commitment letter; $20B Anthropic facility</t>
+        </is>
+      </c>
+      <c r="H17" s="91" t="inlineStr">
+        <is>
+          <t>OpenAI, Anthropic</t>
+        </is>
+      </c>
+      <c r="I17" s="91" t="inlineStr">
+        <is>
+          <t>Equity investments, not debt structures. Anthropic facility unlocks as compute milestones met.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="48" customHeight="1">
+      <c r="A18" s="95" t="inlineStr">
+        <is>
+          <t>Alphabet</t>
+        </is>
+      </c>
+      <c r="B18" s="91" t="inlineStr">
+        <is>
+          <t>TeraWulf DC lease backstops</t>
+        </is>
+      </c>
+      <c r="C18" s="38" t="n"/>
+      <c r="D18" s="38" t="n"/>
+      <c r="E18" s="38" t="inlineStr">
+        <is>
+          <t>~$3B guarantee</t>
+        </is>
+      </c>
+      <c r="F18" s="91" t="inlineStr">
+        <is>
+          <t>N/A — Alphabet is guarantor</t>
+        </is>
+      </c>
+      <c r="G18" s="91" t="inlineStr">
+        <is>
+          <t>Credit derivative / lease payment guarantee</t>
+        </is>
+      </c>
+      <c r="H18" s="91" t="inlineStr">
+        <is>
+          <t>TeraWulf (DC developer)</t>
+        </is>
+      </c>
+      <c r="I18" s="91" t="inlineStr">
+        <is>
+          <t>Disclosed in TeraWulf 8-K filings. Up to 15-yr terms. Contingent liability only if TeraWulf defaults.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="48" customHeight="1">
+      <c r="A19" s="95" t="inlineStr">
+        <is>
+          <t>Alphabet</t>
+        </is>
+      </c>
+      <c r="B19" s="91" t="inlineStr">
+        <is>
+          <t>Anthropic TPU deal (Google as guarantor)</t>
+        </is>
+      </c>
+      <c r="C19" s="38" t="n"/>
+      <c r="D19" s="38" t="n"/>
+      <c r="E19" s="38" t="inlineStr">
+        <is>
+          <t>$35B</t>
+        </is>
+      </c>
+      <c r="F19" s="91" t="inlineStr">
+        <is>
+          <t>Apollo, Blackstone (debt providers)</t>
+        </is>
+      </c>
+      <c r="G19" s="91" t="inlineStr">
+        <is>
+          <t>SPV purchases Google TPUs → leases to Anthropic; Google guarantees payments at 5 DCs</t>
+        </is>
+      </c>
+      <c r="H19" s="91" t="inlineStr">
+        <is>
+          <t>Anthropic (lessee), Google (chip supplier + guarantor)</t>
+        </is>
+      </c>
+      <c r="I19" s="91" t="inlineStr">
+        <is>
+          <t>Closed Jun 2026. Tranches: $6B A1 (T+100bp), $24B A2 (5.75%), $4.5B B (8.5%). Broadcom guarantees hardware residual. ~2.5M TPU chips.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="48" customHeight="1">
+      <c r="A20" s="95" t="inlineStr">
+        <is>
+          <t>Alphabet</t>
+        </is>
+      </c>
+      <c r="B20" s="91" t="inlineStr">
+        <is>
+          <t>Hut 8 / Fluidstack backstop</t>
+        </is>
+      </c>
+      <c r="C20" s="38" t="n"/>
+      <c r="D20" s="38" t="n"/>
+      <c r="E20" s="38" t="inlineStr">
+        <is>
+          <t>$7B exposure</t>
+        </is>
+      </c>
+      <c r="F20" s="91" t="inlineStr">
+        <is>
+          <t>N/A — Alphabet is financial backstop</t>
+        </is>
+      </c>
+      <c r="G20" s="91" t="inlineStr">
+        <is>
+          <t>Credit guarantee for lease payments</t>
+        </is>
+      </c>
+      <c r="H20" s="91" t="inlineStr">
+        <is>
+          <t>Fluidstack (tenant), Hut 8 (landlord)</t>
+        </is>
+      </c>
+      <c r="I20" s="91" t="inlineStr">
+        <is>
+          <t>$7B, 15-yr triple-net lease. Google guarantees full base term payments. River Bend LA (245 MW).</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="36" t="inlineStr">
+        <is>
+          <t>TABLE 2: OFF-BALANCE-SHEET DEBT &amp; GUARANTEE SUMMARY BY HYPERSCALER</t>
+        </is>
+      </c>
+      <c r="B23" s="36" t="n"/>
+      <c r="C23" s="36" t="n"/>
+      <c r="D23" s="36" t="n"/>
+      <c r="E23" s="36" t="n"/>
+      <c r="F23" s="36" t="n"/>
+      <c r="G23" s="36" t="n"/>
+      <c r="H23" s="36" t="n"/>
+      <c r="I23" s="36" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="45" t="inlineStr">
+        <is>
+          <t>Metric</t>
+        </is>
+      </c>
+      <c r="B24" s="37" t="inlineStr">
+        <is>
+          <t>Oracle</t>
+        </is>
+      </c>
+      <c r="C24" s="37" t="inlineStr">
+        <is>
+          <t>Meta</t>
+        </is>
+      </c>
+      <c r="D24" s="37" t="inlineStr">
+        <is>
+          <t>Microsoft</t>
+        </is>
+      </c>
+      <c r="E24" s="37" t="inlineStr">
+        <is>
+          <t>Amazon</t>
+        </is>
+      </c>
+      <c r="F24" s="37" t="inlineStr">
+        <is>
+          <t>Alphabet</t>
+        </is>
+      </c>
+      <c r="G24" s="37" t="inlineStr">
+        <is>
+          <t>Big-5 Total</t>
+        </is>
+      </c>
+      <c r="H24" s="46" t="inlineStr"/>
+      <c r="I24" s="46" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="96" t="inlineStr">
+        <is>
+          <t>Est. off-B/S SPV / JV debt ($B)</t>
+        </is>
+      </c>
+      <c r="B25" s="48" t="n">
+        <v>72</v>
+      </c>
+      <c r="C25" s="48" t="n">
+        <v>40</v>
+      </c>
+      <c r="D25" s="38" t="n"/>
+      <c r="E25" s="38" t="n"/>
+      <c r="F25" s="38" t="n"/>
+      <c r="G25" s="38" t="inlineStr">
+        <is>
+          <t>~$120B+</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="97" t="inlineStr">
+        <is>
+          <t>Est. off-B/S guarantees ($B)</t>
+        </is>
+      </c>
+      <c r="B26" s="43" t="n"/>
+      <c r="C26" s="50" t="n">
+        <v>28</v>
+      </c>
+      <c r="D26" s="43" t="n"/>
+      <c r="E26" s="43" t="n"/>
+      <c r="F26" s="50" t="n">
+        <v>45</v>
+      </c>
+      <c r="G26" s="43" t="inlineStr">
+        <is>
+          <t>~$73B+</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="96" t="inlineStr">
+        <is>
+          <t>Indirect exposure (contract-backed) ($B)</t>
+        </is>
+      </c>
+      <c r="B27" s="38" t="n"/>
+      <c r="C27" s="38" t="n"/>
+      <c r="D27" s="48" t="n">
+        <v>25</v>
+      </c>
+      <c r="E27" s="38" t="n"/>
+      <c r="F27" s="38" t="n"/>
+      <c r="G27" s="38" t="inlineStr">
+        <is>
+          <t>~$25B+</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="97" t="inlineStr">
+        <is>
+          <t>Equity investments / commitments ($B)</t>
+        </is>
+      </c>
+      <c r="B28" s="43" t="n"/>
+      <c r="C28" s="43" t="n"/>
+      <c r="D28" s="50" t="n">
+        <v>45</v>
+      </c>
+      <c r="E28" s="50" t="n">
+        <v>70</v>
+      </c>
+      <c r="F28" s="50" t="n">
+        <v>12</v>
+      </c>
+      <c r="G28" s="43" t="inlineStr">
+        <is>
+          <t>~$127B+</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="90" t="inlineStr">
+        <is>
+          <t>Total off-B/S exposure (est.) ($B)</t>
+        </is>
+      </c>
+      <c r="B29" s="98" t="n">
+        <v>72</v>
+      </c>
+      <c r="C29" s="98" t="n">
+        <v>68</v>
+      </c>
+      <c r="D29" s="98" t="n">
+        <v>70</v>
+      </c>
+      <c r="E29" s="98" t="n">
+        <v>70</v>
+      </c>
+      <c r="F29" s="98" t="n">
+        <v>57</v>
+      </c>
+      <c r="G29" s="99" t="inlineStr">
+        <is>
+          <t>~$337B+</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="96" t="inlineStr"/>
+      <c r="B30" s="38" t="inlineStr"/>
+      <c r="C30" s="38" t="inlineStr"/>
+      <c r="D30" s="38" t="inlineStr"/>
+      <c r="E30" s="38" t="inlineStr"/>
+      <c r="F30" s="38" t="inlineStr"/>
+      <c r="G30" s="38" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="96" t="inlineStr">
+        <is>
+          <t>On-B/S long-term debt ($B)</t>
+        </is>
+      </c>
+      <c r="B31" s="48" t="n">
+        <v>106</v>
+      </c>
+      <c r="C31" s="48" t="n">
+        <v>58.7</v>
+      </c>
+      <c r="D31" s="48" t="n">
+        <v>47</v>
+      </c>
+      <c r="E31" s="48" t="n">
+        <v>119.1</v>
+      </c>
+      <c r="F31" s="48" t="n">
+        <v>12</v>
+      </c>
+      <c r="G31" s="48" t="n">
+        <v>342.8</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="97" t="inlineStr">
+        <is>
+          <t>On-B/S total lease liabilities ($B)</t>
+        </is>
+      </c>
+      <c r="B32" s="50" t="n">
+        <v>13</v>
+      </c>
+      <c r="C32" s="50" t="n">
+        <v>26.1</v>
+      </c>
+      <c r="D32" s="50" t="n">
+        <v>50</v>
+      </c>
+      <c r="E32" s="50" t="n">
+        <v>160</v>
+      </c>
+      <c r="F32" s="50" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="G32" s="50" t="n">
+        <v>271.6</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="93" t="inlineStr">
+        <is>
+          <t>Total on-B/S obligations ($B)</t>
+        </is>
+      </c>
+      <c r="B33" s="100" t="n">
+        <v>119</v>
+      </c>
+      <c r="C33" s="100" t="n">
+        <v>84.8</v>
+      </c>
+      <c r="D33" s="100" t="n">
+        <v>97</v>
+      </c>
+      <c r="E33" s="100" t="n">
+        <v>279.1</v>
+      </c>
+      <c r="F33" s="100" t="n">
+        <v>34.5</v>
+      </c>
+      <c r="G33" s="100" t="n">
+        <v>614.4</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="96" t="inlineStr"/>
+      <c r="B34" s="38" t="inlineStr"/>
+      <c r="C34" s="38" t="inlineStr"/>
+      <c r="D34" s="38" t="inlineStr"/>
+      <c r="E34" s="38" t="inlineStr"/>
+      <c r="F34" s="38" t="inlineStr"/>
+      <c r="G34" s="38" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="96" t="inlineStr">
+        <is>
+          <t>Off-B/S exposure / On-B/S obligations</t>
+        </is>
+      </c>
+      <c r="B35" s="49" t="n">
+        <v>0.605</v>
+      </c>
+      <c r="C35" s="49" t="n">
+        <v>0.802</v>
+      </c>
+      <c r="D35" s="49" t="n">
+        <v>0.722</v>
+      </c>
+      <c r="E35" s="49" t="n">
+        <v>0.251</v>
+      </c>
+      <c r="F35" s="49" t="n">
+        <v>1.652</v>
+      </c>
+      <c r="G35" s="38" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="92" t="inlineStr">
+        <is>
+          <t>Total obligations (on + off B/S) ($B)</t>
+        </is>
+      </c>
+      <c r="B36" s="47" t="n">
+        <v>191</v>
+      </c>
+      <c r="C36" s="47" t="n">
+        <v>152.8</v>
+      </c>
+      <c r="D36" s="47" t="n">
+        <v>167</v>
+      </c>
+      <c r="E36" s="47" t="n">
+        <v>349.1</v>
+      </c>
+      <c r="F36" s="47" t="n">
+        <v>91.5</v>
+      </c>
+      <c r="G36" s="47" t="n">
+        <v>951.4</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="96" t="inlineStr">
+        <is>
+          <t>Total obligations / 2025 Revenue</t>
+        </is>
+      </c>
+      <c r="B37" s="48" t="n">
+        <v>3.162251655629139</v>
+      </c>
+      <c r="C37" s="48" t="n">
+        <v>0.7601990049751244</v>
+      </c>
+      <c r="D37" s="48" t="n">
+        <v>0.5928292509762159</v>
+      </c>
+      <c r="E37" s="48" t="n">
+        <v>0.4869577346910309</v>
+      </c>
+      <c r="F37" s="48" t="n">
+        <v>0.2271598808341609</v>
+      </c>
+      <c r="G37" s="48" t="n">
+        <v>0.5721674284339668</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="97" t="inlineStr">
+        <is>
+          <t>Credit rating (S&amp;P equiv.)</t>
+        </is>
+      </c>
+      <c r="B38" s="43" t="inlineStr">
+        <is>
+          <t>BBB</t>
+        </is>
+      </c>
+      <c r="C38" s="43" t="inlineStr">
+        <is>
+          <t>AA–</t>
+        </is>
+      </c>
+      <c r="D38" s="43" t="inlineStr">
+        <is>
+          <t>AAA</t>
+        </is>
+      </c>
+      <c r="E38" s="43" t="inlineStr">
+        <is>
+          <t>AA</t>
+        </is>
+      </c>
+      <c r="F38" s="43" t="inlineStr">
+        <is>
+          <t>AA+</t>
+        </is>
+      </c>
+      <c r="G38" s="43" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="96" t="inlineStr">
+        <is>
+          <t>Off-B/S strategy</t>
+        </is>
+      </c>
+      <c r="B39" s="101" t="inlineStr">
+        <is>
+          <t>AGGRESSIVE</t>
+        </is>
+      </c>
+      <c r="C39" s="101" t="inlineStr">
+        <is>
+          <t>AGGRESSIVE</t>
+        </is>
+      </c>
+      <c r="D39" s="102" t="inlineStr">
+        <is>
+          <t>MODERATE</t>
+        </is>
+      </c>
+      <c r="E39" s="103" t="inlineStr">
+        <is>
+          <t>MINIMAL</t>
+        </is>
+      </c>
+      <c r="F39" s="103" t="inlineStr">
+        <is>
+          <t>MINIMAL</t>
+        </is>
+      </c>
+      <c r="G39" s="38" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="36" t="inlineStr">
+        <is>
+          <t>TABLE 3: PRIVATE EQUITY / CREDIT FIRM — HYPERSCALER EXPOSURE MAP</t>
+        </is>
+      </c>
+      <c r="B42" s="36" t="n"/>
+      <c r="C42" s="36" t="n"/>
+      <c r="D42" s="36" t="n"/>
+      <c r="E42" s="36" t="n"/>
+      <c r="F42" s="36" t="n"/>
+      <c r="G42" s="36" t="n"/>
+      <c r="H42" s="36" t="n"/>
+      <c r="I42" s="36" t="n"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="37" t="inlineStr">
+        <is>
+          <t>PE / Credit Firm</t>
+        </is>
+      </c>
+      <c r="B43" s="37" t="inlineStr">
+        <is>
+          <t>AUM / Platform ($B)</t>
+        </is>
+      </c>
+      <c r="C43" s="37" t="inlineStr">
+        <is>
+          <t>Meta Deals</t>
+        </is>
+      </c>
+      <c r="D43" s="37" t="inlineStr">
+        <is>
+          <t>Oracle Deals</t>
+        </is>
+      </c>
+      <c r="E43" s="37" t="inlineStr">
+        <is>
+          <t>Microsoft Deals</t>
+        </is>
+      </c>
+      <c r="F43" s="37" t="inlineStr">
+        <is>
+          <t>Amazon Deals</t>
+        </is>
+      </c>
+      <c r="G43" s="37" t="inlineStr">
+        <is>
+          <t>Alphabet Deals</t>
+        </is>
+      </c>
+      <c r="H43" s="37" t="inlineStr">
+        <is>
+          <t>Est. Total DC Exposure ($B)</t>
+        </is>
+      </c>
+      <c r="I43" s="37" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="40" customHeight="1">
+      <c r="A44" s="96" t="inlineStr">
+        <is>
+          <t>Blue Owl Capital</t>
+        </is>
+      </c>
+      <c r="B44" s="38" t="inlineStr">
+        <is>
+          <t>~$250</t>
+        </is>
+      </c>
+      <c r="C44" s="104" t="inlineStr">
+        <is>
+          <t>Hyperion ($27B, 80% equity); TX SPV (~$13B)</t>
+        </is>
+      </c>
+      <c r="D44" s="104" t="inlineStr">
+        <is>
+          <t>Abilene SPV ($13B w/ JPM)</t>
+        </is>
+      </c>
+      <c r="E44" s="91" t="inlineStr"/>
+      <c r="F44" s="91" t="inlineStr"/>
+      <c r="G44" s="91" t="inlineStr"/>
+      <c r="H44" s="38" t="inlineStr">
+        <is>
+          <t>~$50+</t>
+        </is>
+      </c>
+      <c r="I44" s="91" t="inlineStr">
+        <is>
+          <t>Linchpin of off-BS DC financing. Manages SPVs, provides equity, arranges debt.</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="40" customHeight="1">
+      <c r="A45" s="97" t="inlineStr">
+        <is>
+          <t>PIMCO</t>
+        </is>
+      </c>
+      <c r="B45" s="43" t="inlineStr">
+        <is>
+          <t>~$1,900</t>
+        </is>
+      </c>
+      <c r="C45" s="104" t="inlineStr">
+        <is>
+          <t>Hyperion ($18B anchor); 2024 consortium</t>
+        </is>
+      </c>
+      <c r="D45" s="105" t="inlineStr"/>
+      <c r="E45" s="105" t="inlineStr"/>
+      <c r="F45" s="105" t="inlineStr"/>
+      <c r="G45" s="105" t="inlineStr"/>
+      <c r="H45" s="43" t="inlineStr">
+        <is>
+          <t>~$20+</t>
+        </is>
+      </c>
+      <c r="I45" s="105" t="inlineStr">
+        <is>
+          <t>Largest single buyer of Meta Hyperion bonds. Insurance/pension capital.</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="40" customHeight="1">
+      <c r="A46" s="96" t="inlineStr">
+        <is>
+          <t>BlackRock / GIP</t>
+        </is>
+      </c>
+      <c r="B46" s="38" t="inlineStr">
+        <is>
+          <t>~$11,500</t>
+        </is>
+      </c>
+      <c r="C46" s="104" t="inlineStr">
+        <is>
+          <t>Hyperion ($3B); El Paso ($12B reported)</t>
+        </is>
+      </c>
+      <c r="D46" s="91" t="inlineStr"/>
+      <c r="E46" s="104" t="inlineStr">
+        <is>
+          <t>AIP co-founder; Aligned ($40B+$5B)</t>
+        </is>
+      </c>
+      <c r="F46" s="91" t="inlineStr"/>
+      <c r="G46" s="104" t="inlineStr">
+        <is>
+          <t>Anthropic TPU deal ($35B, co-lead)</t>
+        </is>
+      </c>
+      <c r="H46" s="38" t="inlineStr">
+        <is>
+          <t>~$90+</t>
+        </is>
+      </c>
+      <c r="I46" s="91" t="inlineStr">
+        <is>
+          <t>Largest asset manager globally. GIP acquired 2024. AIP targets $100B total.</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="40" customHeight="1">
+      <c r="A47" s="97" t="inlineStr">
+        <is>
+          <t>Apollo Global Mgmt</t>
+        </is>
+      </c>
+      <c r="B47" s="43" t="inlineStr">
+        <is>
+          <t>~$700</t>
+        </is>
+      </c>
+      <c r="C47" s="104" t="inlineStr">
+        <is>
+          <t>2024 leaseback consortium</t>
+        </is>
+      </c>
+      <c r="D47" s="105" t="inlineStr"/>
+      <c r="E47" s="105" t="inlineStr"/>
+      <c r="F47" s="105" t="inlineStr"/>
+      <c r="G47" s="104" t="inlineStr">
+        <is>
+          <t>Anthropic TPU deal ($35B, co-lead)</t>
+        </is>
+      </c>
+      <c r="H47" s="43" t="inlineStr">
+        <is>
+          <t>~$35+</t>
+        </is>
+      </c>
+      <c r="I47" s="105" t="inlineStr">
+        <is>
+          <t>Private credit giant. Co-leads Anthropic TPU financing with Blackstone.</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="40" customHeight="1">
+      <c r="A48" s="96" t="inlineStr">
+        <is>
+          <t>Brookfield</t>
+        </is>
+      </c>
+      <c r="B48" s="38" t="inlineStr">
+        <is>
+          <t>~$1,000</t>
+        </is>
+      </c>
+      <c r="C48" s="104" t="inlineStr">
+        <is>
+          <t>2024 leaseback consortium</t>
+        </is>
+      </c>
+      <c r="D48" s="91" t="inlineStr"/>
+      <c r="E48" s="104" t="inlineStr">
+        <is>
+          <t>MSFT 10.5 GW energy deal ($10B)</t>
+        </is>
+      </c>
+      <c r="F48" s="91" t="inlineStr"/>
+      <c r="G48" s="91" t="inlineStr"/>
+      <c r="H48" s="38" t="inlineStr">
+        <is>
+          <t>~$15+</t>
+        </is>
+      </c>
+      <c r="I48" s="91" t="inlineStr">
+        <is>
+          <t>Infra investor. Owns Compass Datacenters. $10B renewable energy pact with MSFT.</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="40" customHeight="1">
+      <c r="A49" s="97" t="inlineStr">
+        <is>
+          <t>KKR</t>
+        </is>
+      </c>
+      <c r="B49" s="43" t="inlineStr">
+        <is>
+          <t>~$600</t>
+        </is>
+      </c>
+      <c r="C49" s="104" t="inlineStr">
+        <is>
+          <t>2024 leaseback consortium</t>
+        </is>
+      </c>
+      <c r="D49" s="105" t="inlineStr"/>
+      <c r="E49" s="105" t="inlineStr"/>
+      <c r="F49" s="105" t="inlineStr"/>
+      <c r="G49" s="105" t="inlineStr"/>
+      <c r="H49" s="43" t="inlineStr">
+        <is>
+          <t>~$5+</t>
+        </is>
+      </c>
+      <c r="I49" s="105" t="inlineStr">
+        <is>
+          <t>Also owns CyrusOne (with GIP, acquired 2022 for $15B).</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="40" customHeight="1">
+      <c r="A50" s="96" t="inlineStr">
+        <is>
+          <t>Carlyle / AlpInvest</t>
+        </is>
+      </c>
+      <c r="B50" s="38" t="inlineStr">
+        <is>
+          <t>~$425</t>
+        </is>
+      </c>
+      <c r="C50" s="104" t="inlineStr">
+        <is>
+          <t>2024 leaseback consortium</t>
+        </is>
+      </c>
+      <c r="D50" s="91" t="inlineStr"/>
+      <c r="E50" s="91" t="inlineStr"/>
+      <c r="F50" s="91" t="inlineStr"/>
+      <c r="G50" s="91" t="inlineStr"/>
+      <c r="H50" s="38" t="inlineStr">
+        <is>
+          <t>~$3+</t>
+        </is>
+      </c>
+      <c r="I50" s="91" t="inlineStr">
+        <is>
+          <t>PE allocation to DC infrastructure through private credit co-investments.</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="40" customHeight="1">
+      <c r="A51" s="97" t="inlineStr">
+        <is>
+          <t>JPMorgan Chase</t>
+        </is>
+      </c>
+      <c r="B51" s="43" t="inlineStr">
+        <is>
+          <t>N/A (bank)</t>
+        </is>
+      </c>
+      <c r="C51" s="105" t="inlineStr"/>
+      <c r="D51" s="104" t="inlineStr">
+        <is>
+          <t>Abilene ($13B w/ Blue Owl); TX/WI ($38B lead)</t>
+        </is>
+      </c>
+      <c r="E51" s="105" t="inlineStr"/>
+      <c r="F51" s="105" t="inlineStr"/>
+      <c r="G51" s="105" t="inlineStr"/>
+      <c r="H51" s="43" t="inlineStr">
+        <is>
+          <t>~$50+</t>
+        </is>
+      </c>
+      <c r="I51" s="105" t="inlineStr">
+        <is>
+          <t>Syndication of Stargate loans encountering pushback. Oracle concentration risk flagged.</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="40" customHeight="1">
+      <c r="A52" s="96" t="inlineStr">
+        <is>
+          <t>SoftBank / MGX</t>
+        </is>
+      </c>
+      <c r="B52" s="38" t="inlineStr">
+        <is>
+          <t>~$400 / sovereign</t>
+        </is>
+      </c>
+      <c r="C52" s="91" t="inlineStr"/>
+      <c r="D52" s="104" t="inlineStr">
+        <is>
+          <t>Stargate JV co-founder ($500B vision)</t>
+        </is>
+      </c>
+      <c r="E52" s="104" t="inlineStr">
+        <is>
+          <t>AIP co-founder (MGX)</t>
+        </is>
+      </c>
+      <c r="F52" s="91" t="inlineStr"/>
+      <c r="G52" s="91" t="inlineStr"/>
+      <c r="H52" s="38" t="inlineStr">
+        <is>
+          <t>~$40+</t>
+        </is>
+      </c>
+      <c r="I52" s="91" t="inlineStr">
+        <is>
+          <t>SoftBank: Stargate + Lordstown OH. MGX (Abu Dhabi): AIP anchor + Aligned deal.</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="40" customHeight="1">
+      <c r="A53" s="97" t="inlineStr">
+        <is>
+          <t>Morgan Stanley</t>
+        </is>
+      </c>
+      <c r="B53" s="43" t="inlineStr">
+        <is>
+          <t>N/A (bank)</t>
+        </is>
+      </c>
+      <c r="C53" s="104" t="inlineStr">
+        <is>
+          <t>Hyperion exclusive advisor + sole bookrunner</t>
+        </is>
+      </c>
+      <c r="D53" s="105" t="inlineStr"/>
+      <c r="E53" s="105" t="inlineStr"/>
+      <c r="F53" s="105" t="inlineStr"/>
+      <c r="G53" s="105" t="inlineStr"/>
+      <c r="H53" s="43" t="inlineStr">
+        <is>
+          <t>Advisor</t>
+        </is>
+      </c>
+      <c r="I53" s="105" t="inlineStr">
+        <is>
+          <t>Arranged Meta's $27B Beignet bond. Projects $800B more private credit for DCs over 2 yrs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="36" t="inlineStr">
+        <is>
+          <t>TABLE 4: BORROWING COST — ON-BALANCE-SHEET vs OFF-BALANCE-SHEET PREMIUM</t>
+        </is>
+      </c>
+      <c r="B56" s="36" t="n"/>
+      <c r="C56" s="36" t="n"/>
+      <c r="D56" s="36" t="n"/>
+      <c r="E56" s="36" t="n"/>
+      <c r="F56" s="36" t="n"/>
+      <c r="G56" s="36" t="n"/>
+      <c r="H56" s="36" t="n"/>
+      <c r="I56" s="36" t="n"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="37" t="inlineStr">
+        <is>
+          <t>Hyperscaler</t>
+        </is>
+      </c>
+      <c r="B57" s="37" t="inlineStr">
+        <is>
+          <t>Credit Rating</t>
+        </is>
+      </c>
+      <c r="C57" s="37" t="inlineStr">
+        <is>
+          <t>On-B/S Bond Yield (%)</t>
+        </is>
+      </c>
+      <c r="D57" s="37" t="inlineStr">
+        <is>
+          <t>Off-B/S SPV Rate (%)</t>
+        </is>
+      </c>
+      <c r="E57" s="37" t="inlineStr">
+        <is>
+          <t>Spread Premium (bps)</t>
+        </is>
+      </c>
+      <c r="F57" s="37" t="inlineStr">
+        <is>
+          <t>Rationale for Premium</t>
+        </is>
+      </c>
+      <c r="G57" s="46" t="inlineStr"/>
+      <c r="H57" s="46" t="inlineStr"/>
+      <c r="I57" s="46" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="96" t="inlineStr">
+        <is>
+          <t>Oracle</t>
+        </is>
+      </c>
+      <c r="B58" s="38" t="inlineStr">
+        <is>
+          <t>BBB</t>
+        </is>
+      </c>
+      <c r="C58" s="38" t="inlineStr">
+        <is>
+          <t>High 6%</t>
+        </is>
+      </c>
+      <c r="D58" s="38" t="inlineStr">
+        <is>
+          <t>7.5%</t>
+        </is>
+      </c>
+      <c r="E58" s="38" t="inlineStr">
+        <is>
+          <t>~75–100</t>
+        </is>
+      </c>
+      <c r="F58" s="41" t="inlineStr">
+        <is>
+          <t>Weakest credit; heavy customer concentration (OpenAI ~half of backlog). Banks resisting syndication.</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="97" t="inlineStr">
+        <is>
+          <t>Meta</t>
+        </is>
+      </c>
+      <c r="B59" s="43" t="inlineStr">
+        <is>
+          <t>AA–</t>
+        </is>
+      </c>
+      <c r="C59" s="43" t="inlineStr">
+        <is>
+          <t>~5.7%</t>
+        </is>
+      </c>
+      <c r="D59" s="43" t="inlineStr">
+        <is>
+          <t>6.58%</t>
+        </is>
+      </c>
+      <c r="E59" s="43" t="inlineStr">
+        <is>
+          <t>~90–100</t>
+        </is>
+      </c>
+      <c r="F59" s="44" t="inlineStr">
+        <is>
+          <t>SPV A+ rated (1 notch below Meta AA–). Premium for structural complexity + 4-yr rolling lease.</t>
+        </is>
+      </c>
+      <c r="G59" s="52" t="n"/>
+      <c r="H59" s="52" t="n"/>
+      <c r="I59" s="52" t="n"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="96" t="inlineStr">
+        <is>
+          <t>Microsoft</t>
+        </is>
+      </c>
+      <c r="B60" s="38" t="inlineStr">
+        <is>
+          <t>AAA</t>
+        </is>
+      </c>
+      <c r="C60" s="38" t="inlineStr">
+        <is>
+          <t>~4.5–5.0%</t>
+        </is>
+      </c>
+      <c r="D60" s="38" t="inlineStr">
+        <is>
+          <t>N/A (indirect)</t>
+        </is>
+      </c>
+      <c r="E60" s="38" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F60" s="41" t="inlineStr">
+        <is>
+          <t>Does not borrow via SPVs directly. AIP fund borrowing separate. Offtake underwrites partner debt.</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="97" t="inlineStr">
+        <is>
+          <t>Amazon</t>
+        </is>
+      </c>
+      <c r="B61" s="43" t="inlineStr">
+        <is>
+          <t>AA</t>
+        </is>
+      </c>
+      <c r="C61" s="43" t="inlineStr">
+        <is>
+          <t>~5.0%</t>
+        </is>
+      </c>
+      <c r="D61" s="43" t="inlineStr">
+        <is>
+          <t>N/A (no SPVs)</t>
+        </is>
+      </c>
+      <c r="E61" s="43" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F61" s="44" t="inlineStr">
+        <is>
+          <t>Funds entirely on own balance sheet. $79B bonds in 2026. No off-BS borrowing.</t>
+        </is>
+      </c>
+      <c r="G61" s="52" t="n"/>
+      <c r="H61" s="52" t="n"/>
+      <c r="I61" s="52" t="n"/>
+    </row>
+    <row r="62">
+      <c r="A62" s="96" t="inlineStr">
+        <is>
+          <t>Alphabet</t>
+        </is>
+      </c>
+      <c r="B62" s="38" t="inlineStr">
+        <is>
+          <t>AA+</t>
+        </is>
+      </c>
+      <c r="C62" s="38" t="inlineStr">
+        <is>
+          <t>~4.8–5.0%</t>
+        </is>
+      </c>
+      <c r="D62" s="38" t="inlineStr">
+        <is>
+          <t>N/A (guarantor only)</t>
+        </is>
+      </c>
+      <c r="E62" s="38" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F62" s="41" t="inlineStr">
+        <is>
+          <t>Self-funds via bonds + equity raise. Off-BS role limited to credit guarantees / backstops.</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="15" t="inlineStr">
+        <is>
+          <t>Sources &amp; Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="16" t="inlineStr">
+        <is>
+          <t>CCIR Research / TEXXR: Big-5 hyperscalers carry ~$1.65T of estimated off-B/S debt, exceeding ~$1.35T on-B/S. Off-BS grew ~8x from 2022.</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="16" t="inlineStr">
+        <is>
+          <t>Meta Hyperion: $27.3B project bond via Beignet Investor LLC (Blue Owl 80%, Meta 20%). PIMCO $18B anchor, BlackRock $3B. S&amp;P rated A+. 6.58% coupon. Maturity 2049.</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="16" t="inlineStr">
+        <is>
+          <t>Meta's max exposure to loss on Hyperion: ~$46B (investment + leases + funding commitments + $28B residual value guarantee). Meta records no guarantee liability (payment 'not probable').</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="16" t="inlineStr">
+        <is>
+          <t>Meta 2024 leaseback: $29B with Apollo, Brookfield, KKR, Carlyle AlpInvest, PIMCO. PE consortium owns assets; Meta leases back long-term. (GlobalDataCenterHub, FT)</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="16" t="inlineStr">
+        <is>
+          <t>Oracle Stargate SPVs: ~$72B total reported debt across 4+ campus vehicles. JPMorgan led TX/WI $38B but encountered syndication pushback due to Oracle concentration. (BI, Jan 2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="16" t="inlineStr">
+        <is>
+          <t>Oracle borrows at 7.5% in SPVs vs own bonds at high-6%. Half of $638B backlog from single customer (OpenAI, $300B contract). BBB credit rating, weakest of Big-5.</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="16" t="inlineStr">
+        <is>
+          <t>Microsoft AIP: formed Sep 2024 with BlackRock/GIP, MGX. $30B equity target, up to $100B incl. debt. First deal: $40B Aligned Data Centers (closed Jul 2026). MSFT is sponsor, not borrower.</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="16" t="inlineStr">
+        <is>
+          <t>Amazon: funds DC buildout entirely on own B/S. $79B bonds in 2026, LT debt $119B. FCF collapsed to $1.2B. No SPV structures. (CNBC, Jul 2026; GlobalDataCenterHub)</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="16" t="inlineStr">
+        <is>
+          <t>Alphabet: off-BS limited to credit derivatives (TeraWulf ~$3B lease backstops; Anthropic TPU $35B guarantee). Self-funds via bonds + Jun 2026 equity raise. (SEC 10-Q, Bloomberg)</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="16" t="inlineStr">
+        <is>
+          <t>Anthropic TPU deal ($35B): Apollo/Blackstone-led. SPV buys Google TPUs, leases to Anthropic. Google guarantees at 5 DCs. Broadcom guarantees hardware residual. (Bloomberg, Jun 2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="16" t="inlineStr">
+        <is>
+          <t>Morgan Stanley projects $800B+ in additional private credit for DC financing over next 2 years. Quinn Emanuel flags emerging litigation risks in off-BS DC structures.</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="16" t="inlineStr">
+        <is>
+          <t>IFR (Nov 2025): Compared Meta's Beignet structure to 'off-balance-sheet gymnastics 24 years after Enron,' noting S&amp;P assigned A+ while acknowledging Meta provides 'all material economic support.'</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="23">
+    <mergeCell ref="A75:I75"/>
+    <mergeCell ref="F61:I61"/>
+    <mergeCell ref="F58:I58"/>
+    <mergeCell ref="A66:I66"/>
+    <mergeCell ref="A56:I56"/>
+    <mergeCell ref="A74:I74"/>
+    <mergeCell ref="F60:I60"/>
+    <mergeCell ref="A2:I2"/>
+    <mergeCell ref="A71:I71"/>
+    <mergeCell ref="A42:I42"/>
+    <mergeCell ref="A76:I76"/>
+    <mergeCell ref="A23:I23"/>
+    <mergeCell ref="A4:I4"/>
+    <mergeCell ref="A72:I72"/>
+    <mergeCell ref="A68:I68"/>
+    <mergeCell ref="F59:I59"/>
+    <mergeCell ref="A67:I67"/>
+    <mergeCell ref="A77:I77"/>
+    <mergeCell ref="A73:I73"/>
+    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="F62:I62"/>
+    <mergeCell ref="A70:I70"/>
+    <mergeCell ref="A69:I69"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:K39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -5858,7 +7702,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -6916,7 +8760,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -7891,7 +9735,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
